--- a/data/upgrade_transactions_100.xlsx
+++ b/data/upgrade_transactions_100.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mappings" sheetId="1" r:id="R2ab8d7943d6848fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="R25dab8e8798e492a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mappings" sheetId="1" r:id="R56bc0976fb894609"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="R9144a53990454e15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contract Artifacts" sheetId="3" r:id="Rb2677b0b54c743c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +65,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -74,6 +75,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF164E63"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF7C2D12"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -252,7 +258,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="65">
+  <x:cellXfs count="75">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -309,16 +315,46 @@
     <x:xf numFmtId="201" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -341,10 +377,10 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -372,7 +408,27 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="2">
+  <x:dxfs count="4">
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDCFCE7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDCFCE7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
     <x:dxf>
       <x:font>
         <x:color rgb="FF166534"/>
@@ -415,9 +471,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpgradeMappings" displayName="UpgradeMappings" ref="A1:Y101" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:Y101"/>
-  <x:tableColumns count="25">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpgradeMappings" displayName="UpgradeMappings" ref="A1:AI101" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:AI101"/>
+  <x:tableColumns count="35">
     <x:tableColumn id="1" name="dataset_id"/>
     <x:tableColumn id="2" name="chain_id"/>
     <x:tableColumn id="3" name="network"/>
@@ -443,8 +499,47 @@
     <x:tableColumn id="23" name="selection_rank_sha256"/>
     <x:tableColumn id="24" name="validation_rpc_host"/>
     <x:tableColumn id="25" name="validated_at_utc"/>
+    <x:tableColumn id="26" name="new_implementation_artifact_dir"/>
+    <x:tableColumn id="27" name="new_implementation_runtime_bytecode_path"/>
+    <x:tableColumn id="28" name="new_implementation_runtime_bytecode_sha256"/>
+    <x:tableColumn id="29" name="new_implementation_runtime_bytecode_size_bytes"/>
+    <x:tableColumn id="30" name="new_implementation_source_available"/>
+    <x:tableColumn id="31" name="new_implementation_source_provider"/>
+    <x:tableColumn id="32" name="new_implementation_source_match"/>
+    <x:tableColumn id="33" name="new_implementation_source_file_count"/>
+    <x:tableColumn id="34" name="new_implementation_contract_name"/>
+    <x:tableColumn id="35" name="new_implementation_compiler_version"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ContractArtifacts" displayName="ContractArtifacts" ref="A1:T86" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:T86"/>
+  <x:tableColumns count="20">
+    <x:tableColumn id="1" name="implementation_address"/>
+    <x:tableColumn id="2" name="mapping_count"/>
+    <x:tableColumn id="3" name="artifact_dir"/>
+    <x:tableColumn id="4" name="runtime_bytecode_path"/>
+    <x:tableColumn id="5" name="runtime_bytecode_sha256"/>
+    <x:tableColumn id="6" name="runtime_bytecode_size_bytes"/>
+    <x:tableColumn id="7" name="source_available"/>
+    <x:tableColumn id="8" name="source_provider"/>
+    <x:tableColumn id="9" name="source_match"/>
+    <x:tableColumn id="10" name="source_file_count"/>
+    <x:tableColumn id="11" name="contract_name"/>
+    <x:tableColumn id="12" name="compiler"/>
+    <x:tableColumn id="13" name="compiler_version"/>
+    <x:tableColumn id="14" name="abi_path"/>
+    <x:tableColumn id="15" name="metadata_path"/>
+    <x:tableColumn id="16" name="standard_json_input_path"/>
+    <x:tableColumn id="17" name="storage_layout_path"/>
+    <x:tableColumn id="18" name="verification_manifest_path"/>
+    <x:tableColumn id="19" name="verification_url"/>
+    <x:tableColumn id="20" name="collected_at_utc"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -668,9 +763,19 @@
     <x:col min="23" max="23" width="68" hidden="0" customWidth="1"/>
     <x:col min="24" max="24" width="25" hidden="0" customWidth="1"/>
     <x:col min="25" max="25" width="22" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="55" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="65" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="68" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="20" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="17" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="18" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="18" hidden="0" customWidth="1"/>
+    <x:col min="33" max="33" width="18" hidden="0" customWidth="1"/>
+    <x:col min="34" max="34" width="24" hidden="0" customWidth="1"/>
+    <x:col min="35" max="35" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="42" customHeight="1">
+    <x:row r="1" ht="50" customHeight="1">
       <x:c r="A1" s="18" t="str">
         <x:v>dataset_id</x:v>
       </x:c>
@@ -745,6 +850,36 @@
       </x:c>
       <x:c r="Y1" s="18" t="str">
         <x:v>validated_at_utc</x:v>
+      </x:c>
+      <x:c r="Z1" s="18" t="str">
+        <x:v>new_implementation_artifact_dir</x:v>
+      </x:c>
+      <x:c r="AA1" s="18" t="str">
+        <x:v>new_implementation_runtime_bytecode_path</x:v>
+      </x:c>
+      <x:c r="AB1" s="18" t="str">
+        <x:v>new_implementation_runtime_bytecode_sha256</x:v>
+      </x:c>
+      <x:c r="AC1" s="18" t="str">
+        <x:v>new_implementation_runtime_bytecode_size_bytes</x:v>
+      </x:c>
+      <x:c r="AD1" s="18" t="str">
+        <x:v>new_implementation_source_available</x:v>
+      </x:c>
+      <x:c r="AE1" s="18" t="str">
+        <x:v>new_implementation_source_provider</x:v>
+      </x:c>
+      <x:c r="AF1" s="18" t="str">
+        <x:v>new_implementation_source_match</x:v>
+      </x:c>
+      <x:c r="AG1" s="18" t="str">
+        <x:v>new_implementation_source_file_count</x:v>
+      </x:c>
+      <x:c r="AH1" s="18" t="str">
+        <x:v>new_implementation_contract_name</x:v>
+      </x:c>
+      <x:c r="AI1" s="18" t="str">
+        <x:v>new_implementation_compiler_version</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
@@ -802,7 +937,7 @@
       <x:c r="R2" s="7" t="n">
         <x:v>43398.73019675926</x:v>
       </x:c>
-      <x:c r="S2" s="8" t="b">
+      <x:c r="S2" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T2" s="22" t="str">
@@ -823,6 +958,32 @@
       <x:c r="Y2" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z2" s="22" t="str">
+        <x:v>contracts/0x33beeb42544f6276c51e4d29c5d62e226fb337fa</x:v>
+      </x:c>
+      <x:c r="AA2" s="22" t="str">
+        <x:v>contracts/0x33beeb42544f6276c51e4d29c5d62e226fb337fa/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB2" s="22" t="str">
+        <x:v>1102918538cf772a2f43a5bc7a107b50033280ae6a7e3505fe0fc6a1e93581b5</x:v>
+      </x:c>
+      <x:c r="AC2" s="20" t="n">
+        <x:v>4902</x:v>
+      </x:c>
+      <x:c r="AD2" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE2" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF2" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG2" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH2" s="22" t="str"/>
+      <x:c r="AI2" s="22" t="str"/>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="22" t="str">
@@ -879,7 +1040,7 @@
       <x:c r="R3" s="7" t="n">
         <x:v>43402.56643518519</x:v>
       </x:c>
-      <x:c r="S3" s="8" t="b">
+      <x:c r="S3" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T3" s="22" t="str">
@@ -900,6 +1061,32 @@
       <x:c r="Y3" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z3" s="22" t="str">
+        <x:v>contracts/0xbdd20d63ff83f5ce8359ee9c7842b4a621f601c2</x:v>
+      </x:c>
+      <x:c r="AA3" s="22" t="str">
+        <x:v>contracts/0xbdd20d63ff83f5ce8359ee9c7842b4a621f601c2/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB3" s="22" t="str">
+        <x:v>dbf702cbdc0d32f67a2c527ff0113f7931a194e2e1d38ba8949c55399161ced3</x:v>
+      </x:c>
+      <x:c r="AC3" s="20" t="n">
+        <x:v>10105</x:v>
+      </x:c>
+      <x:c r="AD3" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE3" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF3" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG3" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH3" s="22" t="str"/>
+      <x:c r="AI3" s="22" t="str"/>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="22" t="str">
@@ -956,7 +1143,7 @@
       <x:c r="R4" s="7" t="n">
         <x:v>43431.30483796296</x:v>
       </x:c>
-      <x:c r="S4" s="8" t="b">
+      <x:c r="S4" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T4" s="22" t="str">
@@ -976,6 +1163,36 @@
       </x:c>
       <x:c r="Y4" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z4" s="22" t="str">
+        <x:v>contracts/0xcfdffa11672688131bbeba3af1596055e0fa7498</x:v>
+      </x:c>
+      <x:c r="AA4" s="22" t="str">
+        <x:v>contracts/0xcfdffa11672688131bbeba3af1596055e0fa7498/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB4" s="22" t="str">
+        <x:v>5e200d6718a6e02fa003036c5f784795fc64f4ce606ae939d1fa01e38d5c40f2</x:v>
+      </x:c>
+      <x:c r="AC4" s="20" t="n">
+        <x:v>6682</x:v>
+      </x:c>
+      <x:c r="AD4" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE4" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF4" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG4" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH4" s="22" t="str">
+        <x:v>Winner</x:v>
+      </x:c>
+      <x:c r="AI4" s="22" t="str">
+        <x:v>0.4.24+commit.e67f0147</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
@@ -1033,7 +1250,7 @@
       <x:c r="R5" s="7" t="n">
         <x:v>43457.496932870374</x:v>
       </x:c>
-      <x:c r="S5" s="8" t="b">
+      <x:c r="S5" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T5" s="22" t="str">
@@ -1054,6 +1271,32 @@
       <x:c r="Y5" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z5" s="22" t="str">
+        <x:v>contracts/0x4394271f0fa7b20b4a2378269b1ef99ddd4ed543</x:v>
+      </x:c>
+      <x:c r="AA5" s="22" t="str">
+        <x:v>contracts/0x4394271f0fa7b20b4a2378269b1ef99ddd4ed543/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB5" s="22" t="str">
+        <x:v>96acce99823b437d80be0cc9c24c1041cdae76f338cee37ffefcce041cd8df19</x:v>
+      </x:c>
+      <x:c r="AC5" s="20" t="n">
+        <x:v>10086</x:v>
+      </x:c>
+      <x:c r="AD5" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE5" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF5" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG5" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH5" s="22" t="str"/>
+      <x:c r="AI5" s="22" t="str"/>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="22" t="str">
@@ -1110,7 +1353,7 @@
       <x:c r="R6" s="7" t="n">
         <x:v>43564.029444444444</x:v>
       </x:c>
-      <x:c r="S6" s="8" t="b">
+      <x:c r="S6" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T6" s="22" t="str">
@@ -1130,6 +1373,36 @@
       </x:c>
       <x:c r="Y6" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z6" s="22" t="str">
+        <x:v>contracts/0x137ceed64037adab752ed4a4afbec1df3d2f0dad</x:v>
+      </x:c>
+      <x:c r="AA6" s="22" t="str">
+        <x:v>contracts/0x137ceed64037adab752ed4a4afbec1df3d2f0dad/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB6" s="22" t="str">
+        <x:v>507e3afe457f66437858843b6a81588a8b2169f17b38833f97f316db9220e8f2</x:v>
+      </x:c>
+      <x:c r="AC6" s="20" t="n">
+        <x:v>5551</x:v>
+      </x:c>
+      <x:c r="AD6" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE6" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF6" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG6" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH6" s="22" t="str">
+        <x:v>Registry</x:v>
+      </x:c>
+      <x:c r="AI6" s="22" t="str">
+        <x:v>0.4.23+commit.124ca40d</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
@@ -1187,7 +1460,7 @@
       <x:c r="R7" s="7" t="n">
         <x:v>43564.15960648148</x:v>
       </x:c>
-      <x:c r="S7" s="8" t="b">
+      <x:c r="S7" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T7" s="22" t="str">
@@ -1208,6 +1481,32 @@
       <x:c r="Y7" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z7" s="22" t="str">
+        <x:v>contracts/0x77521046edd9eb81cffecf55f3aec9bc000d05b2</x:v>
+      </x:c>
+      <x:c r="AA7" s="22" t="str">
+        <x:v>contracts/0x77521046edd9eb81cffecf55f3aec9bc000d05b2/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB7" s="22" t="str">
+        <x:v>d767b43b0f1b24ab5087745de335905dd3a4cc2430b32f9290844982e95ad15f</x:v>
+      </x:c>
+      <x:c r="AC7" s="20" t="n">
+        <x:v>11970</x:v>
+      </x:c>
+      <x:c r="AD7" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE7" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF7" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG7" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH7" s="22" t="str"/>
+      <x:c r="AI7" s="22" t="str"/>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="22" t="str">
@@ -1264,7 +1563,7 @@
       <x:c r="R8" s="7" t="n">
         <x:v>43567.34491898148</x:v>
       </x:c>
-      <x:c r="S8" s="8" t="b">
+      <x:c r="S8" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T8" s="22" t="str">
@@ -1285,6 +1584,32 @@
       <x:c r="Y8" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z8" s="22" t="str">
+        <x:v>contracts/0x81e66a89696c65d4cb1c17cc477afd6be3348c9f</x:v>
+      </x:c>
+      <x:c r="AA8" s="22" t="str">
+        <x:v>contracts/0x81e66a89696c65d4cb1c17cc477afd6be3348c9f/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB8" s="22" t="str">
+        <x:v>19279e531c3d5584444bbddd9af48055d2a8b31c6c7a212cb5327de4ca0c5432</x:v>
+      </x:c>
+      <x:c r="AC8" s="20" t="n">
+        <x:v>1305</x:v>
+      </x:c>
+      <x:c r="AD8" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE8" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF8" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG8" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH8" s="22" t="str"/>
+      <x:c r="AI8" s="22" t="str"/>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="22" t="str">
@@ -1341,7 +1666,7 @@
       <x:c r="R9" s="7" t="n">
         <x:v>43571.48370370371</x:v>
       </x:c>
-      <x:c r="S9" s="8" t="b">
+      <x:c r="S9" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T9" s="22" t="str">
@@ -1362,6 +1687,32 @@
       <x:c r="Y9" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z9" s="22" t="str">
+        <x:v>contracts/0xd642b2892f9fd56d2e6290007909940c5bd83ff8</x:v>
+      </x:c>
+      <x:c r="AA9" s="22" t="str">
+        <x:v>contracts/0xd642b2892f9fd56d2e6290007909940c5bd83ff8/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB9" s="22" t="str">
+        <x:v>e8cd0ee9aa14f08efc41883fdfb726caf9e6cc145844e2e33bddfc47700142ca</x:v>
+      </x:c>
+      <x:c r="AC9" s="20" t="n">
+        <x:v>10290</x:v>
+      </x:c>
+      <x:c r="AD9" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE9" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF9" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG9" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH9" s="22" t="str"/>
+      <x:c r="AI9" s="22" t="str"/>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="22" t="str">
@@ -1418,7 +1769,7 @@
       <x:c r="R10" s="7" t="n">
         <x:v>43574.18407407407</x:v>
       </x:c>
-      <x:c r="S10" s="8" t="b">
+      <x:c r="S10" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T10" s="22" t="str">
@@ -1438,6 +1789,36 @@
       </x:c>
       <x:c r="Y10" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z10" s="22" t="str">
+        <x:v>contracts/0x3592d5037865f425628583ca1ca3bdc069dfcdd8</x:v>
+      </x:c>
+      <x:c r="AA10" s="22" t="str">
+        <x:v>contracts/0x3592d5037865f425628583ca1ca3bdc069dfcdd8/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB10" s="22" t="str">
+        <x:v>f26b82009f29edce69ba73bd69d8c0bf1dfe658c3d2044dbf4e5e79f0e3fb50d</x:v>
+      </x:c>
+      <x:c r="AC10" s="20" t="n">
+        <x:v>13804</x:v>
+      </x:c>
+      <x:c r="AD10" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE10" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF10" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG10" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH10" s="22" t="str">
+        <x:v>TrueAUDMock</x:v>
+      </x:c>
+      <x:c r="AI10" s="22" t="str">
+        <x:v>0.4.23+commit.124ca40d</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
@@ -1495,7 +1876,7 @@
       <x:c r="R11" s="7" t="n">
         <x:v>43581.33482638889</x:v>
       </x:c>
-      <x:c r="S11" s="8" t="b">
+      <x:c r="S11" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T11" s="22" t="str">
@@ -1515,6 +1896,36 @@
       </x:c>
       <x:c r="Y11" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z11" s="22" t="str">
+        <x:v>contracts/0x5dba7dfcdbfb8812d30fdd99d9441f8b7a605621</x:v>
+      </x:c>
+      <x:c r="AA11" s="22" t="str">
+        <x:v>contracts/0x5dba7dfcdbfb8812d30fdd99d9441f8b7a605621/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB11" s="22" t="str">
+        <x:v>c3c3e0bdb6f52cae35d2e69d4e0d042ab5d1fc55c045ad8c5f3b4732ea9a6fba</x:v>
+      </x:c>
+      <x:c r="AC11" s="20" t="n">
+        <x:v>14228</x:v>
+      </x:c>
+      <x:c r="AD11" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE11" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF11" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG11" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AH11" s="22" t="str">
+        <x:v>OKBImplementation</x:v>
+      </x:c>
+      <x:c r="AI11" s="22" t="str">
+        <x:v>0.4.24+commit.e67f0147</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
@@ -1572,7 +1983,7 @@
       <x:c r="R12" s="7" t="n">
         <x:v>43713.80311342593</x:v>
       </x:c>
-      <x:c r="S12" s="8" t="b">
+      <x:c r="S12" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T12" s="22" t="str">
@@ -1592,6 +2003,36 @@
       </x:c>
       <x:c r="Y12" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z12" s="22" t="str">
+        <x:v>contracts/0x3747f235d1e7ae96ebd54bc049cc68b2714d7586</x:v>
+      </x:c>
+      <x:c r="AA12" s="22" t="str">
+        <x:v>contracts/0x3747f235d1e7ae96ebd54bc049cc68b2714d7586/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB12" s="22" t="str">
+        <x:v>e06a8436398dea9deb1fb77a0de082c985002372c461fac81b2f4109db3a9170</x:v>
+      </x:c>
+      <x:c r="AC12" s="20" t="n">
+        <x:v>15447</x:v>
+      </x:c>
+      <x:c r="AD12" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE12" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF12" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG12" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH12" s="22" t="str">
+        <x:v>Vesting</x:v>
+      </x:c>
+      <x:c r="AI12" s="22" t="str">
+        <x:v>0.5.8+commit.23d335f2</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
@@ -1649,7 +2090,7 @@
       <x:c r="R13" s="7" t="n">
         <x:v>43824.69516203704</x:v>
       </x:c>
-      <x:c r="S13" s="8" t="b">
+      <x:c r="S13" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T13" s="22" t="str">
@@ -1670,6 +2111,32 @@
       <x:c r="Y13" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z13" s="22" t="str">
+        <x:v>contracts/0x55429d416d5b2909454cbdce542fc1577f2d2acd</x:v>
+      </x:c>
+      <x:c r="AA13" s="22" t="str">
+        <x:v>contracts/0x55429d416d5b2909454cbdce542fc1577f2d2acd/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB13" s="22" t="str">
+        <x:v>138b45e27568ac06d3b8ee6ede9c31ef093f53d3d824ef8d237790eef2f61280</x:v>
+      </x:c>
+      <x:c r="AC13" s="20" t="n">
+        <x:v>9197</x:v>
+      </x:c>
+      <x:c r="AD13" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE13" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF13" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG13" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH13" s="22" t="str"/>
+      <x:c r="AI13" s="22" t="str"/>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="22" t="str">
@@ -1726,7 +2193,7 @@
       <x:c r="R14" s="7" t="n">
         <x:v>43964.47746527778</x:v>
       </x:c>
-      <x:c r="S14" s="8" t="b">
+      <x:c r="S14" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T14" s="22" t="str">
@@ -1746,6 +2213,36 @@
       </x:c>
       <x:c r="Y14" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z14" s="22" t="str">
+        <x:v>contracts/0x5bfe46a07ce43644e590ad50d1cd0edd23951538</x:v>
+      </x:c>
+      <x:c r="AA14" s="22" t="str">
+        <x:v>contracts/0x5bfe46a07ce43644e590ad50d1cd0edd23951538/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB14" s="22" t="str">
+        <x:v>d81a72901cdf4043a17ed8a5d5d43e6ae97083c6839e088bf7a8e3853ca94d9c</x:v>
+      </x:c>
+      <x:c r="AC14" s="20" t="n">
+        <x:v>16193</x:v>
+      </x:c>
+      <x:c r="AD14" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE14" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF14" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG14" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH14" s="22" t="str">
+        <x:v>EdgeTokenConstructorUpgrade</x:v>
+      </x:c>
+      <x:c r="AI14" s="22" t="str">
+        <x:v>0.5.0+commit.1d4f565a</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
@@ -1803,7 +2300,7 @@
       <x:c r="R15" s="7" t="n">
         <x:v>44041.92490740741</x:v>
       </x:c>
-      <x:c r="S15" s="8" t="b">
+      <x:c r="S15" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T15" s="22" t="str">
@@ -1823,6 +2320,36 @@
       </x:c>
       <x:c r="Y15" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z15" s="22" t="str">
+        <x:v>contracts/0x970f1299a6a95bcace134814ebc40abb0418cdeb</x:v>
+      </x:c>
+      <x:c r="AA15" s="22" t="str">
+        <x:v>contracts/0x970f1299a6a95bcace134814ebc40abb0418cdeb/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB15" s="22" t="str">
+        <x:v>25afd593c3d357dd128a5e8a2395e07f44490ab087ce24e9897709d5ec089054</x:v>
+      </x:c>
+      <x:c r="AC15" s="20" t="n">
+        <x:v>7106</x:v>
+      </x:c>
+      <x:c r="AD15" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE15" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF15" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG15" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH15" s="22" t="str">
+        <x:v>DfDepositToken</x:v>
+      </x:c>
+      <x:c r="AI15" s="22" t="str">
+        <x:v>0.5.17+commit.d19bba13</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
@@ -1880,7 +2407,7 @@
       <x:c r="R16" s="7" t="n">
         <x:v>44089.53800925926</x:v>
       </x:c>
-      <x:c r="S16" s="8" t="b">
+      <x:c r="S16" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T16" s="22" t="str">
@@ -1900,6 +2427,36 @@
       </x:c>
       <x:c r="Y16" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z16" s="22" t="str">
+        <x:v>contracts/0xb2fd6574bbc7f18d9ebfeca4f7a11dfe4b09d740</x:v>
+      </x:c>
+      <x:c r="AA16" s="22" t="str">
+        <x:v>contracts/0xb2fd6574bbc7f18d9ebfeca4f7a11dfe4b09d740/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB16" s="22" t="str">
+        <x:v>22755a7bf7368e732e902a6e2c685f7cb043c9be1402fe8bf1a34ae483af8974</x:v>
+      </x:c>
+      <x:c r="AC16" s="20" t="n">
+        <x:v>13512</x:v>
+      </x:c>
+      <x:c r="AD16" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE16" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF16" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG16" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH16" s="22" t="str">
+        <x:v>DfTokenizedDeposit</x:v>
+      </x:c>
+      <x:c r="AI16" s="22" t="str">
+        <x:v>0.5.17+commit.d19bba13</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
@@ -1957,7 +2514,7 @@
       <x:c r="R17" s="7" t="n">
         <x:v>44119.82194444445</x:v>
       </x:c>
-      <x:c r="S17" s="8" t="b">
+      <x:c r="S17" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T17" s="22" t="str">
@@ -1977,6 +2534,36 @@
       </x:c>
       <x:c r="Y17" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z17" s="22" t="str">
+        <x:v>contracts/0x7f1d120750ca4154f0edb37efbf57982ff7a6a5e</x:v>
+      </x:c>
+      <x:c r="AA17" s="22" t="str">
+        <x:v>contracts/0x7f1d120750ca4154f0edb37efbf57982ff7a6a5e/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB17" s="22" t="str">
+        <x:v>cf0d78cce945aefe553064c6e16baa59900c4c213e5b9157cdf0511d8e6f9628</x:v>
+      </x:c>
+      <x:c r="AC17" s="20" t="n">
+        <x:v>16880</x:v>
+      </x:c>
+      <x:c r="AD17" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE17" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF17" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG17" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH17" s="22" t="str">
+        <x:v>OptionFactory</x:v>
+      </x:c>
+      <x:c r="AI17" s="22" t="str">
+        <x:v>0.6.12+commit.27d51765</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
@@ -2034,7 +2621,7 @@
       <x:c r="R18" s="7" t="n">
         <x:v>44127.68827546296</x:v>
       </x:c>
-      <x:c r="S18" s="8" t="b">
+      <x:c r="S18" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T18" s="22" t="str">
@@ -2054,6 +2641,36 @@
       </x:c>
       <x:c r="Y18" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z18" s="22" t="str">
+        <x:v>contracts/0x5a48866c0faa3947838bd945e85d550d94530ee7</x:v>
+      </x:c>
+      <x:c r="AA18" s="22" t="str">
+        <x:v>contracts/0x5a48866c0faa3947838bd945e85d550d94530ee7/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB18" s="22" t="str">
+        <x:v>6417b8cfb297bd350f33cbffbaee9cc6bb3db506818d255ee5139a6c4064cc86</x:v>
+      </x:c>
+      <x:c r="AC18" s="20" t="n">
+        <x:v>3929</x:v>
+      </x:c>
+      <x:c r="AD18" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE18" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF18" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG18" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH18" s="22" t="str">
+        <x:v>ShareholderVomer</x:v>
+      </x:c>
+      <x:c r="AI18" s="22" t="str">
+        <x:v>0.5.17+commit.d19bba13</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
@@ -2111,7 +2728,7 @@
       <x:c r="R19" s="7" t="n">
         <x:v>44149.31091435185</x:v>
       </x:c>
-      <x:c r="S19" s="8" t="b">
+      <x:c r="S19" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T19" s="22" t="str">
@@ -2132,6 +2749,32 @@
       <x:c r="Y19" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z19" s="22" t="str">
+        <x:v>contracts/0xdd423fb05fccdfc37ea730b8f7965332c19f25f4</x:v>
+      </x:c>
+      <x:c r="AA19" s="22" t="str">
+        <x:v>contracts/0xdd423fb05fccdfc37ea730b8f7965332c19f25f4/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB19" s="22" t="str">
+        <x:v>9859ed131bb8041cbab2127893cb35b464d24f0c74eb4289ab53e8241f72399e</x:v>
+      </x:c>
+      <x:c r="AC19" s="20" t="n">
+        <x:v>7087</x:v>
+      </x:c>
+      <x:c r="AD19" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE19" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF19" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG19" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH19" s="22" t="str"/>
+      <x:c r="AI19" s="22" t="str"/>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="22" t="str">
@@ -2188,7 +2831,7 @@
       <x:c r="R20" s="7" t="n">
         <x:v>44153.284467592595</x:v>
       </x:c>
-      <x:c r="S20" s="8" t="b">
+      <x:c r="S20" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T20" s="22" t="str">
@@ -2208,6 +2851,36 @@
       </x:c>
       <x:c r="Y20" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z20" s="22" t="str">
+        <x:v>contracts/0x76e28a61d9bd58c5ec598a6bc25d8279aea8d2cf</x:v>
+      </x:c>
+      <x:c r="AA20" s="22" t="str">
+        <x:v>contracts/0x76e28a61d9bd58c5ec598a6bc25d8279aea8d2cf/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB20" s="22" t="str">
+        <x:v>853c944c49743d21e8cb2599f1e8fa84fd0b48140507e594d1e300a3b76f8ffa</x:v>
+      </x:c>
+      <x:c r="AC20" s="20" t="n">
+        <x:v>16358</x:v>
+      </x:c>
+      <x:c r="AD20" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE20" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF20" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG20" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH20" s="22" t="str">
+        <x:v>TrueFiPool</x:v>
+      </x:c>
+      <x:c r="AI20" s="22" t="str">
+        <x:v>0.6.10+commit.00c0fcaf</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
@@ -2265,7 +2938,7 @@
       <x:c r="R21" s="7" t="n">
         <x:v>44202.20600694444</x:v>
       </x:c>
-      <x:c r="S21" s="8" t="b">
+      <x:c r="S21" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T21" s="22" t="str">
@@ -2285,6 +2958,36 @@
       </x:c>
       <x:c r="Y21" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z21" s="22" t="str">
+        <x:v>contracts/0x0bcb3b8becaae10acc13fddc0ab09be3351cd30d</x:v>
+      </x:c>
+      <x:c r="AA21" s="22" t="str">
+        <x:v>contracts/0x0bcb3b8becaae10acc13fddc0ab09be3351cd30d/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB21" s="22" t="str">
+        <x:v>808b99798c2563a94b3e9f71a11be1246d21346e6f36826c9b1510939ce87824</x:v>
+      </x:c>
+      <x:c r="AC21" s="20" t="n">
+        <x:v>14970</x:v>
+      </x:c>
+      <x:c r="AD21" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE21" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF21" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG21" s="20" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="AH21" s="22" t="str">
+        <x:v>MozartCoreV2</x:v>
+      </x:c>
+      <x:c r="AI21" s="22" t="str">
+        <x:v>0.5.16+commit.9c3226ce</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
@@ -2342,7 +3045,7 @@
       <x:c r="R22" s="7" t="n">
         <x:v>44205.267175925925</x:v>
       </x:c>
-      <x:c r="S22" s="8" t="b">
+      <x:c r="S22" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T22" s="22" t="str">
@@ -2363,6 +3066,32 @@
       <x:c r="Y22" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z22" s="22" t="str">
+        <x:v>contracts/0xb9ba467bd91aa634e7e3202becc3222644280066</x:v>
+      </x:c>
+      <x:c r="AA22" s="22" t="str">
+        <x:v>contracts/0xb9ba467bd91aa634e7e3202becc3222644280066/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB22" s="22" t="str">
+        <x:v>2f891cd9a463d71bf0c3ec4cb8acd4d812c0d4f6116c04ce5c0df171b3425fb9</x:v>
+      </x:c>
+      <x:c r="AC22" s="20" t="n">
+        <x:v>2676</x:v>
+      </x:c>
+      <x:c r="AD22" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE22" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF22" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG22" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH22" s="22" t="str"/>
+      <x:c r="AI22" s="22" t="str"/>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="22" t="str">
@@ -2419,7 +3148,7 @@
       <x:c r="R23" s="7" t="n">
         <x:v>44214.129212962966</x:v>
       </x:c>
-      <x:c r="S23" s="8" t="b">
+      <x:c r="S23" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T23" s="22" t="str">
@@ -2439,6 +3168,36 @@
       </x:c>
       <x:c r="Y23" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z23" s="22" t="str">
+        <x:v>contracts/0xe6abfcabe24f06197a7a20dc9c81c251f2862430</x:v>
+      </x:c>
+      <x:c r="AA23" s="22" t="str">
+        <x:v>contracts/0xe6abfcabe24f06197a7a20dc9c81c251f2862430/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB23" s="22" t="str">
+        <x:v>6ebc0f7f093351005b9e041aad9ac7408d0b79b6b2da83e4b8deb8ed44d6e798</x:v>
+      </x:c>
+      <x:c r="AC23" s="20" t="n">
+        <x:v>21741</x:v>
+      </x:c>
+      <x:c r="AD23" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE23" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF23" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG23" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH23" s="22" t="str">
+        <x:v>LoopringAmmPool</x:v>
+      </x:c>
+      <x:c r="AI23" s="22" t="str">
+        <x:v>0.7.0+commit.9e61f92b</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
@@ -2496,7 +3255,7 @@
       <x:c r="R24" s="7" t="n">
         <x:v>44222.76116898148</x:v>
       </x:c>
-      <x:c r="S24" s="8" t="b">
+      <x:c r="S24" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T24" s="22" t="str">
@@ -2517,6 +3276,32 @@
       <x:c r="Y24" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z24" s="22" t="str">
+        <x:v>contracts/0x8ee68e86e9f4b7c167e20b198638bec8c46059c2</x:v>
+      </x:c>
+      <x:c r="AA24" s="22" t="str">
+        <x:v>contracts/0x8ee68e86e9f4b7c167e20b198638bec8c46059c2/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB24" s="22" t="str">
+        <x:v>09a5f0e2b744bf40c93ebeb04f9afb565208db2a990d46d6ff2618051cba9af8</x:v>
+      </x:c>
+      <x:c r="AC24" s="20" t="n">
+        <x:v>9437</x:v>
+      </x:c>
+      <x:c r="AD24" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE24" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF24" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG24" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH24" s="22" t="str"/>
+      <x:c r="AI24" s="22" t="str"/>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="22" t="str">
@@ -2573,7 +3358,7 @@
       <x:c r="R25" s="7" t="n">
         <x:v>44252.16027777778</x:v>
       </x:c>
-      <x:c r="S25" s="8" t="b">
+      <x:c r="S25" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T25" s="22" t="str">
@@ -2593,6 +3378,36 @@
       </x:c>
       <x:c r="Y25" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z25" s="22" t="str">
+        <x:v>contracts/0x28ecb9b0fb44873106fc1b31bc9189b3f82cf517</x:v>
+      </x:c>
+      <x:c r="AA25" s="22" t="str">
+        <x:v>contracts/0x28ecb9b0fb44873106fc1b31bc9189b3f82cf517/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB25" s="22" t="str">
+        <x:v>6b8f14e6e1dad26aeadbcee7f2117c99139c353184385d16704116148fbf92c4</x:v>
+      </x:c>
+      <x:c r="AC25" s="20" t="n">
+        <x:v>10812</x:v>
+      </x:c>
+      <x:c r="AD25" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE25" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF25" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG25" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH25" s="22" t="str">
+        <x:v>CrossDelegate</x:v>
+      </x:c>
+      <x:c r="AI25" s="22" t="str">
+        <x:v>0.4.26+commit.4563c3fc</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
@@ -2650,7 +3465,7 @@
       <x:c r="R26" s="7" t="n">
         <x:v>44252.547627314816</x:v>
       </x:c>
-      <x:c r="S26" s="8" t="b">
+      <x:c r="S26" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T26" s="22" t="str">
@@ -2670,6 +3485,36 @@
       </x:c>
       <x:c r="Y26" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z26" s="22" t="str">
+        <x:v>contracts/0xe6abfcabe24f06197a7a20dc9c81c251f2862430</x:v>
+      </x:c>
+      <x:c r="AA26" s="22" t="str">
+        <x:v>contracts/0xe6abfcabe24f06197a7a20dc9c81c251f2862430/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB26" s="22" t="str">
+        <x:v>6ebc0f7f093351005b9e041aad9ac7408d0b79b6b2da83e4b8deb8ed44d6e798</x:v>
+      </x:c>
+      <x:c r="AC26" s="20" t="n">
+        <x:v>21741</x:v>
+      </x:c>
+      <x:c r="AD26" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE26" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF26" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG26" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH26" s="22" t="str">
+        <x:v>LoopringAmmPool</x:v>
+      </x:c>
+      <x:c r="AI26" s="22" t="str">
+        <x:v>0.7.0+commit.9e61f92b</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="18" customHeight="1">
@@ -2727,7 +3572,7 @@
       <x:c r="R27" s="7" t="n">
         <x:v>44272.31568287037</x:v>
       </x:c>
-      <x:c r="S27" s="8" t="b">
+      <x:c r="S27" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T27" s="22" t="str">
@@ -2747,6 +3592,36 @@
       </x:c>
       <x:c r="Y27" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z27" s="22" t="str">
+        <x:v>contracts/0xe6abfcabe24f06197a7a20dc9c81c251f2862430</x:v>
+      </x:c>
+      <x:c r="AA27" s="22" t="str">
+        <x:v>contracts/0xe6abfcabe24f06197a7a20dc9c81c251f2862430/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB27" s="22" t="str">
+        <x:v>6ebc0f7f093351005b9e041aad9ac7408d0b79b6b2da83e4b8deb8ed44d6e798</x:v>
+      </x:c>
+      <x:c r="AC27" s="20" t="n">
+        <x:v>21741</x:v>
+      </x:c>
+      <x:c r="AD27" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE27" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF27" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG27" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH27" s="22" t="str">
+        <x:v>LoopringAmmPool</x:v>
+      </x:c>
+      <x:c r="AI27" s="22" t="str">
+        <x:v>0.7.0+commit.9e61f92b</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="18" customHeight="1">
@@ -2804,7 +3679,7 @@
       <x:c r="R28" s="7" t="n">
         <x:v>44280.18017361111</x:v>
       </x:c>
-      <x:c r="S28" s="8" t="b">
+      <x:c r="S28" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T28" s="22" t="str">
@@ -2824,6 +3699,36 @@
       </x:c>
       <x:c r="Y28" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z28" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258</x:v>
+      </x:c>
+      <x:c r="AA28" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB28" s="22" t="str">
+        <x:v>2172ffe2fdcceb9450519d06338aa4fc905fb50d4f5aacb3d4865a7696d61df8</x:v>
+      </x:c>
+      <x:c r="AC28" s="20" t="n">
+        <x:v>20375</x:v>
+      </x:c>
+      <x:c r="AD28" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE28" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF28" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG28" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH28" s="22" t="str">
+        <x:v>LoopringAmmPool</x:v>
+      </x:c>
+      <x:c r="AI28" s="22" t="str">
+        <x:v>0.7.6+commit.7338295f</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="18" customHeight="1">
@@ -2881,7 +3786,7 @@
       <x:c r="R29" s="7" t="n">
         <x:v>44280.18568287037</x:v>
       </x:c>
-      <x:c r="S29" s="8" t="b">
+      <x:c r="S29" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T29" s="22" t="str">
@@ -2901,6 +3806,36 @@
       </x:c>
       <x:c r="Y29" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z29" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258</x:v>
+      </x:c>
+      <x:c r="AA29" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB29" s="22" t="str">
+        <x:v>2172ffe2fdcceb9450519d06338aa4fc905fb50d4f5aacb3d4865a7696d61df8</x:v>
+      </x:c>
+      <x:c r="AC29" s="20" t="n">
+        <x:v>20375</x:v>
+      </x:c>
+      <x:c r="AD29" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE29" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF29" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG29" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH29" s="22" t="str">
+        <x:v>LoopringAmmPool</x:v>
+      </x:c>
+      <x:c r="AI29" s="22" t="str">
+        <x:v>0.7.6+commit.7338295f</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="18" customHeight="1">
@@ -2958,7 +3893,7 @@
       <x:c r="R30" s="7" t="n">
         <x:v>44280.187476851854</x:v>
       </x:c>
-      <x:c r="S30" s="8" t="b">
+      <x:c r="S30" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T30" s="22" t="str">
@@ -2978,6 +3913,36 @@
       </x:c>
       <x:c r="Y30" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z30" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258</x:v>
+      </x:c>
+      <x:c r="AA30" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB30" s="22" t="str">
+        <x:v>2172ffe2fdcceb9450519d06338aa4fc905fb50d4f5aacb3d4865a7696d61df8</x:v>
+      </x:c>
+      <x:c r="AC30" s="20" t="n">
+        <x:v>20375</x:v>
+      </x:c>
+      <x:c r="AD30" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE30" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF30" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG30" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH30" s="22" t="str">
+        <x:v>LoopringAmmPool</x:v>
+      </x:c>
+      <x:c r="AI30" s="22" t="str">
+        <x:v>0.7.6+commit.7338295f</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="18" customHeight="1">
@@ -3035,7 +4000,7 @@
       <x:c r="R31" s="7" t="n">
         <x:v>44280.18771990741</x:v>
       </x:c>
-      <x:c r="S31" s="8" t="b">
+      <x:c r="S31" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T31" s="22" t="str">
@@ -3055,6 +4020,36 @@
       </x:c>
       <x:c r="Y31" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z31" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258</x:v>
+      </x:c>
+      <x:c r="AA31" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB31" s="22" t="str">
+        <x:v>2172ffe2fdcceb9450519d06338aa4fc905fb50d4f5aacb3d4865a7696d61df8</x:v>
+      </x:c>
+      <x:c r="AC31" s="20" t="n">
+        <x:v>20375</x:v>
+      </x:c>
+      <x:c r="AD31" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE31" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF31" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG31" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH31" s="22" t="str">
+        <x:v>LoopringAmmPool</x:v>
+      </x:c>
+      <x:c r="AI31" s="22" t="str">
+        <x:v>0.7.6+commit.7338295f</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="18" customHeight="1">
@@ -3112,7 +4107,7 @@
       <x:c r="R32" s="7" t="n">
         <x:v>44280.19216435185</x:v>
       </x:c>
-      <x:c r="S32" s="8" t="b">
+      <x:c r="S32" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T32" s="22" t="str">
@@ -3132,6 +4127,36 @@
       </x:c>
       <x:c r="Y32" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z32" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258</x:v>
+      </x:c>
+      <x:c r="AA32" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB32" s="22" t="str">
+        <x:v>2172ffe2fdcceb9450519d06338aa4fc905fb50d4f5aacb3d4865a7696d61df8</x:v>
+      </x:c>
+      <x:c r="AC32" s="20" t="n">
+        <x:v>20375</x:v>
+      </x:c>
+      <x:c r="AD32" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE32" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF32" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG32" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH32" s="22" t="str">
+        <x:v>LoopringAmmPool</x:v>
+      </x:c>
+      <x:c r="AI32" s="22" t="str">
+        <x:v>0.7.6+commit.7338295f</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="18" customHeight="1">
@@ -3189,7 +4214,7 @@
       <x:c r="R33" s="7" t="n">
         <x:v>44293.39141203704</x:v>
       </x:c>
-      <x:c r="S33" s="8" t="b">
+      <x:c r="S33" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T33" s="22" t="str">
@@ -3209,6 +4234,36 @@
       </x:c>
       <x:c r="Y33" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z33" s="22" t="str">
+        <x:v>contracts/0xe6abfcabe24f06197a7a20dc9c81c251f2862430</x:v>
+      </x:c>
+      <x:c r="AA33" s="22" t="str">
+        <x:v>contracts/0xe6abfcabe24f06197a7a20dc9c81c251f2862430/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB33" s="22" t="str">
+        <x:v>6ebc0f7f093351005b9e041aad9ac7408d0b79b6b2da83e4b8deb8ed44d6e798</x:v>
+      </x:c>
+      <x:c r="AC33" s="20" t="n">
+        <x:v>21741</x:v>
+      </x:c>
+      <x:c r="AD33" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE33" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF33" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG33" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH33" s="22" t="str">
+        <x:v>LoopringAmmPool</x:v>
+      </x:c>
+      <x:c r="AI33" s="22" t="str">
+        <x:v>0.7.0+commit.9e61f92b</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="18" customHeight="1">
@@ -3266,7 +4321,7 @@
       <x:c r="R34" s="7" t="n">
         <x:v>44308.35833333333</x:v>
       </x:c>
-      <x:c r="S34" s="8" t="b">
+      <x:c r="S34" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T34" s="22" t="str">
@@ -3286,6 +4341,36 @@
       </x:c>
       <x:c r="Y34" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z34" s="22" t="str">
+        <x:v>contracts/0x1b48d2ea2f9b868ea2f276b431f49879ae58082d</x:v>
+      </x:c>
+      <x:c r="AA34" s="22" t="str">
+        <x:v>contracts/0x1b48d2ea2f9b868ea2f276b431f49879ae58082d/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB34" s="22" t="str">
+        <x:v>548acc6046d2bffdef4feb95ffe5446668c87c6d0c9eccff863540a8be64b841</x:v>
+      </x:c>
+      <x:c r="AC34" s="20" t="n">
+        <x:v>17361</x:v>
+      </x:c>
+      <x:c r="AD34" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE34" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF34" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG34" s="20" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="AH34" s="22" t="str">
+        <x:v>VesperWBTCPlus</x:v>
+      </x:c>
+      <x:c r="AI34" s="22" t="str">
+        <x:v>0.8.0+commit.c7dfd78e</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="18" customHeight="1">
@@ -3343,7 +4428,7 @@
       <x:c r="R35" s="7" t="n">
         <x:v>44312.24690972222</x:v>
       </x:c>
-      <x:c r="S35" s="8" t="b">
+      <x:c r="S35" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T35" s="22" t="str">
@@ -3363,6 +4448,36 @@
       </x:c>
       <x:c r="Y35" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z35" s="22" t="str">
+        <x:v>contracts/0xe53a78e8744568904741d5d0139fad45b1df104b</x:v>
+      </x:c>
+      <x:c r="AA35" s="22" t="str">
+        <x:v>contracts/0xe53a78e8744568904741d5d0139fad45b1df104b/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB35" s="22" t="str">
+        <x:v>955a10de59e993fd3364ad086ca19a035ee43585e610b9eff41f8eeef3c2952e</x:v>
+      </x:c>
+      <x:c r="AC35" s="20" t="n">
+        <x:v>20838</x:v>
+      </x:c>
+      <x:c r="AD35" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE35" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF35" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG35" s="20" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="AH35" s="22" t="str">
+        <x:v>BadgerRenCrvPlus</x:v>
+      </x:c>
+      <x:c r="AI35" s="22" t="str">
+        <x:v>0.8.0+commit.c7dfd78e</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="18" customHeight="1">
@@ -3420,7 +4535,7 @@
       <x:c r="R36" s="7" t="n">
         <x:v>44331.39707175926</x:v>
       </x:c>
-      <x:c r="S36" s="8" t="b">
+      <x:c r="S36" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T36" s="22" t="str">
@@ -3440,6 +4555,36 @@
       </x:c>
       <x:c r="Y36" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z36" s="22" t="str">
+        <x:v>contracts/0x4794387af607b5eb8d65d0ad044d60033c2f1196</x:v>
+      </x:c>
+      <x:c r="AA36" s="22" t="str">
+        <x:v>contracts/0x4794387af607b5eb8d65d0ad044d60033c2f1196/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB36" s="22" t="str">
+        <x:v>4eb19f8c989b6b1f8fd092922eb416afafc9aba0358f276b2b9157ae512a8bf1</x:v>
+      </x:c>
+      <x:c r="AC36" s="20" t="n">
+        <x:v>21677</x:v>
+      </x:c>
+      <x:c r="AD36" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE36" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF36" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG36" s="20" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="AH36" s="22" t="str">
+        <x:v>CurveBTCPlus</x:v>
+      </x:c>
+      <x:c r="AI36" s="22" t="str">
+        <x:v>0.8.0+commit.c7dfd78e</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="18" customHeight="1">
@@ -3497,7 +4642,7 @@
       <x:c r="R37" s="7" t="n">
         <x:v>44356.004270833335</x:v>
       </x:c>
-      <x:c r="S37" s="8" t="b">
+      <x:c r="S37" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T37" s="22" t="str">
@@ -3518,6 +4663,32 @@
       <x:c r="Y37" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z37" s="22" t="str">
+        <x:v>contracts/0x95235173ce34c35e050a97e89ac0d8d7053406ea</x:v>
+      </x:c>
+      <x:c r="AA37" s="22" t="str">
+        <x:v>contracts/0x95235173ce34c35e050a97e89ac0d8d7053406ea/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB37" s="22" t="str">
+        <x:v>dc57805cbb4a8bc0f9bee823ef2ec844bad826fe9d77cb16974f8bf07d579732</x:v>
+      </x:c>
+      <x:c r="AC37" s="20" t="n">
+        <x:v>7977</x:v>
+      </x:c>
+      <x:c r="AD37" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE37" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF37" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG37" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH37" s="22" t="str"/>
+      <x:c r="AI37" s="22" t="str"/>
     </x:row>
     <x:row r="38" ht="18" customHeight="1">
       <x:c r="A38" s="22" t="str">
@@ -3574,7 +4745,7 @@
       <x:c r="R38" s="7" t="n">
         <x:v>44400.30420138889</x:v>
       </x:c>
-      <x:c r="S38" s="8" t="b">
+      <x:c r="S38" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T38" s="22" t="str">
@@ -3595,6 +4766,32 @@
       <x:c r="Y38" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z38" s="22" t="str">
+        <x:v>contracts/0x72a3409af79fb55c7612304b7ce3e56731ab615d</x:v>
+      </x:c>
+      <x:c r="AA38" s="22" t="str">
+        <x:v>contracts/0x72a3409af79fb55c7612304b7ce3e56731ab615d/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB38" s="22" t="str">
+        <x:v>772de4867a745cf96b190e47a67e8e7e534689c72f62fa3c1b417ba327839b15</x:v>
+      </x:c>
+      <x:c r="AC38" s="20" t="n">
+        <x:v>13481</x:v>
+      </x:c>
+      <x:c r="AD38" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE38" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF38" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG38" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH38" s="22" t="str"/>
+      <x:c r="AI38" s="22" t="str"/>
     </x:row>
     <x:row r="39" ht="18" customHeight="1">
       <x:c r="A39" s="22" t="str">
@@ -3651,7 +4848,7 @@
       <x:c r="R39" s="7" t="n">
         <x:v>44420.41353009259</x:v>
       </x:c>
-      <x:c r="S39" s="8" t="b">
+      <x:c r="S39" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T39" s="22" t="str">
@@ -3671,6 +4868,36 @@
       </x:c>
       <x:c r="Y39" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z39" s="22" t="str">
+        <x:v>contracts/0xa8e5ea57f875d8cb5700eb270238ce52ede9cad8</x:v>
+      </x:c>
+      <x:c r="AA39" s="22" t="str">
+        <x:v>contracts/0xa8e5ea57f875d8cb5700eb270238ce52ede9cad8/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB39" s="22" t="str">
+        <x:v>74c87970983c756d7f97c2e244d1d04fc3edfe350df90f9ca552cb5e3b1d21ba</x:v>
+      </x:c>
+      <x:c r="AC39" s="20" t="n">
+        <x:v>19047</x:v>
+      </x:c>
+      <x:c r="AD39" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE39" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF39" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG39" s="20" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AH39" s="22" t="str">
+        <x:v>StakingVault</x:v>
+      </x:c>
+      <x:c r="AI39" s="22" t="str">
+        <x:v>0.8.4+commit.c7e474f2</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="18" customHeight="1">
@@ -3728,7 +4955,7 @@
       <x:c r="R40" s="7" t="n">
         <x:v>44432.301620370374</x:v>
       </x:c>
-      <x:c r="S40" s="8" t="b">
+      <x:c r="S40" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T40" s="22" t="str">
@@ -3748,6 +4975,36 @@
       </x:c>
       <x:c r="Y40" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z40" s="22" t="str">
+        <x:v>contracts/0xc83e731e0cab21ce5b0bbbe3252baefd0e11fc03</x:v>
+      </x:c>
+      <x:c r="AA40" s="22" t="str">
+        <x:v>contracts/0xc83e731e0cab21ce5b0bbbe3252baefd0e11fc03/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB40" s="22" t="str">
+        <x:v>c1a7cbccc73a0224e57e0592ccbc0faccf27890bf167ced5d07fbf6218affe0d</x:v>
+      </x:c>
+      <x:c r="AC40" s="20" t="n">
+        <x:v>17683</x:v>
+      </x:c>
+      <x:c r="AD40" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE40" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF40" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG40" s="20" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="AH40" s="22" t="str">
+        <x:v>SAFU</x:v>
+      </x:c>
+      <x:c r="AI40" s="22" t="str">
+        <x:v>0.6.10+commit.00c0fcaf</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="18" customHeight="1">
@@ -3805,7 +5062,7 @@
       <x:c r="R41" s="7" t="n">
         <x:v>44433.63284722222</x:v>
       </x:c>
-      <x:c r="S41" s="8" t="b">
+      <x:c r="S41" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T41" s="22" t="str">
@@ -3825,6 +5082,36 @@
       </x:c>
       <x:c r="Y41" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z41" s="22" t="str">
+        <x:v>contracts/0x43cfeaa64013071d5505acf98b137f74c8ccd423</x:v>
+      </x:c>
+      <x:c r="AA41" s="22" t="str">
+        <x:v>contracts/0x43cfeaa64013071d5505acf98b137f74c8ccd423/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB41" s="22" t="str">
+        <x:v>8761e354790a2dceafe50fcab6a6e1bab794a6e8474c91db97ecd9652a64fd3f</x:v>
+      </x:c>
+      <x:c r="AC41" s="20" t="n">
+        <x:v>22911</x:v>
+      </x:c>
+      <x:c r="AD41" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE41" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF41" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG41" s="20" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AH41" s="22" t="str">
+        <x:v>RibbonThetaVault</x:v>
+      </x:c>
+      <x:c r="AI41" s="22" t="str">
+        <x:v>0.7.3+commit.9bfce1f6</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="18" customHeight="1">
@@ -3882,7 +5169,7 @@
       <x:c r="R42" s="7" t="n">
         <x:v>44457.21744212963</x:v>
       </x:c>
-      <x:c r="S42" s="8" t="b">
+      <x:c r="S42" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T42" s="22" t="str">
@@ -3902,6 +5189,36 @@
       </x:c>
       <x:c r="Y42" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z42" s="22" t="str">
+        <x:v>contracts/0xfbf2310fefbe2f8969c58675406db2257ee66733</x:v>
+      </x:c>
+      <x:c r="AA42" s="22" t="str">
+        <x:v>contracts/0xfbf2310fefbe2f8969c58675406db2257ee66733/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB42" s="22" t="str">
+        <x:v>405b1caf0b54478d0a3d8a58072ac87d0f59ee16f20950f7703288f92962347b</x:v>
+      </x:c>
+      <x:c r="AC42" s="20" t="n">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="AD42" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE42" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF42" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG42" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AH42" s="22" t="str">
+        <x:v>PriceOracleDelegate</x:v>
+      </x:c>
+      <x:c r="AI42" s="22" t="str">
+        <x:v>0.7.6+commit.7338295f</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="18" customHeight="1">
@@ -3959,7 +5276,7 @@
       <x:c r="R43" s="7" t="n">
         <x:v>44517.04326388889</x:v>
       </x:c>
-      <x:c r="S43" s="8" t="b">
+      <x:c r="S43" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T43" s="22" t="str">
@@ -3979,6 +5296,36 @@
       </x:c>
       <x:c r="Y43" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z43" s="22" t="str">
+        <x:v>contracts/0xe35518c73996fdc7e4db7733d4e98209dd5a1768</x:v>
+      </x:c>
+      <x:c r="AA43" s="22" t="str">
+        <x:v>contracts/0xe35518c73996fdc7e4db7733d4e98209dd5a1768/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB43" s="22" t="str">
+        <x:v>c2cfd2aa3d04ffe1f59543ddff8209e36425e0ec8b59574ca8572f72f3f7ddf3</x:v>
+      </x:c>
+      <x:c r="AC43" s="20" t="n">
+        <x:v>2837</x:v>
+      </x:c>
+      <x:c r="AD43" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE43" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF43" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG43" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH43" s="22" t="str">
+        <x:v>Vesting</x:v>
+      </x:c>
+      <x:c r="AI43" s="22" t="str">
+        <x:v>0.6.12+commit.27d51765</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="18" customHeight="1">
@@ -4036,7 +5383,7 @@
       <x:c r="R44" s="7" t="n">
         <x:v>44599.45253472222</x:v>
       </x:c>
-      <x:c r="S44" s="8" t="b">
+      <x:c r="S44" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T44" s="22" t="str">
@@ -4056,6 +5403,36 @@
       </x:c>
       <x:c r="Y44" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z44" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258</x:v>
+      </x:c>
+      <x:c r="AA44" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB44" s="22" t="str">
+        <x:v>2172ffe2fdcceb9450519d06338aa4fc905fb50d4f5aacb3d4865a7696d61df8</x:v>
+      </x:c>
+      <x:c r="AC44" s="20" t="n">
+        <x:v>20375</x:v>
+      </x:c>
+      <x:c r="AD44" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE44" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF44" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG44" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH44" s="22" t="str">
+        <x:v>LoopringAmmPool</x:v>
+      </x:c>
+      <x:c r="AI44" s="22" t="str">
+        <x:v>0.7.6+commit.7338295f</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="18" customHeight="1">
@@ -4113,7 +5490,7 @@
       <x:c r="R45" s="7" t="n">
         <x:v>44629.06236111111</x:v>
       </x:c>
-      <x:c r="S45" s="8" t="b">
+      <x:c r="S45" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T45" s="22" t="str">
@@ -4133,6 +5510,36 @@
       </x:c>
       <x:c r="Y45" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z45" s="22" t="str">
+        <x:v>contracts/0x8c1bb096b14cf48ab46a1fe7c8e0c57053ea4519</x:v>
+      </x:c>
+      <x:c r="AA45" s="22" t="str">
+        <x:v>contracts/0x8c1bb096b14cf48ab46a1fe7c8e0c57053ea4519/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB45" s="22" t="str">
+        <x:v>a9585cc32a70fddb13d3b2bd043fd3c9d1fd26d422c6e485634f24f2451dd2a6</x:v>
+      </x:c>
+      <x:c r="AC45" s="20" t="n">
+        <x:v>17650</x:v>
+      </x:c>
+      <x:c r="AD45" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE45" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF45" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG45" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH45" s="22" t="str">
+        <x:v>Sales721ForEth</x:v>
+      </x:c>
+      <x:c r="AI45" s="22" t="str">
+        <x:v>0.6.12+commit.27d51765</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="18" customHeight="1">
@@ -4190,7 +5597,7 @@
       <x:c r="R46" s="7" t="n">
         <x:v>44639.589166666665</x:v>
       </x:c>
-      <x:c r="S46" s="8" t="b">
+      <x:c r="S46" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T46" s="22" t="str">
@@ -4211,6 +5618,32 @@
       <x:c r="Y46" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z46" s="22" t="str">
+        <x:v>contracts/0xee2003f259a882f9ffa3bc2b602b02607462b846</x:v>
+      </x:c>
+      <x:c r="AA46" s="22" t="str">
+        <x:v>contracts/0xee2003f259a882f9ffa3bc2b602b02607462b846/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB46" s="22" t="str">
+        <x:v>4fd5dc30823b12d9726c80cac22f2bdf9c651775244be88d6be1ea08de2e5684</x:v>
+      </x:c>
+      <x:c r="AC46" s="20" t="n">
+        <x:v>6958</x:v>
+      </x:c>
+      <x:c r="AD46" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE46" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF46" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG46" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH46" s="22" t="str"/>
+      <x:c r="AI46" s="22" t="str"/>
     </x:row>
     <x:row r="47" ht="18" customHeight="1">
       <x:c r="A47" s="22" t="str">
@@ -4267,7 +5700,7 @@
       <x:c r="R47" s="7" t="n">
         <x:v>44647.255902777775</x:v>
       </x:c>
-      <x:c r="S47" s="8" t="b">
+      <x:c r="S47" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T47" s="22" t="str">
@@ -4287,6 +5720,36 @@
       </x:c>
       <x:c r="Y47" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z47" s="22" t="str">
+        <x:v>contracts/0x1a0a086a6ecc74dd0ba1ac82e5fc60003155e632</x:v>
+      </x:c>
+      <x:c r="AA47" s="22" t="str">
+        <x:v>contracts/0x1a0a086a6ecc74dd0ba1ac82e5fc60003155e632/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB47" s="22" t="str">
+        <x:v>6db28d8e682473f8b190b7e1f3ed20dcf1ba6998ebf8bc8ea193a40104c3aee9</x:v>
+      </x:c>
+      <x:c r="AC47" s="20" t="n">
+        <x:v>24451</x:v>
+      </x:c>
+      <x:c r="AD47" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE47" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF47" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG47" s="20" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="AH47" s="22" t="str">
+        <x:v>FreaksNGuildsMigrated</x:v>
+      </x:c>
+      <x:c r="AI47" s="22" t="str">
+        <x:v>0.8.11+commit.d7f03943</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="18" customHeight="1">
@@ -4344,7 +5807,7 @@
       <x:c r="R48" s="7" t="n">
         <x:v>44651.76935185185</x:v>
       </x:c>
-      <x:c r="S48" s="8" t="b">
+      <x:c r="S48" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T48" s="22" t="str">
@@ -4365,6 +5828,32 @@
       <x:c r="Y48" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z48" s="22" t="str">
+        <x:v>contracts/0x1e8fe97b27db8d16e69e1f15069c61fdbe66b66d</x:v>
+      </x:c>
+      <x:c r="AA48" s="22" t="str">
+        <x:v>contracts/0x1e8fe97b27db8d16e69e1f15069c61fdbe66b66d/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB48" s="22" t="str">
+        <x:v>6581cda9aad54b5603d1e82fd8cdf5c4383ea0c8f9dfda0c5aba521abc2d0675</x:v>
+      </x:c>
+      <x:c r="AC48" s="20" t="n">
+        <x:v>10854</x:v>
+      </x:c>
+      <x:c r="AD48" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE48" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF48" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG48" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH48" s="22" t="str"/>
+      <x:c r="AI48" s="22" t="str"/>
     </x:row>
     <x:row r="49" ht="18" customHeight="1">
       <x:c r="A49" s="22" t="str">
@@ -4421,7 +5910,7 @@
       <x:c r="R49" s="7" t="n">
         <x:v>44657.523252314815</x:v>
       </x:c>
-      <x:c r="S49" s="8" t="b">
+      <x:c r="S49" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T49" s="22" t="str">
@@ -4441,6 +5930,36 @@
       </x:c>
       <x:c r="Y49" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z49" s="22" t="str">
+        <x:v>contracts/0x03fa83d1cff019eee2ea1e12e2b8c4f2abcdd709</x:v>
+      </x:c>
+      <x:c r="AA49" s="22" t="str">
+        <x:v>contracts/0x03fa83d1cff019eee2ea1e12e2b8c4f2abcdd709/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB49" s="22" t="str">
+        <x:v>0d21511a2938456a031768f57bb8a05247edc1980bfe9df1c8f7a9b09ac89192</x:v>
+      </x:c>
+      <x:c r="AC49" s="20" t="n">
+        <x:v>14941</x:v>
+      </x:c>
+      <x:c r="AD49" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE49" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF49" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG49" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH49" s="22" t="str">
+        <x:v>SROOT</x:v>
+      </x:c>
+      <x:c r="AI49" s="22" t="str">
+        <x:v>0.8.7+commit.e28d00a7</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="18" customHeight="1">
@@ -4498,7 +6017,7 @@
       <x:c r="R50" s="7" t="n">
         <x:v>44667.57210648148</x:v>
       </x:c>
-      <x:c r="S50" s="8" t="b">
+      <x:c r="S50" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T50" s="22" t="str">
@@ -4518,6 +6037,36 @@
       </x:c>
       <x:c r="Y50" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z50" s="22" t="str">
+        <x:v>contracts/0xb8adf0585d263f3ba6f73bce1ccc56b821581ab8</x:v>
+      </x:c>
+      <x:c r="AA50" s="22" t="str">
+        <x:v>contracts/0xb8adf0585d263f3ba6f73bce1ccc56b821581ab8/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB50" s="22" t="str">
+        <x:v>59a34b452856bc1d58eb8d0a4e2ad251afe77a877e93c6a3371a83eb1cf53922</x:v>
+      </x:c>
+      <x:c r="AC50" s="20" t="n">
+        <x:v>12750</x:v>
+      </x:c>
+      <x:c r="AD50" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE50" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF50" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG50" s="20" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="AH50" s="22" t="str">
+        <x:v>LandRegistry</x:v>
+      </x:c>
+      <x:c r="AI50" s="22" t="str">
+        <x:v>0.8.13+commit.abaa5c0e</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="18" customHeight="1">
@@ -4575,7 +6124,7 @@
       <x:c r="R51" s="7" t="n">
         <x:v>44676.71949074074</x:v>
       </x:c>
-      <x:c r="S51" s="8" t="b">
+      <x:c r="S51" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T51" s="22" t="str">
@@ -4596,6 +6145,32 @@
       <x:c r="Y51" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z51" s="22" t="str">
+        <x:v>contracts/0xcf2bd216729092e9726f21116f380d412bd4a32e</x:v>
+      </x:c>
+      <x:c r="AA51" s="22" t="str">
+        <x:v>contracts/0xcf2bd216729092e9726f21116f380d412bd4a32e/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB51" s="22" t="str">
+        <x:v>094dd2c9882d1298e9b4e03cad38eed6d098ad7d3432f18193534ea1355a94be</x:v>
+      </x:c>
+      <x:c r="AC51" s="20" t="n">
+        <x:v>8635</x:v>
+      </x:c>
+      <x:c r="AD51" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE51" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF51" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG51" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH51" s="22" t="str"/>
+      <x:c r="AI51" s="22" t="str"/>
     </x:row>
     <x:row r="52" ht="18" customHeight="1">
       <x:c r="A52" s="22" t="str">
@@ -4652,7 +6227,7 @@
       <x:c r="R52" s="7" t="n">
         <x:v>44678.75100694445</x:v>
       </x:c>
-      <x:c r="S52" s="8" t="b">
+      <x:c r="S52" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T52" s="22" t="str">
@@ -4673,6 +6248,32 @@
       <x:c r="Y52" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z52" s="22" t="str">
+        <x:v>contracts/0xf335fc85f32d2373a03d2c4ad06b644187780c13</x:v>
+      </x:c>
+      <x:c r="AA52" s="22" t="str">
+        <x:v>contracts/0xf335fc85f32d2373a03d2c4ad06b644187780c13/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB52" s="22" t="str">
+        <x:v>9e2b9b3542883a4a011c01a1cbfae59680a5fdc33912e1493a9814699a55ca41</x:v>
+      </x:c>
+      <x:c r="AC52" s="20" t="n">
+        <x:v>3383</x:v>
+      </x:c>
+      <x:c r="AD52" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE52" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF52" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG52" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH52" s="22" t="str"/>
+      <x:c r="AI52" s="22" t="str"/>
     </x:row>
     <x:row r="53" ht="18" customHeight="1">
       <x:c r="A53" s="22" t="str">
@@ -4729,7 +6330,7 @@
       <x:c r="R53" s="7" t="n">
         <x:v>44688.88049768518</x:v>
       </x:c>
-      <x:c r="S53" s="8" t="b">
+      <x:c r="S53" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T53" s="22" t="str">
@@ -4750,6 +6351,32 @@
       <x:c r="Y53" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z53" s="22" t="str">
+        <x:v>contracts/0xb5113245e64e2eed58e683573694c84f4b193fa5</x:v>
+      </x:c>
+      <x:c r="AA53" s="22" t="str">
+        <x:v>contracts/0xb5113245e64e2eed58e683573694c84f4b193fa5/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB53" s="22" t="str">
+        <x:v>25a484692d3c17fc5649ac68631553bfa65ccd7faa11c296b737e844e544055e</x:v>
+      </x:c>
+      <x:c r="AC53" s="20" t="n">
+        <x:v>9444</x:v>
+      </x:c>
+      <x:c r="AD53" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE53" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF53" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG53" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH53" s="22" t="str"/>
+      <x:c r="AI53" s="22" t="str"/>
     </x:row>
     <x:row r="54" ht="18" customHeight="1">
       <x:c r="A54" s="22" t="str">
@@ -4806,7 +6433,7 @@
       <x:c r="R54" s="7" t="n">
         <x:v>44703.50108796296</x:v>
       </x:c>
-      <x:c r="S54" s="8" t="b">
+      <x:c r="S54" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T54" s="22" t="str">
@@ -4826,6 +6453,36 @@
       </x:c>
       <x:c r="Y54" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z54" s="22" t="str">
+        <x:v>contracts/0x62e269cfd1951498d93db8be9003c3f454a126f9</x:v>
+      </x:c>
+      <x:c r="AA54" s="22" t="str">
+        <x:v>contracts/0x62e269cfd1951498d93db8be9003c3f454a126f9/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB54" s="22" t="str">
+        <x:v>c85abbf1f71007e393059a73164a5871d732621f4ea31578d819527349d95fcd</x:v>
+      </x:c>
+      <x:c r="AC54" s="20" t="n">
+        <x:v>9809</x:v>
+      </x:c>
+      <x:c r="AD54" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE54" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF54" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG54" s="20" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="AH54" s="22" t="str">
+        <x:v>BibizStakeUpgradeable</x:v>
+      </x:c>
+      <x:c r="AI54" s="22" t="str">
+        <x:v>0.8.13+commit.abaa5c0e</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="18" customHeight="1">
@@ -4883,7 +6540,7 @@
       <x:c r="R55" s="7" t="n">
         <x:v>44739.025729166664</x:v>
       </x:c>
-      <x:c r="S55" s="8" t="b">
+      <x:c r="S55" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T55" s="22" t="str">
@@ -4904,6 +6561,32 @@
       <x:c r="Y55" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z55" s="22" t="str">
+        <x:v>contracts/0xbe275258013e5bbb740f77fd5c34e424e6841c86</x:v>
+      </x:c>
+      <x:c r="AA55" s="22" t="str">
+        <x:v>contracts/0xbe275258013e5bbb740f77fd5c34e424e6841c86/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB55" s="22" t="str">
+        <x:v>9aac6ec9ffa92ed69f05dcc93fde2c674bcd5993cd08f63bf13dd7de8de7ac2e</x:v>
+      </x:c>
+      <x:c r="AC55" s="20" t="n">
+        <x:v>2920</x:v>
+      </x:c>
+      <x:c r="AD55" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE55" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF55" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG55" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH55" s="22" t="str"/>
+      <x:c r="AI55" s="22" t="str"/>
     </x:row>
     <x:row r="56" ht="18" customHeight="1">
       <x:c r="A56" s="22" t="str">
@@ -4960,7 +6643,7 @@
       <x:c r="R56" s="7" t="n">
         <x:v>44750.31972222222</x:v>
       </x:c>
-      <x:c r="S56" s="8" t="b">
+      <x:c r="S56" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T56" s="22" t="str">
@@ -4980,6 +6663,36 @@
       </x:c>
       <x:c r="Y56" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z56" s="22" t="str">
+        <x:v>contracts/0x2c39cfa826c139ebc98e9ec2cd8a67ea76dba006</x:v>
+      </x:c>
+      <x:c r="AA56" s="22" t="str">
+        <x:v>contracts/0x2c39cfa826c139ebc98e9ec2cd8a67ea76dba006/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB56" s="22" t="str">
+        <x:v>689bf3780b95ecf63e12074bfbdd5898a6fb2ebeebec9c7ceb9f1f94ecdfd089</x:v>
+      </x:c>
+      <x:c r="AC56" s="20" t="n">
+        <x:v>2464</x:v>
+      </x:c>
+      <x:c r="AD56" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE56" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF56" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG56" s="20" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="AH56" s="22" t="str">
+        <x:v>ProfitRecord</x:v>
+      </x:c>
+      <x:c r="AI56" s="22" t="str">
+        <x:v>0.8.9+commit.e5eed63a</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="18" customHeight="1">
@@ -5037,7 +6750,7 @@
       <x:c r="R57" s="7" t="n">
         <x:v>44753.78511574074</x:v>
       </x:c>
-      <x:c r="S57" s="8" t="b">
+      <x:c r="S57" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T57" s="22" t="str">
@@ -5057,6 +6770,36 @@
       </x:c>
       <x:c r="Y57" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z57" s="22" t="str">
+        <x:v>contracts/0x943d71ed2a27e2cab27bb2c79488eec3cd2db33b</x:v>
+      </x:c>
+      <x:c r="AA57" s="22" t="str">
+        <x:v>contracts/0x943d71ed2a27e2cab27bb2c79488eec3cd2db33b/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB57" s="22" t="str">
+        <x:v>857dc0fab6141b601ed1c8b3a47a3b5f2ed2286db76be425ddd2245e7467ffd3</x:v>
+      </x:c>
+      <x:c r="AC57" s="20" t="n">
+        <x:v>18031</x:v>
+      </x:c>
+      <x:c r="AD57" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE57" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF57" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG57" s="20" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="AH57" s="22" t="str">
+        <x:v>Fibswap</x:v>
+      </x:c>
+      <x:c r="AI57" s="22" t="str">
+        <x:v>0.8.11+commit.d7f03943</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="18" customHeight="1">
@@ -5114,7 +6857,7 @@
       <x:c r="R58" s="7" t="n">
         <x:v>44774.67592592593</x:v>
       </x:c>
-      <x:c r="S58" s="8" t="b">
+      <x:c r="S58" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T58" s="22" t="str">
@@ -5135,6 +6878,32 @@
       <x:c r="Y58" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z58" s="22" t="str">
+        <x:v>contracts/0x3884d9ed20b76af88c93f39cf65546f866195b54</x:v>
+      </x:c>
+      <x:c r="AA58" s="22" t="str">
+        <x:v>contracts/0x3884d9ed20b76af88c93f39cf65546f866195b54/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB58" s="22" t="str">
+        <x:v>140183a242c62b068faba3ec1c88584511c87a170ea59df589101b093d6185f7</x:v>
+      </x:c>
+      <x:c r="AC58" s="20" t="n">
+        <x:v>12585</x:v>
+      </x:c>
+      <x:c r="AD58" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE58" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF58" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG58" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH58" s="22" t="str"/>
+      <x:c r="AI58" s="22" t="str"/>
     </x:row>
     <x:row r="59" ht="18" customHeight="1">
       <x:c r="A59" s="22" t="str">
@@ -5191,7 +6960,7 @@
       <x:c r="R59" s="7" t="n">
         <x:v>44780.51436342593</x:v>
       </x:c>
-      <x:c r="S59" s="8" t="b">
+      <x:c r="S59" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T59" s="22" t="str">
@@ -5212,6 +6981,32 @@
       <x:c r="Y59" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z59" s="22" t="str">
+        <x:v>contracts/0x2239eb2fc8b94db19dcae519a93445b97c0a5e22</x:v>
+      </x:c>
+      <x:c r="AA59" s="22" t="str">
+        <x:v>contracts/0x2239eb2fc8b94db19dcae519a93445b97c0a5e22/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB59" s="22" t="str">
+        <x:v>12a4507ec38ebad8e594b2d7eb8c675ac1ea19a3a2f45873284ebe4ec35afec0</x:v>
+      </x:c>
+      <x:c r="AC59" s="20" t="n">
+        <x:v>3828</x:v>
+      </x:c>
+      <x:c r="AD59" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE59" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF59" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG59" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH59" s="22" t="str"/>
+      <x:c r="AI59" s="22" t="str"/>
     </x:row>
     <x:row r="60" ht="18" customHeight="1">
       <x:c r="A60" s="22" t="str">
@@ -5268,7 +7063,7 @@
       <x:c r="R60" s="7" t="n">
         <x:v>44785.208391203705</x:v>
       </x:c>
-      <x:c r="S60" s="8" t="b">
+      <x:c r="S60" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T60" s="22" t="str">
@@ -5289,6 +7084,32 @@
       <x:c r="Y60" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z60" s="22" t="str">
+        <x:v>contracts/0x8342c92235d044aadebd3c4de858e26696b8a602</x:v>
+      </x:c>
+      <x:c r="AA60" s="22" t="str">
+        <x:v>contracts/0x8342c92235d044aadebd3c4de858e26696b8a602/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB60" s="22" t="str">
+        <x:v>4e73a98645973afedb2cbcd7d7384bead286a3342c8d8bee989987c0b44c3a17</x:v>
+      </x:c>
+      <x:c r="AC60" s="20" t="n">
+        <x:v>16590</x:v>
+      </x:c>
+      <x:c r="AD60" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE60" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF60" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG60" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH60" s="22" t="str"/>
+      <x:c r="AI60" s="22" t="str"/>
     </x:row>
     <x:row r="61" ht="18" customHeight="1">
       <x:c r="A61" s="22" t="str">
@@ -5345,7 +7166,7 @@
       <x:c r="R61" s="7" t="n">
         <x:v>44796.767476851855</x:v>
       </x:c>
-      <x:c r="S61" s="8" t="b">
+      <x:c r="S61" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T61" s="22" t="str">
@@ -5365,6 +7186,36 @@
       </x:c>
       <x:c r="Y61" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z61" s="22" t="str">
+        <x:v>contracts/0xc9e3d7d8f196a7e915a5c7ce49fde19be7ca35b6</x:v>
+      </x:c>
+      <x:c r="AA61" s="22" t="str">
+        <x:v>contracts/0xc9e3d7d8f196a7e915a5c7ce49fde19be7ca35b6/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB61" s="22" t="str">
+        <x:v>41ed8a9d2036a678db3883fb04100b19b2af68678a738e9833677c593561b65e</x:v>
+      </x:c>
+      <x:c r="AC61" s="20" t="n">
+        <x:v>7813</x:v>
+      </x:c>
+      <x:c r="AD61" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE61" s="22" t="str">
+        <x:v>blockscout</x:v>
+      </x:c>
+      <x:c r="AF61" s="22" t="str">
+        <x:v>partial_match</x:v>
+      </x:c>
+      <x:c r="AG61" s="20" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="AH61" s="22" t="str">
+        <x:v>Bridge</x:v>
+      </x:c>
+      <x:c r="AI61" s="22" t="str">
+        <x:v>v0.8.14+commit.80d49f37</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="18" customHeight="1">
@@ -5422,7 +7273,7 @@
       <x:c r="R62" s="7" t="n">
         <x:v>44798.35150462963</x:v>
       </x:c>
-      <x:c r="S62" s="8" t="b">
+      <x:c r="S62" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T62" s="22" t="str">
@@ -5442,6 +7293,36 @@
       </x:c>
       <x:c r="Y62" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z62" s="22" t="str">
+        <x:v>contracts/0x204d0e6a1be0d11d88dcb48c69f3180b0f772ce2</x:v>
+      </x:c>
+      <x:c r="AA62" s="22" t="str">
+        <x:v>contracts/0x204d0e6a1be0d11d88dcb48c69f3180b0f772ce2/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB62" s="22" t="str">
+        <x:v>0844aee005703f50a8d789c4b6227e877a22d20a29fb58b04a6af7a3626cbb20</x:v>
+      </x:c>
+      <x:c r="AC62" s="20" t="n">
+        <x:v>23931</x:v>
+      </x:c>
+      <x:c r="AD62" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE62" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF62" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG62" s="20" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="AH62" s="22" t="str">
+        <x:v>Minter</x:v>
+      </x:c>
+      <x:c r="AI62" s="22" t="str">
+        <x:v>0.8.7+commit.e28d00a7</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="18" customHeight="1">
@@ -5499,7 +7380,7 @@
       <x:c r="R63" s="7" t="n">
         <x:v>44798.49334490741</x:v>
       </x:c>
-      <x:c r="S63" s="8" t="b">
+      <x:c r="S63" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T63" s="22" t="str">
@@ -5520,6 +7401,32 @@
       <x:c r="Y63" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z63" s="22" t="str">
+        <x:v>contracts/0x2fe3b082c28df92d7e2f9c726a7d0e6cd2c8a061</x:v>
+      </x:c>
+      <x:c r="AA63" s="22" t="str">
+        <x:v>contracts/0x2fe3b082c28df92d7e2f9c726a7d0e6cd2c8a061/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB63" s="22" t="str">
+        <x:v>6c78e0cfbc0ce137dad3efcb2c70a273c9ff2d357d49f40544c1a4be9b1dcb0a</x:v>
+      </x:c>
+      <x:c r="AC63" s="20" t="n">
+        <x:v>13004</x:v>
+      </x:c>
+      <x:c r="AD63" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE63" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF63" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG63" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH63" s="22" t="str"/>
+      <x:c r="AI63" s="22" t="str"/>
     </x:row>
     <x:row r="64" ht="18" customHeight="1">
       <x:c r="A64" s="22" t="str">
@@ -5576,7 +7483,7 @@
       <x:c r="R64" s="7" t="n">
         <x:v>44802.66239583334</x:v>
       </x:c>
-      <x:c r="S64" s="8" t="b">
+      <x:c r="S64" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T64" s="22" t="str">
@@ -5597,6 +7504,32 @@
       <x:c r="Y64" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z64" s="22" t="str">
+        <x:v>contracts/0x1b3efa9a64af24781f4c4e36576c73dbea2ebfdf</x:v>
+      </x:c>
+      <x:c r="AA64" s="22" t="str">
+        <x:v>contracts/0x1b3efa9a64af24781f4c4e36576c73dbea2ebfdf/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB64" s="22" t="str">
+        <x:v>59528f03b01b193602c7bd2346e3ebc9a57b48426dcffb3dc8c1af73cd642a8f</x:v>
+      </x:c>
+      <x:c r="AC64" s="20" t="n">
+        <x:v>9063</x:v>
+      </x:c>
+      <x:c r="AD64" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE64" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF64" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG64" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH64" s="22" t="str"/>
+      <x:c r="AI64" s="22" t="str"/>
     </x:row>
     <x:row r="65" ht="18" customHeight="1">
       <x:c r="A65" s="22" t="str">
@@ -5653,7 +7586,7 @@
       <x:c r="R65" s="7" t="n">
         <x:v>44803.74041666667</x:v>
       </x:c>
-      <x:c r="S65" s="8" t="b">
+      <x:c r="S65" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T65" s="22" t="str">
@@ -5673,6 +7606,36 @@
       </x:c>
       <x:c r="Y65" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z65" s="22" t="str">
+        <x:v>contracts/0x0cb95a8577f694d741be100fdb3efab369ecc945</x:v>
+      </x:c>
+      <x:c r="AA65" s="22" t="str">
+        <x:v>contracts/0x0cb95a8577f694d741be100fdb3efab369ecc945/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB65" s="22" t="str">
+        <x:v>dc7bfccea6f3b6066f2a0df9ecfdffc6e9911838a306b49779df468324b680f6</x:v>
+      </x:c>
+      <x:c r="AC65" s="20" t="n">
+        <x:v>12211</x:v>
+      </x:c>
+      <x:c r="AD65" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE65" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF65" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG65" s="20" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="AH65" s="22" t="str">
+        <x:v>ERC721Burnable</x:v>
+      </x:c>
+      <x:c r="AI65" s="22" t="str">
+        <x:v>0.8.13+commit.abaa5c0e</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="18" customHeight="1">
@@ -5730,7 +7693,7 @@
       <x:c r="R66" s="7" t="n">
         <x:v>44831.42721064815</x:v>
       </x:c>
-      <x:c r="S66" s="8" t="b">
+      <x:c r="S66" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T66" s="22" t="str">
@@ -5751,6 +7714,32 @@
       <x:c r="Y66" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z66" s="22" t="str">
+        <x:v>contracts/0xae90a7868c46861912a5cb12c1c5e9d3a1dd3e60</x:v>
+      </x:c>
+      <x:c r="AA66" s="22" t="str">
+        <x:v>contracts/0xae90a7868c46861912a5cb12c1c5e9d3a1dd3e60/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB66" s="22" t="str">
+        <x:v>b229487044864cbb197aa77e0af28d6d02f1c9ca2dd221877f8ca55854420770</x:v>
+      </x:c>
+      <x:c r="AC66" s="20" t="n">
+        <x:v>2920</x:v>
+      </x:c>
+      <x:c r="AD66" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE66" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF66" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG66" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH66" s="22" t="str"/>
+      <x:c r="AI66" s="22" t="str"/>
     </x:row>
     <x:row r="67" ht="18" customHeight="1">
       <x:c r="A67" s="22" t="str">
@@ -5807,7 +7796,7 @@
       <x:c r="R67" s="7" t="n">
         <x:v>44832.61179398148</x:v>
       </x:c>
-      <x:c r="S67" s="8" t="b">
+      <x:c r="S67" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T67" s="22" t="str">
@@ -5828,6 +7817,32 @@
       <x:c r="Y67" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z67" s="22" t="str">
+        <x:v>contracts/0x514aabfe54f63d5dc4719d2d26ae9895a1b6350d</x:v>
+      </x:c>
+      <x:c r="AA67" s="22" t="str">
+        <x:v>contracts/0x514aabfe54f63d5dc4719d2d26ae9895a1b6350d/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB67" s="22" t="str">
+        <x:v>3b8c333954da96a4caa5ed6bd32ad17490614e7550c9ad9adce96a549559be17</x:v>
+      </x:c>
+      <x:c r="AC67" s="20" t="n">
+        <x:v>20274</x:v>
+      </x:c>
+      <x:c r="AD67" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE67" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF67" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG67" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH67" s="22" t="str"/>
+      <x:c r="AI67" s="22" t="str"/>
     </x:row>
     <x:row r="68" ht="18" customHeight="1">
       <x:c r="A68" s="22" t="str">
@@ -5884,7 +7899,7 @@
       <x:c r="R68" s="7" t="n">
         <x:v>44836.51971064815</x:v>
       </x:c>
-      <x:c r="S68" s="8" t="b">
+      <x:c r="S68" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T68" s="22" t="str">
@@ -5904,6 +7919,36 @@
       </x:c>
       <x:c r="Y68" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z68" s="22" t="str">
+        <x:v>contracts/0xb54d451c9be013425564c2a2065bec0ade4b95af</x:v>
+      </x:c>
+      <x:c r="AA68" s="22" t="str">
+        <x:v>contracts/0xb54d451c9be013425564c2a2065bec0ade4b95af/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB68" s="22" t="str">
+        <x:v>8644b2fc9f6c20e866badcb991223cfd89c6382f7b83fec57468f96edc5660f5</x:v>
+      </x:c>
+      <x:c r="AC68" s="20" t="n">
+        <x:v>6170</x:v>
+      </x:c>
+      <x:c r="AD68" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE68" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF68" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG68" s="20" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="AH68" s="22" t="str">
+        <x:v>WAGMIClaimable</x:v>
+      </x:c>
+      <x:c r="AI68" s="22" t="str">
+        <x:v>0.8.17+commit.8df45f5f</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="18" customHeight="1">
@@ -5961,7 +8006,7 @@
       <x:c r="R69" s="7" t="n">
         <x:v>44853.72540509259</x:v>
       </x:c>
-      <x:c r="S69" s="8" t="b">
+      <x:c r="S69" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T69" s="22" t="str">
@@ -5981,6 +8026,36 @@
       </x:c>
       <x:c r="Y69" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z69" s="22" t="str">
+        <x:v>contracts/0x97d3e5fbcf6dd93a2abfb95a00d2da7199ee3f57</x:v>
+      </x:c>
+      <x:c r="AA69" s="22" t="str">
+        <x:v>contracts/0x97d3e5fbcf6dd93a2abfb95a00d2da7199ee3f57/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB69" s="22" t="str">
+        <x:v>309beb9b64d576c3009e99b134a09fae71ea420575879b22663cc1259ec90772</x:v>
+      </x:c>
+      <x:c r="AC69" s="20" t="n">
+        <x:v>20832</x:v>
+      </x:c>
+      <x:c r="AD69" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE69" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF69" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG69" s="20" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="AH69" s="22" t="str">
+        <x:v>QuantumSpaces</x:v>
+      </x:c>
+      <x:c r="AI69" s="22" t="str">
+        <x:v>0.8.11+commit.d7f03943</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="18" customHeight="1">
@@ -6038,7 +8113,7 @@
       <x:c r="R70" s="7" t="n">
         <x:v>44858.592210648145</x:v>
       </x:c>
-      <x:c r="S70" s="8" t="b">
+      <x:c r="S70" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T70" s="22" t="str">
@@ -6059,6 +8134,32 @@
       <x:c r="Y70" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z70" s="22" t="str">
+        <x:v>contracts/0x0c763c902a2d4a0e841ab8dc73a36fa776915950</x:v>
+      </x:c>
+      <x:c r="AA70" s="22" t="str">
+        <x:v>contracts/0x0c763c902a2d4a0e841ab8dc73a36fa776915950/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB70" s="22" t="str">
+        <x:v>dee5b2a1f9034d400e621a356869acafcc40f601708a0c5e637cef2430ceb312</x:v>
+      </x:c>
+      <x:c r="AC70" s="20" t="n">
+        <x:v>2920</x:v>
+      </x:c>
+      <x:c r="AD70" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE70" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF70" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG70" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH70" s="22" t="str"/>
+      <x:c r="AI70" s="22" t="str"/>
     </x:row>
     <x:row r="71" ht="18" customHeight="1">
       <x:c r="A71" s="22" t="str">
@@ -6115,7 +8216,7 @@
       <x:c r="R71" s="7" t="n">
         <x:v>44861.6727662037</x:v>
       </x:c>
-      <x:c r="S71" s="8" t="b">
+      <x:c r="S71" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T71" s="22" t="str">
@@ -6135,6 +8236,36 @@
       </x:c>
       <x:c r="Y71" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z71" s="22" t="str">
+        <x:v>contracts/0xf9e266af4bca5890e2781812cc6a6e89495a79f2</x:v>
+      </x:c>
+      <x:c r="AA71" s="22" t="str">
+        <x:v>contracts/0xf9e266af4bca5890e2781812cc6a6e89495a79f2/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB71" s="22" t="str">
+        <x:v>74e5883541ea918b0c2dae357920b953302a7685da3d73c2623cfc7fef88174f</x:v>
+      </x:c>
+      <x:c r="AC71" s="20" t="n">
+        <x:v>2082</x:v>
+      </x:c>
+      <x:c r="AD71" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE71" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF71" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG71" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH71" s="22" t="str">
+        <x:v>AuthenticatedProxy</x:v>
+      </x:c>
+      <x:c r="AI71" s="22" t="str">
+        <x:v>0.4.23+commit.124ca40d</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="18" customHeight="1">
@@ -6192,7 +8323,7 @@
       <x:c r="R72" s="7" t="n">
         <x:v>44877.975266203706</x:v>
       </x:c>
-      <x:c r="S72" s="8" t="b">
+      <x:c r="S72" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T72" s="22" t="str">
@@ -6212,6 +8343,36 @@
       </x:c>
       <x:c r="Y72" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z72" s="22" t="str">
+        <x:v>contracts/0x8b5c19cdb8afb458bbb3ce53bf1ef1754df09b88</x:v>
+      </x:c>
+      <x:c r="AA72" s="22" t="str">
+        <x:v>contracts/0x8b5c19cdb8afb458bbb3ce53bf1ef1754df09b88/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB72" s="22" t="str">
+        <x:v>203a60b87444d9baab66478dc8c6909188fc1b0429e3025d3925dbf400a8b288</x:v>
+      </x:c>
+      <x:c r="AC72" s="20" t="n">
+        <x:v>16642</x:v>
+      </x:c>
+      <x:c r="AD72" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE72" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF72" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG72" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AH72" s="22" t="str">
+        <x:v>EGT</x:v>
+      </x:c>
+      <x:c r="AI72" s="22" t="str">
+        <x:v>0.8.12+commit.f00d7308</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="18" customHeight="1">
@@ -6269,7 +8430,7 @@
       <x:c r="R73" s="7" t="n">
         <x:v>44880.085543981484</x:v>
       </x:c>
-      <x:c r="S73" s="8" t="b">
+      <x:c r="S73" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T73" s="22" t="str">
@@ -6289,6 +8450,36 @@
       </x:c>
       <x:c r="Y73" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z73" s="22" t="str">
+        <x:v>contracts/0x3883f75b2be639f9236ed230dd7202f31eaf38d5</x:v>
+      </x:c>
+      <x:c r="AA73" s="22" t="str">
+        <x:v>contracts/0x3883f75b2be639f9236ed230dd7202f31eaf38d5/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB73" s="22" t="str">
+        <x:v>95ffc79cd5015cc5c586f14057b7c2cb170fd7a4182cb69837a0934e5a1733c0</x:v>
+      </x:c>
+      <x:c r="AC73" s="20" t="n">
+        <x:v>6682</x:v>
+      </x:c>
+      <x:c r="AD73" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE73" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF73" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG73" s="20" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="AH73" s="22" t="str">
+        <x:v>LockTOSv2Proxy</x:v>
+      </x:c>
+      <x:c r="AI73" s="22" t="str">
+        <x:v>0.7.6+commit.7338295f</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="18" customHeight="1">
@@ -6346,7 +8537,7 @@
       <x:c r="R74" s="7" t="n">
         <x:v>44880.311793981484</x:v>
       </x:c>
-      <x:c r="S74" s="8" t="b">
+      <x:c r="S74" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T74" s="22" t="str">
@@ -6367,6 +8558,32 @@
       <x:c r="Y74" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z74" s="22" t="str">
+        <x:v>contracts/0xe3b81fa71fc815e233cd5c2fe97f583ebe31b723</x:v>
+      </x:c>
+      <x:c r="AA74" s="22" t="str">
+        <x:v>contracts/0xe3b81fa71fc815e233cd5c2fe97f583ebe31b723/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB74" s="22" t="str">
+        <x:v>abbd122997eee54ab63b543e9396bbd5aed49deabdb8fb1979edd546c18ed521</x:v>
+      </x:c>
+      <x:c r="AC74" s="20" t="n">
+        <x:v>13356</x:v>
+      </x:c>
+      <x:c r="AD74" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE74" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF74" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG74" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH74" s="22" t="str"/>
+      <x:c r="AI74" s="22" t="str"/>
     </x:row>
     <x:row r="75" ht="18" customHeight="1">
       <x:c r="A75" s="22" t="str">
@@ -6423,7 +8640,7 @@
       <x:c r="R75" s="7" t="n">
         <x:v>44881.75859953704</x:v>
       </x:c>
-      <x:c r="S75" s="8" t="b">
+      <x:c r="S75" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T75" s="22" t="str">
@@ -6444,6 +8661,32 @@
       <x:c r="Y75" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z75" s="22" t="str">
+        <x:v>contracts/0x2d897534673be5d5b801a7a6be3dab29f8a17e83</x:v>
+      </x:c>
+      <x:c r="AA75" s="22" t="str">
+        <x:v>contracts/0x2d897534673be5d5b801a7a6be3dab29f8a17e83/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB75" s="22" t="str">
+        <x:v>73ce5735c10c0acfcc5f3853374b60ca24f9d8bb94efc83b0b393a56bd52422b</x:v>
+      </x:c>
+      <x:c r="AC75" s="20" t="n">
+        <x:v>13824</x:v>
+      </x:c>
+      <x:c r="AD75" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE75" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF75" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG75" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH75" s="22" t="str"/>
+      <x:c r="AI75" s="22" t="str"/>
     </x:row>
     <x:row r="76" ht="18" customHeight="1">
       <x:c r="A76" s="22" t="str">
@@ -6500,7 +8743,7 @@
       <x:c r="R76" s="7" t="n">
         <x:v>44894.23832175926</x:v>
       </x:c>
-      <x:c r="S76" s="8" t="b">
+      <x:c r="S76" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T76" s="22" t="str">
@@ -6521,6 +8764,32 @@
       <x:c r="Y76" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z76" s="22" t="str">
+        <x:v>contracts/0x7baad50a656c484330f9e9ae720798edcd739c83</x:v>
+      </x:c>
+      <x:c r="AA76" s="22" t="str">
+        <x:v>contracts/0x7baad50a656c484330f9e9ae720798edcd739c83/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB76" s="22" t="str">
+        <x:v>0fe92e8aea127a4d9de01a89c4ed217557fd29dc74adfa87b1da751936a7bfa0</x:v>
+      </x:c>
+      <x:c r="AC76" s="20" t="n">
+        <x:v>3851</x:v>
+      </x:c>
+      <x:c r="AD76" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE76" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF76" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG76" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH76" s="22" t="str"/>
+      <x:c r="AI76" s="22" t="str"/>
     </x:row>
     <x:row r="77" ht="18" customHeight="1">
       <x:c r="A77" s="22" t="str">
@@ -6577,7 +8846,7 @@
       <x:c r="R77" s="7" t="n">
         <x:v>44898.523043981484</x:v>
       </x:c>
-      <x:c r="S77" s="8" t="b">
+      <x:c r="S77" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T77" s="22" t="str">
@@ -6598,6 +8867,32 @@
       <x:c r="Y77" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z77" s="22" t="str">
+        <x:v>contracts/0x67d6897ec4e903e4163649ac064ae1020635e379</x:v>
+      </x:c>
+      <x:c r="AA77" s="22" t="str">
+        <x:v>contracts/0x67d6897ec4e903e4163649ac064ae1020635e379/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB77" s="22" t="str">
+        <x:v>118560776779d79e5de2d2ed1ee07f858c9bb5508be3d626d7a9ecfa9f8d1bb6</x:v>
+      </x:c>
+      <x:c r="AC77" s="20" t="n">
+        <x:v>2905</x:v>
+      </x:c>
+      <x:c r="AD77" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE77" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF77" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG77" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH77" s="22" t="str"/>
+      <x:c r="AI77" s="22" t="str"/>
     </x:row>
     <x:row r="78" ht="18" customHeight="1">
       <x:c r="A78" s="22" t="str">
@@ -6654,7 +8949,7 @@
       <x:c r="R78" s="7" t="n">
         <x:v>44899.86498842593</x:v>
       </x:c>
-      <x:c r="S78" s="8" t="b">
+      <x:c r="S78" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T78" s="22" t="str">
@@ -6675,6 +8970,32 @@
       <x:c r="Y78" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z78" s="22" t="str">
+        <x:v>contracts/0x67d6897ec4e903e4163649ac064ae1020635e379</x:v>
+      </x:c>
+      <x:c r="AA78" s="22" t="str">
+        <x:v>contracts/0x67d6897ec4e903e4163649ac064ae1020635e379/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB78" s="22" t="str">
+        <x:v>118560776779d79e5de2d2ed1ee07f858c9bb5508be3d626d7a9ecfa9f8d1bb6</x:v>
+      </x:c>
+      <x:c r="AC78" s="20" t="n">
+        <x:v>2905</x:v>
+      </x:c>
+      <x:c r="AD78" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE78" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF78" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG78" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH78" s="22" t="str"/>
+      <x:c r="AI78" s="22" t="str"/>
     </x:row>
     <x:row r="79" ht="18" customHeight="1">
       <x:c r="A79" s="22" t="str">
@@ -6731,7 +9052,7 @@
       <x:c r="R79" s="7" t="n">
         <x:v>44901.63748842593</x:v>
       </x:c>
-      <x:c r="S79" s="8" t="b">
+      <x:c r="S79" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T79" s="22" t="str">
@@ -6751,6 +9072,36 @@
       </x:c>
       <x:c r="Y79" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z79" s="22" t="str">
+        <x:v>contracts/0x6564fe0809e8b520a0e26ee644d98c4ea2c6fb45</x:v>
+      </x:c>
+      <x:c r="AA79" s="22" t="str">
+        <x:v>contracts/0x6564fe0809e8b520a0e26ee644d98c4ea2c6fb45/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB79" s="22" t="str">
+        <x:v>959375847291ac4d49306b512acad984d4ee429c03c5ef15d6e20db1b2b289d2</x:v>
+      </x:c>
+      <x:c r="AC79" s="20" t="n">
+        <x:v>6998</x:v>
+      </x:c>
+      <x:c r="AD79" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE79" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF79" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG79" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH79" s="22" t="str">
+        <x:v>OperatorVault</x:v>
+      </x:c>
+      <x:c r="AI79" s="22" t="str">
+        <x:v>0.8.15+commit.e14f2714</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="18" customHeight="1">
@@ -6808,7 +9159,7 @@
       <x:c r="R80" s="7" t="n">
         <x:v>44910.18790509259</x:v>
       </x:c>
-      <x:c r="S80" s="8" t="b">
+      <x:c r="S80" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T80" s="22" t="str">
@@ -6828,6 +9179,36 @@
       </x:c>
       <x:c r="Y80" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z80" s="22" t="str">
+        <x:v>contracts/0xc600727f1ce705436734f2367e7fc449da5fb3a6</x:v>
+      </x:c>
+      <x:c r="AA80" s="22" t="str">
+        <x:v>contracts/0xc600727f1ce705436734f2367e7fc449da5fb3a6/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB80" s="22" t="str">
+        <x:v>8f3a0a73767e258d99a5375ccaf2a8f01170b9c0622b36141e453fb4d2d327c0</x:v>
+      </x:c>
+      <x:c r="AC80" s="20" t="n">
+        <x:v>23133</x:v>
+      </x:c>
+      <x:c r="AD80" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE80" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF80" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG80" s="20" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="AH80" s="22" t="str">
+        <x:v>AutoCoinageSnapshot2</x:v>
+      </x:c>
+      <x:c r="AI80" s="22" t="str">
+        <x:v>0.8.4+commit.c7e474f2</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="18" customHeight="1">
@@ -6885,7 +9266,7 @@
       <x:c r="R81" s="7" t="n">
         <x:v>44921.90609953704</x:v>
       </x:c>
-      <x:c r="S81" s="8" t="b">
+      <x:c r="S81" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T81" s="22" t="str">
@@ -6905,6 +9286,36 @@
       </x:c>
       <x:c r="Y81" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z81" s="22" t="str">
+        <x:v>contracts/0x535640946c6f47806faf036f14d23e85a42c5544</x:v>
+      </x:c>
+      <x:c r="AA81" s="22" t="str">
+        <x:v>contracts/0x535640946c6f47806faf036f14d23e85a42c5544/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB81" s="22" t="str">
+        <x:v>cc126d154b32ceb9c242b6f807f4a826ec95b2c40bfc2ca37fc57c17c90d64d1</x:v>
+      </x:c>
+      <x:c r="AC81" s="20" t="n">
+        <x:v>10570</x:v>
+      </x:c>
+      <x:c r="AD81" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE81" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF81" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG81" s="20" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="AH81" s="22" t="str">
+        <x:v>ENSAvatarMirror</x:v>
+      </x:c>
+      <x:c r="AI81" s="22" t="str">
+        <x:v>0.8.17+commit.8df45f5f</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="18" customHeight="1">
@@ -6962,7 +9373,7 @@
       <x:c r="R82" s="7" t="n">
         <x:v>44969.80971064815</x:v>
       </x:c>
-      <x:c r="S82" s="8" t="b">
+      <x:c r="S82" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T82" s="22" t="str">
@@ -6982,6 +9393,36 @@
       </x:c>
       <x:c r="Y82" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z82" s="22" t="str">
+        <x:v>contracts/0x28546ea0c2894e4b83f91dc6db52c83d0ca61f0e</x:v>
+      </x:c>
+      <x:c r="AA82" s="22" t="str">
+        <x:v>contracts/0x28546ea0c2894e4b83f91dc6db52c83d0ca61f0e/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB82" s="22" t="str">
+        <x:v>190d1589c3f735c9774b126f56f75e7a802f992916939b0653738d0b0eb37c05</x:v>
+      </x:c>
+      <x:c r="AC82" s="20" t="n">
+        <x:v>24195</x:v>
+      </x:c>
+      <x:c r="AD82" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE82" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF82" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG82" s="20" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="AH82" s="22" t="str">
+        <x:v>DaoMarketPlace</x:v>
+      </x:c>
+      <x:c r="AI82" s="22" t="str">
+        <x:v>0.8.13+commit.abaa5c0e</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="18" customHeight="1">
@@ -7039,7 +9480,7 @@
       <x:c r="R83" s="7" t="n">
         <x:v>44977.46971064815</x:v>
       </x:c>
-      <x:c r="S83" s="8" t="b">
+      <x:c r="S83" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T83" s="22" t="str">
@@ -7060,6 +9501,32 @@
       <x:c r="Y83" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z83" s="22" t="str">
+        <x:v>contracts/0x0d970afb431c8188a49eaa3782e6e37ffb16011a</x:v>
+      </x:c>
+      <x:c r="AA83" s="22" t="str">
+        <x:v>contracts/0x0d970afb431c8188a49eaa3782e6e37ffb16011a/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB83" s="22" t="str">
+        <x:v>1f969f0960e35d2e9d12149f83e41a3d626bb0053d0cfe31bf21426bd5a3b0e9</x:v>
+      </x:c>
+      <x:c r="AC83" s="20" t="n">
+        <x:v>8309</x:v>
+      </x:c>
+      <x:c r="AD83" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE83" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF83" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG83" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH83" s="22" t="str"/>
+      <x:c r="AI83" s="22" t="str"/>
     </x:row>
     <x:row r="84" ht="18" customHeight="1">
       <x:c r="A84" s="22" t="str">
@@ -7116,7 +9583,7 @@
       <x:c r="R84" s="7" t="n">
         <x:v>44977.52276620371</x:v>
       </x:c>
-      <x:c r="S84" s="8" t="b">
+      <x:c r="S84" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T84" s="22" t="str">
@@ -7137,6 +9604,32 @@
       <x:c r="Y84" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z84" s="22" t="str">
+        <x:v>contracts/0xda5c71f78c34f3315eb4458939ad84ee78e0d8e7</x:v>
+      </x:c>
+      <x:c r="AA84" s="22" t="str">
+        <x:v>contracts/0xda5c71f78c34f3315eb4458939ad84ee78e0d8e7/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB84" s="22" t="str">
+        <x:v>e8358bce56a22dc4d4ffc169f295181d701a9b3e05254b694b79bd3a081802c9</x:v>
+      </x:c>
+      <x:c r="AC84" s="20" t="n">
+        <x:v>8309</x:v>
+      </x:c>
+      <x:c r="AD84" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE84" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF84" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG84" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH84" s="22" t="str"/>
+      <x:c r="AI84" s="22" t="str"/>
     </x:row>
     <x:row r="85" ht="18" customHeight="1">
       <x:c r="A85" s="22" t="str">
@@ -7193,7 +9686,7 @@
       <x:c r="R85" s="7" t="n">
         <x:v>44980.48762731482</x:v>
       </x:c>
-      <x:c r="S85" s="8" t="b">
+      <x:c r="S85" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T85" s="22" t="str">
@@ -7213,6 +9706,36 @@
       </x:c>
       <x:c r="Y85" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z85" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0</x:v>
+      </x:c>
+      <x:c r="AA85" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB85" s="22" t="str">
+        <x:v>6a1b7f749b21e2e90ad971d8988746fcde9e50f955ee8ba11f8d6461f2d0658d</x:v>
+      </x:c>
+      <x:c r="AC85" s="20" t="n">
+        <x:v>24493</x:v>
+      </x:c>
+      <x:c r="AD85" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE85" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF85" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG85" s="20" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="AH85" s="22" t="str">
+        <x:v>ERC721Drop</x:v>
+      </x:c>
+      <x:c r="AI85" s="22" t="str">
+        <x:v>0.8.17+commit.8df45f5f</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="18" customHeight="1">
@@ -7270,7 +9793,7 @@
       <x:c r="R86" s="7" t="n">
         <x:v>44982.10943287037</x:v>
       </x:c>
-      <x:c r="S86" s="8" t="b">
+      <x:c r="S86" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T86" s="22" t="str">
@@ -7290,6 +9813,36 @@
       </x:c>
       <x:c r="Y86" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z86" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0</x:v>
+      </x:c>
+      <x:c r="AA86" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB86" s="22" t="str">
+        <x:v>6a1b7f749b21e2e90ad971d8988746fcde9e50f955ee8ba11f8d6461f2d0658d</x:v>
+      </x:c>
+      <x:c r="AC86" s="20" t="n">
+        <x:v>24493</x:v>
+      </x:c>
+      <x:c r="AD86" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE86" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF86" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG86" s="20" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="AH86" s="22" t="str">
+        <x:v>ERC721Drop</x:v>
+      </x:c>
+      <x:c r="AI86" s="22" t="str">
+        <x:v>0.8.17+commit.8df45f5f</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="18" customHeight="1">
@@ -7347,7 +9900,7 @@
       <x:c r="R87" s="7" t="n">
         <x:v>44984.66096064815</x:v>
       </x:c>
-      <x:c r="S87" s="8" t="b">
+      <x:c r="S87" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T87" s="22" t="str">
@@ -7367,6 +9920,36 @@
       </x:c>
       <x:c r="Y87" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z87" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0</x:v>
+      </x:c>
+      <x:c r="AA87" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB87" s="22" t="str">
+        <x:v>6a1b7f749b21e2e90ad971d8988746fcde9e50f955ee8ba11f8d6461f2d0658d</x:v>
+      </x:c>
+      <x:c r="AC87" s="20" t="n">
+        <x:v>24493</x:v>
+      </x:c>
+      <x:c r="AD87" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE87" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF87" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG87" s="20" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="AH87" s="22" t="str">
+        <x:v>ERC721Drop</x:v>
+      </x:c>
+      <x:c r="AI87" s="22" t="str">
+        <x:v>0.8.17+commit.8df45f5f</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="18" customHeight="1">
@@ -7424,7 +10007,7 @@
       <x:c r="R88" s="7" t="n">
         <x:v>44984.665127314816</x:v>
       </x:c>
-      <x:c r="S88" s="8" t="b">
+      <x:c r="S88" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T88" s="22" t="str">
@@ -7444,6 +10027,36 @@
       </x:c>
       <x:c r="Y88" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z88" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0</x:v>
+      </x:c>
+      <x:c r="AA88" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB88" s="22" t="str">
+        <x:v>6a1b7f749b21e2e90ad971d8988746fcde9e50f955ee8ba11f8d6461f2d0658d</x:v>
+      </x:c>
+      <x:c r="AC88" s="20" t="n">
+        <x:v>24493</x:v>
+      </x:c>
+      <x:c r="AD88" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE88" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF88" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG88" s="20" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="AH88" s="22" t="str">
+        <x:v>ERC721Drop</x:v>
+      </x:c>
+      <x:c r="AI88" s="22" t="str">
+        <x:v>0.8.17+commit.8df45f5f</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="18" customHeight="1">
@@ -7501,7 +10114,7 @@
       <x:c r="R89" s="7" t="n">
         <x:v>44988.694016203706</x:v>
       </x:c>
-      <x:c r="S89" s="8" t="b">
+      <x:c r="S89" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T89" s="22" t="str">
@@ -7522,6 +10135,32 @@
       <x:c r="Y89" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z89" s="22" t="str">
+        <x:v>contracts/0xf61f1450d38848e7df7cc9dfe1019a397c392055</x:v>
+      </x:c>
+      <x:c r="AA89" s="22" t="str">
+        <x:v>contracts/0xf61f1450d38848e7df7cc9dfe1019a397c392055/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB89" s="22" t="str">
+        <x:v>9f4d944d024557a925df323b3afb0ef824a59cacf4adde13e3c68a9b4b72d007</x:v>
+      </x:c>
+      <x:c r="AC89" s="20" t="n">
+        <x:v>1670</x:v>
+      </x:c>
+      <x:c r="AD89" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE89" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF89" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG89" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH89" s="22" t="str"/>
+      <x:c r="AI89" s="22" t="str"/>
     </x:row>
     <x:row r="90" ht="18" customHeight="1">
       <x:c r="A90" s="22" t="str">
@@ -7578,7 +10217,7 @@
       <x:c r="R90" s="7" t="n">
         <x:v>44990.758738425924</x:v>
       </x:c>
-      <x:c r="S90" s="8" t="b">
+      <x:c r="S90" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T90" s="22" t="str">
@@ -7598,6 +10237,36 @@
       </x:c>
       <x:c r="Y90" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z90" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0</x:v>
+      </x:c>
+      <x:c r="AA90" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB90" s="22" t="str">
+        <x:v>6a1b7f749b21e2e90ad971d8988746fcde9e50f955ee8ba11f8d6461f2d0658d</x:v>
+      </x:c>
+      <x:c r="AC90" s="20" t="n">
+        <x:v>24493</x:v>
+      </x:c>
+      <x:c r="AD90" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE90" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF90" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG90" s="20" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="AH90" s="22" t="str">
+        <x:v>ERC721Drop</x:v>
+      </x:c>
+      <x:c r="AI90" s="22" t="str">
+        <x:v>0.8.17+commit.8df45f5f</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="18" customHeight="1">
@@ -7655,7 +10324,7 @@
       <x:c r="R91" s="7" t="n">
         <x:v>45002.497349537036</x:v>
       </x:c>
-      <x:c r="S91" s="8" t="b">
+      <x:c r="S91" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T91" s="22" t="str">
@@ -7675,6 +10344,36 @@
       </x:c>
       <x:c r="Y91" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z91" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0</x:v>
+      </x:c>
+      <x:c r="AA91" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB91" s="22" t="str">
+        <x:v>6a1b7f749b21e2e90ad971d8988746fcde9e50f955ee8ba11f8d6461f2d0658d</x:v>
+      </x:c>
+      <x:c r="AC91" s="20" t="n">
+        <x:v>24493</x:v>
+      </x:c>
+      <x:c r="AD91" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE91" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF91" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG91" s="20" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="AH91" s="22" t="str">
+        <x:v>ERC721Drop</x:v>
+      </x:c>
+      <x:c r="AI91" s="22" t="str">
+        <x:v>0.8.17+commit.8df45f5f</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="18" customHeight="1">
@@ -7732,7 +10431,7 @@
       <x:c r="R92" s="7" t="n">
         <x:v>45007.42832175926</x:v>
       </x:c>
-      <x:c r="S92" s="8" t="b">
+      <x:c r="S92" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T92" s="22" t="str">
@@ -7752,6 +10451,36 @@
       </x:c>
       <x:c r="Y92" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z92" s="22" t="str">
+        <x:v>contracts/0xb2999240765ce4334400ab1d5ef24163c30fb35f</x:v>
+      </x:c>
+      <x:c r="AA92" s="22" t="str">
+        <x:v>contracts/0xb2999240765ce4334400ab1d5ef24163c30fb35f/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB92" s="22" t="str">
+        <x:v>2946bbe9e5c2d16ee6a272decedadac06bad07ca78f21457f94071fa3627ea57</x:v>
+      </x:c>
+      <x:c r="AC92" s="20" t="n">
+        <x:v>17551</x:v>
+      </x:c>
+      <x:c r="AD92" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE92" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF92" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG92" s="20" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="AH92" s="22" t="str">
+        <x:v>ComplianceRegistry</x:v>
+      </x:c>
+      <x:c r="AI92" s="22" t="str">
+        <x:v>0.6.2+commit.bacdbe57</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="18" customHeight="1">
@@ -7809,7 +10538,7 @@
       <x:c r="R93" s="7" t="n">
         <x:v>45014.55401620371</x:v>
       </x:c>
-      <x:c r="S93" s="8" t="b">
+      <x:c r="S93" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T93" s="22" t="str">
@@ -7829,6 +10558,36 @@
       </x:c>
       <x:c r="Y93" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z93" s="22" t="str">
+        <x:v>contracts/0x9e05d613e09e878cc14e5c25a79028b8dcff79d3</x:v>
+      </x:c>
+      <x:c r="AA93" s="22" t="str">
+        <x:v>contracts/0x9e05d613e09e878cc14e5c25a79028b8dcff79d3/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB93" s="22" t="str">
+        <x:v>74fd1401213e2f54fe54cd960edddd010af7ab2d24d903d5aa9657afad20e24f</x:v>
+      </x:c>
+      <x:c r="AC93" s="20" t="n">
+        <x:v>15769</x:v>
+      </x:c>
+      <x:c r="AD93" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE93" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF93" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="AG93" s="20" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="AH93" s="22" t="str">
+        <x:v>OTCWrapper</x:v>
+      </x:c>
+      <x:c r="AI93" s="22" t="str">
+        <x:v>0.8.10+commit.fc410830</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="18" customHeight="1">
@@ -7886,7 +10645,7 @@
       <x:c r="R94" s="7" t="n">
         <x:v>45026.912766203706</x:v>
       </x:c>
-      <x:c r="S94" s="8" t="b">
+      <x:c r="S94" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T94" s="22" t="str">
@@ -7906,6 +10665,36 @@
       </x:c>
       <x:c r="Y94" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z94" s="22" t="str">
+        <x:v>contracts/0x26daa1a88c9b2bcda8b0c928e0024130ede7ca0b</x:v>
+      </x:c>
+      <x:c r="AA94" s="22" t="str">
+        <x:v>contracts/0x26daa1a88c9b2bcda8b0c928e0024130ede7ca0b/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB94" s="22" t="str">
+        <x:v>8c64658bd56ad582c890a0f037d76a57ed0ebb8f2115a1bc7142e31f9dff91aa</x:v>
+      </x:c>
+      <x:c r="AC94" s="20" t="n">
+        <x:v>20111</x:v>
+      </x:c>
+      <x:c r="AD94" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE94" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF94" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG94" s="20" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="AH94" s="22" t="str">
+        <x:v>MegaForceSentinels</x:v>
+      </x:c>
+      <x:c r="AI94" s="22" t="str">
+        <x:v>0.8.17+commit.8df45f5f</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="18" customHeight="1">
@@ -7963,7 +10752,7 @@
       <x:c r="R95" s="7" t="n">
         <x:v>45037.73873842593</x:v>
       </x:c>
-      <x:c r="S95" s="8" t="b">
+      <x:c r="S95" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T95" s="22" t="str">
@@ -7983,6 +10772,36 @@
       </x:c>
       <x:c r="Y95" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z95" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0</x:v>
+      </x:c>
+      <x:c r="AA95" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB95" s="22" t="str">
+        <x:v>6a1b7f749b21e2e90ad971d8988746fcde9e50f955ee8ba11f8d6461f2d0658d</x:v>
+      </x:c>
+      <x:c r="AC95" s="20" t="n">
+        <x:v>24493</x:v>
+      </x:c>
+      <x:c r="AD95" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE95" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF95" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG95" s="20" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="AH95" s="22" t="str">
+        <x:v>ERC721Drop</x:v>
+      </x:c>
+      <x:c r="AI95" s="22" t="str">
+        <x:v>0.8.17+commit.8df45f5f</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="18" customHeight="1">
@@ -8040,7 +10859,7 @@
       <x:c r="R96" s="7" t="n">
         <x:v>45037.947488425925</x:v>
       </x:c>
-      <x:c r="S96" s="8" t="b">
+      <x:c r="S96" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T96" s="22" t="str">
@@ -8060,6 +10879,36 @@
       </x:c>
       <x:c r="Y96" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z96" s="22" t="str">
+        <x:v>contracts/0x49d82927e32138d8d6cedea634231443ee26e00e</x:v>
+      </x:c>
+      <x:c r="AA96" s="22" t="str">
+        <x:v>contracts/0x49d82927e32138d8d6cedea634231443ee26e00e/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB96" s="22" t="str">
+        <x:v>dc43c0f2b51d497248db0995388b2ef669e38dee3b40d7264f2983b648ce9c88</x:v>
+      </x:c>
+      <x:c r="AC96" s="20" t="n">
+        <x:v>9452</x:v>
+      </x:c>
+      <x:c r="AD96" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE96" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF96" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG96" s="20" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="AH96" s="22" t="str">
+        <x:v>QuirklingsImplementationV2</x:v>
+      </x:c>
+      <x:c r="AI96" s="22" t="str">
+        <x:v>0.8.17+commit.8df45f5f</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="18" customHeight="1">
@@ -8117,7 +10966,7 @@
       <x:c r="R97" s="7" t="n">
         <x:v>45045.494988425926</x:v>
       </x:c>
-      <x:c r="S97" s="8" t="b">
+      <x:c r="S97" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T97" s="22" t="str">
@@ -8138,6 +10987,32 @@
       <x:c r="Y97" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z97" s="22" t="str">
+        <x:v>contracts/0x18911b9793d6f063bbebb024dccea5f290f17e4d</x:v>
+      </x:c>
+      <x:c r="AA97" s="22" t="str">
+        <x:v>contracts/0x18911b9793d6f063bbebb024dccea5f290f17e4d/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB97" s="22" t="str">
+        <x:v>4608e2f7cf2d144a2c713fee79a7da73fc93c01b0c68dd8a355fe2fd00893fb2</x:v>
+      </x:c>
+      <x:c r="AC97" s="20" t="n">
+        <x:v>11471</x:v>
+      </x:c>
+      <x:c r="AD97" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE97" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF97" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG97" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH97" s="22" t="str"/>
+      <x:c r="AI97" s="22" t="str"/>
     </x:row>
     <x:row r="98" ht="18" customHeight="1">
       <x:c r="A98" s="22" t="str">
@@ -8194,7 +11069,7 @@
       <x:c r="R98" s="7" t="n">
         <x:v>45057.75568287037</x:v>
       </x:c>
-      <x:c r="S98" s="8" t="b">
+      <x:c r="S98" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T98" s="22" t="str">
@@ -8214,6 +11089,36 @@
       </x:c>
       <x:c r="Y98" s="7" t="n">
         <x:v>46252.77583333333</x:v>
+      </x:c>
+      <x:c r="Z98" s="22" t="str">
+        <x:v>contracts/0x982edd74fb8a7d04c95eda20e475fc57d92af0a9</x:v>
+      </x:c>
+      <x:c r="AA98" s="22" t="str">
+        <x:v>contracts/0x982edd74fb8a7d04c95eda20e475fc57d92af0a9/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB98" s="22" t="str">
+        <x:v>8b0b4bbdd579b5a93b69a0756e92adb822e572d04bf54dcfe818e42f329169e5</x:v>
+      </x:c>
+      <x:c r="AC98" s="20" t="n">
+        <x:v>14355</x:v>
+      </x:c>
+      <x:c r="AD98" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE98" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="AF98" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="AG98" s="20" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="AH98" s="22" t="str">
+        <x:v>MEMEKONG</x:v>
+      </x:c>
+      <x:c r="AI98" s="22" t="str">
+        <x:v>0.8.18+commit.87f61d96</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="18" customHeight="1">
@@ -8271,7 +11176,7 @@
       <x:c r="R99" s="7" t="n">
         <x:v>45062.380266203705</x:v>
       </x:c>
-      <x:c r="S99" s="8" t="b">
+      <x:c r="S99" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T99" s="22" t="str">
@@ -8292,6 +11197,32 @@
       <x:c r="Y99" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z99" s="22" t="str">
+        <x:v>contracts/0xbd1ab5ed43cd8377c8fa3dbebcd5b466b1beeba0</x:v>
+      </x:c>
+      <x:c r="AA99" s="22" t="str">
+        <x:v>contracts/0xbd1ab5ed43cd8377c8fa3dbebcd5b466b1beeba0/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB99" s="22" t="str">
+        <x:v>163ab0522e2b219d55694431141db2de20649ae9ece6f03e578868761b84cb9e</x:v>
+      </x:c>
+      <x:c r="AC99" s="20" t="n">
+        <x:v>5825</x:v>
+      </x:c>
+      <x:c r="AD99" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE99" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF99" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG99" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH99" s="22" t="str"/>
+      <x:c r="AI99" s="22" t="str"/>
     </x:row>
     <x:row r="100" ht="18" customHeight="1">
       <x:c r="A100" s="22" t="str">
@@ -8348,7 +11279,7 @@
       <x:c r="R100" s="7" t="n">
         <x:v>45081.03679398148</x:v>
       </x:c>
-      <x:c r="S100" s="8" t="b">
+      <x:c r="S100" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T100" s="22" t="str">
@@ -8369,6 +11300,32 @@
       <x:c r="Y100" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z100" s="22" t="str">
+        <x:v>contracts/0xbdadd6dc0a1f8905cc339b9ce0a25208fd2b5da5</x:v>
+      </x:c>
+      <x:c r="AA100" s="22" t="str">
+        <x:v>contracts/0xbdadd6dc0a1f8905cc339b9ce0a25208fd2b5da5/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB100" s="22" t="str">
+        <x:v>9f13624f25554384c247a00c3e2d0a85d1ae80b84b4c392ac7a7a3c4ce424017</x:v>
+      </x:c>
+      <x:c r="AC100" s="20" t="n">
+        <x:v>1757</x:v>
+      </x:c>
+      <x:c r="AD100" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE100" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF100" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG100" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH100" s="22" t="str"/>
+      <x:c r="AI100" s="22" t="str"/>
     </x:row>
     <x:row r="101" ht="18" customHeight="1">
       <x:c r="A101" s="22" t="str">
@@ -8425,7 +11382,7 @@
       <x:c r="R101" s="7" t="n">
         <x:v>45082.2377662037</x:v>
       </x:c>
-      <x:c r="S101" s="8" t="b">
+      <x:c r="S101" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T101" s="22" t="str">
@@ -8446,6 +11403,32 @@
       <x:c r="Y101" s="7" t="n">
         <x:v>46252.77583333333</x:v>
       </x:c>
+      <x:c r="Z101" s="22" t="str">
+        <x:v>contracts/0x987411b73708d5746de2c412cc234da90b1245a7</x:v>
+      </x:c>
+      <x:c r="AA101" s="22" t="str">
+        <x:v>contracts/0x987411b73708d5746de2c412cc234da90b1245a7/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="AB101" s="22" t="str">
+        <x:v>25f04f52ac94a9221ef0e92c413120409ced084e4bd80126d214682527d6f31b</x:v>
+      </x:c>
+      <x:c r="AC101" s="20" t="n">
+        <x:v>2042</x:v>
+      </x:c>
+      <x:c r="AD101" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE101" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="AF101" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="AG101" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH101" s="22" t="str"/>
+      <x:c r="AI101" s="22" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="Q2:Q101">
@@ -8458,9 +11441,14 @@
       <x:formula>TRUE</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="AD2:AD101">
+    <x:cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <x:formula>TRUE</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b320b974e6c4aad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R778f1233056346a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8469,147 +11457,4924 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="105" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="48" customHeight="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="66" t="str">
         <x:v>Solidity Upgrade Transactions 100</x:v>
       </x:c>
-      <x:c r="B1" s="56"/>
-    </x:row>
-    <x:row r="2" ht="28" customHeight="1">
-      <x:c r="A2" s="57" t="str">
-        <x:v>Research-ready mapping release: Ethereum mainnet upgrade transaction → new implementation</x:v>
-      </x:c>
-      <x:c r="B2" s="57"/>
+      <x:c r="B1" s="66"/>
+    </x:row>
+    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A2" s="67" t="str">
+        <x:v>Ethereum mainnet upgrade transaction → new implementation, with linked code artifacts</x:v>
+      </x:c>
+      <x:c r="B2" s="67"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="58"/>
-      <x:c r="B3" s="58"/>
+      <x:c r="A3" s="68"/>
+      <x:c r="B3" s="68"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="59" t="str">
+      <x:c r="A4" s="69" t="str">
         <x:v>Quality check</x:v>
       </x:c>
-      <x:c r="B4" s="60" t="str">
+      <x:c r="B4" s="70" t="str">
         <x:v>Value</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="61" t="str">
+      <x:c r="A5" s="71" t="str">
         <x:v>Mapping rows</x:v>
       </x:c>
-      <x:c r="B5" s="62" t="n">
+      <x:c r="B5" s="72" t="n">
         <x:f>COUNTA('Mappings'!$A$2:$A$101)</x:f>
         <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="61" t="str">
+      <x:c r="A6" s="71" t="str">
         <x:v>Successful receipts</x:v>
       </x:c>
-      <x:c r="B6" s="62" t="n">
+      <x:c r="B6" s="72" t="n">
         <x:f>COUNTIF('Mappings'!$O$2:$O$101,"success")</x:f>
         <x:v>100</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A7" s="61" t="str">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="71" t="str">
         <x:v>Rows with Upgraded(address) validation flag</x:v>
       </x:c>
-      <x:c r="B7" s="62" t="n">
+      <x:c r="B7" s="72" t="n">
         <x:f>COUNTA('Mappings'!$Q$2:$Q$101)</x:f>
         <x:v>100</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A8" s="61" t="str">
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="71" t="str">
         <x:v>Rows with source/block timestamp validation flag</x:v>
       </x:c>
-      <x:c r="B8" s="62" t="n">
+      <x:c r="B8" s="72" t="n">
         <x:f>COUNTA('Mappings'!$S$2:$S$101)</x:f>
         <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="61" t="str">
+      <x:c r="A9" s="71" t="str">
+        <x:v>Distinct new implementations</x:v>
+      </x:c>
+      <x:c r="B9" s="72" t="n">
+        <x:f>COUNTA('Contract Artifacts'!$A$2:$A$86)</x:f>
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="71" t="str">
+        <x:v>Runtime bytecode artifacts</x:v>
+      </x:c>
+      <x:c r="B10" s="72" t="n">
+        <x:f>COUNTA('Contract Artifacts'!$D$2:$D$86)</x:f>
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="71" t="str">
+        <x:v>Implementations with verified source</x:v>
+      </x:c>
+      <x:c r="B11" s="72" t="n">
+        <x:f>COUNTIF('Contract Artifacts'!$H$2:$H$86,"sourcify")+COUNTIF('Contract Artifacts'!$H$2:$H$86,"blockscout")</x:f>
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="71" t="str">
+        <x:v>Implementations without verified source</x:v>
+      </x:c>
+      <x:c r="B12" s="72" t="n">
+        <x:f>COUNTIF('Contract Artifacts'!$H$2:$H$86,"none")</x:f>
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="71" t="str">
         <x:v>Network</x:v>
       </x:c>
-      <x:c r="B9" s="62" t="str">
+      <x:c r="B13" s="72" t="str">
         <x:v>Ethereum mainnet (chain ID 1)</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="61" t="str">
-        <x:v>Selection</x:v>
-      </x:c>
-      <x:c r="B10" s="62" t="str">
-        <x:v>Deterministic SHA-256 ranking; at most one mapping per event-emitting proxy</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="61" t="str">
-        <x:v>Scope</x:v>
-      </x:c>
-      <x:c r="B11" s="62" t="str">
-        <x:v>Direct upgradeTo(address) and upgradeToAndCall(address,bytes) only</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="63" t="str">
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="73" t="str">
         <x:v>Important limit</x:v>
       </x:c>
-      <x:c r="B12" s="64" t="str">
-        <x:v>This maps transactions to new implementations; it is not yet an old/new verification snapshot benchmark.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="58"/>
-      <x:c r="B13" s="58"/>
-    </x:row>
-    <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="59" t="str">
+      <x:c r="B14" s="74" t="str">
+        <x:v>Artifacts cover new implementations. Old implementation resolution and historical state snapshots remain incomplete.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="68"/>
+      <x:c r="B15" s="68"/>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="69" t="str">
         <x:v>Provenance</x:v>
       </x:c>
-      <x:c r="B14" s="60" t="str">
+      <x:c r="B16" s="70" t="str">
         <x:v>Value</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="15" hidden="0" customHeight="1">
-      <x:c r="A15" s="61" t="str">
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="71" t="str">
         <x:v>Candidate dataset</x:v>
       </x:c>
-      <x:c r="B15" s="62" t="str">
+      <x:c r="B17" s="72" t="str">
         <x:v>USCDetector</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="61" t="str">
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="71" t="str">
         <x:v>Pinned source commit</x:v>
       </x:c>
-      <x:c r="B16" s="62" t="str">
+      <x:c r="B18" s="72" t="str">
         <x:v>9b2bf71d1929a8bc27c88b52fe9224c24325cd68</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A17" s="61" t="str">
-        <x:v>Pinned artifact URL</x:v>
-      </x:c>
-      <x:c r="B17" s="62" t="str">
-        <x:v>https://raw.githubusercontent.com/xiaofan88/USCDetector/9b2bf71d1929a8bc27c88b52fe9224c24325cd68/upgrade_chains_data/proxy_upgrade_transactions_group_all_remove_repeat.json</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="63" t="str">
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="71" t="str">
+        <x:v>Source-code services</x:v>
+      </x:c>
+      <x:c r="B19" s="72" t="str">
+        <x:v>Sourcify v2, with Blockscout fallback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="73" t="str">
         <x:v>Paper</x:v>
       </x:c>
-      <x:c r="B18" s="64" t="str">
+      <x:c r="B20" s="74" t="str">
         <x:v>Xiaofan Li et al., Characterizing Ethereum Upgradable Smart Contracts and Their Security Implications, WWW 2024</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="44" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="55" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="65" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="68" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="28" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="60" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="60" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="65" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="60" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="65" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="75" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="50" customHeight="1">
+      <x:c r="A1" s="32" t="str">
+        <x:v>implementation_address</x:v>
+      </x:c>
+      <x:c r="B1" s="32" t="str">
+        <x:v>mapping_count</x:v>
+      </x:c>
+      <x:c r="C1" s="32" t="str">
+        <x:v>artifact_dir</x:v>
+      </x:c>
+      <x:c r="D1" s="32" t="str">
+        <x:v>runtime_bytecode_path</x:v>
+      </x:c>
+      <x:c r="E1" s="32" t="str">
+        <x:v>runtime_bytecode_sha256</x:v>
+      </x:c>
+      <x:c r="F1" s="32" t="str">
+        <x:v>runtime_bytecode_size_bytes</x:v>
+      </x:c>
+      <x:c r="G1" s="32" t="str">
+        <x:v>source_available</x:v>
+      </x:c>
+      <x:c r="H1" s="32" t="str">
+        <x:v>source_provider</x:v>
+      </x:c>
+      <x:c r="I1" s="32" t="str">
+        <x:v>source_match</x:v>
+      </x:c>
+      <x:c r="J1" s="32" t="str">
+        <x:v>source_file_count</x:v>
+      </x:c>
+      <x:c r="K1" s="32" t="str">
+        <x:v>contract_name</x:v>
+      </x:c>
+      <x:c r="L1" s="32" t="str">
+        <x:v>compiler</x:v>
+      </x:c>
+      <x:c r="M1" s="32" t="str">
+        <x:v>compiler_version</x:v>
+      </x:c>
+      <x:c r="N1" s="32" t="str">
+        <x:v>abi_path</x:v>
+      </x:c>
+      <x:c r="O1" s="32" t="str">
+        <x:v>metadata_path</x:v>
+      </x:c>
+      <x:c r="P1" s="32" t="str">
+        <x:v>standard_json_input_path</x:v>
+      </x:c>
+      <x:c r="Q1" s="32" t="str">
+        <x:v>storage_layout_path</x:v>
+      </x:c>
+      <x:c r="R1" s="32" t="str">
+        <x:v>verification_manifest_path</x:v>
+      </x:c>
+      <x:c r="S1" s="32" t="str">
+        <x:v>verification_url</x:v>
+      </x:c>
+      <x:c r="T1" s="32" t="str">
+        <x:v>collected_at_utc</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="22" t="str">
+        <x:v>0x03fa83d1cff019eee2ea1e12e2b8c4f2abcdd709</x:v>
+      </x:c>
+      <x:c r="B2" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="22" t="str">
+        <x:v>contracts/0x03fa83d1cff019eee2ea1e12e2b8c4f2abcdd709</x:v>
+      </x:c>
+      <x:c r="D2" s="22" t="str">
+        <x:v>contracts/0x03fa83d1cff019eee2ea1e12e2b8c4f2abcdd709/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E2" s="22" t="str">
+        <x:v>0d21511a2938456a031768f57bb8a05247edc1980bfe9df1c8f7a9b09ac89192</x:v>
+      </x:c>
+      <x:c r="F2" s="20" t="n">
+        <x:v>14941</x:v>
+      </x:c>
+      <x:c r="G2" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H2" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I2" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J2" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K2" s="22" t="str">
+        <x:v>SROOT</x:v>
+      </x:c>
+      <x:c r="L2" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M2" s="22" t="str">
+        <x:v>0.8.7+commit.e28d00a7</x:v>
+      </x:c>
+      <x:c r="N2" s="22" t="str">
+        <x:v>contracts/0x03fa83d1cff019eee2ea1e12e2b8c4f2abcdd709/abi.json</x:v>
+      </x:c>
+      <x:c r="O2" s="22" t="str">
+        <x:v>contracts/0x03fa83d1cff019eee2ea1e12e2b8c4f2abcdd709/metadata.json</x:v>
+      </x:c>
+      <x:c r="P2" s="22" t="str">
+        <x:v>contracts/0x03fa83d1cff019eee2ea1e12e2b8c4f2abcdd709/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q2" s="22" t="str">
+        <x:v>contracts/0x03fa83d1cff019eee2ea1e12e2b8c4f2abcdd709/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R2" s="22" t="str">
+        <x:v>contracts/0x03fa83d1cff019eee2ea1e12e2b8c4f2abcdd709/verification.json</x:v>
+      </x:c>
+      <x:c r="S2" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x03fa83d1cff019eee2ea1e12e2b8c4f2abcdd709?fields=all</x:v>
+      </x:c>
+      <x:c r="T2" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="18" customHeight="1">
+      <x:c r="A3" s="22" t="str">
+        <x:v>0x0bcb3b8becaae10acc13fddc0ab09be3351cd30d</x:v>
+      </x:c>
+      <x:c r="B3" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C3" s="22" t="str">
+        <x:v>contracts/0x0bcb3b8becaae10acc13fddc0ab09be3351cd30d</x:v>
+      </x:c>
+      <x:c r="D3" s="22" t="str">
+        <x:v>contracts/0x0bcb3b8becaae10acc13fddc0ab09be3351cd30d/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E3" s="22" t="str">
+        <x:v>808b99798c2563a94b3e9f71a11be1246d21346e6f36826c9b1510939ce87824</x:v>
+      </x:c>
+      <x:c r="F3" s="20" t="n">
+        <x:v>14970</x:v>
+      </x:c>
+      <x:c r="G3" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H3" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I3" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J3" s="20" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K3" s="22" t="str">
+        <x:v>MozartCoreV2</x:v>
+      </x:c>
+      <x:c r="L3" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M3" s="22" t="str">
+        <x:v>0.5.16+commit.9c3226ce</x:v>
+      </x:c>
+      <x:c r="N3" s="22" t="str">
+        <x:v>contracts/0x0bcb3b8becaae10acc13fddc0ab09be3351cd30d/abi.json</x:v>
+      </x:c>
+      <x:c r="O3" s="22" t="str">
+        <x:v>contracts/0x0bcb3b8becaae10acc13fddc0ab09be3351cd30d/metadata.json</x:v>
+      </x:c>
+      <x:c r="P3" s="22" t="str">
+        <x:v>contracts/0x0bcb3b8becaae10acc13fddc0ab09be3351cd30d/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q3" s="22" t="str">
+        <x:v>contracts/0x0bcb3b8becaae10acc13fddc0ab09be3351cd30d/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R3" s="22" t="str">
+        <x:v>contracts/0x0bcb3b8becaae10acc13fddc0ab09be3351cd30d/verification.json</x:v>
+      </x:c>
+      <x:c r="S3" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x0bcb3b8becaae10acc13fddc0ab09be3351cd30d?fields=all</x:v>
+      </x:c>
+      <x:c r="T3" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="18" customHeight="1">
+      <x:c r="A4" s="22" t="str">
+        <x:v>0x0c763c902a2d4a0e841ab8dc73a36fa776915950</x:v>
+      </x:c>
+      <x:c r="B4" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="22" t="str">
+        <x:v>contracts/0x0c763c902a2d4a0e841ab8dc73a36fa776915950</x:v>
+      </x:c>
+      <x:c r="D4" s="22" t="str">
+        <x:v>contracts/0x0c763c902a2d4a0e841ab8dc73a36fa776915950/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E4" s="22" t="str">
+        <x:v>dee5b2a1f9034d400e621a356869acafcc40f601708a0c5e637cef2430ceb312</x:v>
+      </x:c>
+      <x:c r="F4" s="20" t="n">
+        <x:v>2920</x:v>
+      </x:c>
+      <x:c r="G4" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H4" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I4" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J4" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K4" s="22" t="str"/>
+      <x:c r="L4" s="22" t="str"/>
+      <x:c r="M4" s="22" t="str"/>
+      <x:c r="N4" s="22" t="str"/>
+      <x:c r="O4" s="22" t="str"/>
+      <x:c r="P4" s="22" t="str"/>
+      <x:c r="Q4" s="22" t="str"/>
+      <x:c r="R4" s="22" t="str">
+        <x:v>contracts/0x0c763c902a2d4a0e841ab8dc73a36fa776915950/verification.json</x:v>
+      </x:c>
+      <x:c r="S4" s="22" t="str"/>
+      <x:c r="T4" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="18" customHeight="1">
+      <x:c r="A5" s="22" t="str">
+        <x:v>0x0cb95a8577f694d741be100fdb3efab369ecc945</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="22" t="str">
+        <x:v>contracts/0x0cb95a8577f694d741be100fdb3efab369ecc945</x:v>
+      </x:c>
+      <x:c r="D5" s="22" t="str">
+        <x:v>contracts/0x0cb95a8577f694d741be100fdb3efab369ecc945/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E5" s="22" t="str">
+        <x:v>dc7bfccea6f3b6066f2a0df9ecfdffc6e9911838a306b49779df468324b680f6</x:v>
+      </x:c>
+      <x:c r="F5" s="20" t="n">
+        <x:v>12211</x:v>
+      </x:c>
+      <x:c r="G5" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H5" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I5" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J5" s="20" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K5" s="22" t="str">
+        <x:v>ERC721Burnable</x:v>
+      </x:c>
+      <x:c r="L5" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M5" s="22" t="str">
+        <x:v>0.8.13+commit.abaa5c0e</x:v>
+      </x:c>
+      <x:c r="N5" s="22" t="str">
+        <x:v>contracts/0x0cb95a8577f694d741be100fdb3efab369ecc945/abi.json</x:v>
+      </x:c>
+      <x:c r="O5" s="22" t="str">
+        <x:v>contracts/0x0cb95a8577f694d741be100fdb3efab369ecc945/metadata.json</x:v>
+      </x:c>
+      <x:c r="P5" s="22" t="str">
+        <x:v>contracts/0x0cb95a8577f694d741be100fdb3efab369ecc945/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q5" s="22" t="str">
+        <x:v>contracts/0x0cb95a8577f694d741be100fdb3efab369ecc945/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R5" s="22" t="str">
+        <x:v>contracts/0x0cb95a8577f694d741be100fdb3efab369ecc945/verification.json</x:v>
+      </x:c>
+      <x:c r="S5" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x0cb95a8577f694d741be100fdb3efab369ecc945?fields=all</x:v>
+      </x:c>
+      <x:c r="T5" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="18" customHeight="1">
+      <x:c r="A6" s="22" t="str">
+        <x:v>0x0d970afb431c8188a49eaa3782e6e37ffb16011a</x:v>
+      </x:c>
+      <x:c r="B6" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C6" s="22" t="str">
+        <x:v>contracts/0x0d970afb431c8188a49eaa3782e6e37ffb16011a</x:v>
+      </x:c>
+      <x:c r="D6" s="22" t="str">
+        <x:v>contracts/0x0d970afb431c8188a49eaa3782e6e37ffb16011a/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E6" s="22" t="str">
+        <x:v>1f969f0960e35d2e9d12149f83e41a3d626bb0053d0cfe31bf21426bd5a3b0e9</x:v>
+      </x:c>
+      <x:c r="F6" s="20" t="n">
+        <x:v>8309</x:v>
+      </x:c>
+      <x:c r="G6" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I6" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J6" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6" s="22" t="str"/>
+      <x:c r="L6" s="22" t="str"/>
+      <x:c r="M6" s="22" t="str"/>
+      <x:c r="N6" s="22" t="str"/>
+      <x:c r="O6" s="22" t="str"/>
+      <x:c r="P6" s="22" t="str"/>
+      <x:c r="Q6" s="22" t="str"/>
+      <x:c r="R6" s="22" t="str">
+        <x:v>contracts/0x0d970afb431c8188a49eaa3782e6e37ffb16011a/verification.json</x:v>
+      </x:c>
+      <x:c r="S6" s="22" t="str"/>
+      <x:c r="T6" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="18" customHeight="1">
+      <x:c r="A7" s="22" t="str">
+        <x:v>0x137ceed64037adab752ed4a4afbec1df3d2f0dad</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="22" t="str">
+        <x:v>contracts/0x137ceed64037adab752ed4a4afbec1df3d2f0dad</x:v>
+      </x:c>
+      <x:c r="D7" s="22" t="str">
+        <x:v>contracts/0x137ceed64037adab752ed4a4afbec1df3d2f0dad/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E7" s="22" t="str">
+        <x:v>507e3afe457f66437858843b6a81588a8b2169f17b38833f97f316db9220e8f2</x:v>
+      </x:c>
+      <x:c r="F7" s="20" t="n">
+        <x:v>5551</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H7" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I7" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J7" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K7" s="22" t="str">
+        <x:v>Registry</x:v>
+      </x:c>
+      <x:c r="L7" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M7" s="22" t="str">
+        <x:v>0.4.23+commit.124ca40d</x:v>
+      </x:c>
+      <x:c r="N7" s="22" t="str">
+        <x:v>contracts/0x137ceed64037adab752ed4a4afbec1df3d2f0dad/abi.json</x:v>
+      </x:c>
+      <x:c r="O7" s="22" t="str">
+        <x:v>contracts/0x137ceed64037adab752ed4a4afbec1df3d2f0dad/metadata.json</x:v>
+      </x:c>
+      <x:c r="P7" s="22" t="str">
+        <x:v>contracts/0x137ceed64037adab752ed4a4afbec1df3d2f0dad/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q7" s="22" t="str"/>
+      <x:c r="R7" s="22" t="str">
+        <x:v>contracts/0x137ceed64037adab752ed4a4afbec1df3d2f0dad/verification.json</x:v>
+      </x:c>
+      <x:c r="S7" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x137ceed64037adab752ed4a4afbec1df3d2f0dad?fields=all</x:v>
+      </x:c>
+      <x:c r="T7" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="18" customHeight="1">
+      <x:c r="A8" s="22" t="str">
+        <x:v>0x18911b9793d6f063bbebb024dccea5f290f17e4d</x:v>
+      </x:c>
+      <x:c r="B8" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="22" t="str">
+        <x:v>contracts/0x18911b9793d6f063bbebb024dccea5f290f17e4d</x:v>
+      </x:c>
+      <x:c r="D8" s="22" t="str">
+        <x:v>contracts/0x18911b9793d6f063bbebb024dccea5f290f17e4d/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E8" s="22" t="str">
+        <x:v>4608e2f7cf2d144a2c713fee79a7da73fc93c01b0c68dd8a355fe2fd00893fb2</x:v>
+      </x:c>
+      <x:c r="F8" s="20" t="n">
+        <x:v>11471</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I8" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J8" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8" s="22" t="str"/>
+      <x:c r="L8" s="22" t="str"/>
+      <x:c r="M8" s="22" t="str"/>
+      <x:c r="N8" s="22" t="str"/>
+      <x:c r="O8" s="22" t="str"/>
+      <x:c r="P8" s="22" t="str"/>
+      <x:c r="Q8" s="22" t="str"/>
+      <x:c r="R8" s="22" t="str">
+        <x:v>contracts/0x18911b9793d6f063bbebb024dccea5f290f17e4d/verification.json</x:v>
+      </x:c>
+      <x:c r="S8" s="22" t="str"/>
+      <x:c r="T8" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="18" customHeight="1">
+      <x:c r="A9" s="22" t="str">
+        <x:v>0x1a0a086a6ecc74dd0ba1ac82e5fc60003155e632</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="22" t="str">
+        <x:v>contracts/0x1a0a086a6ecc74dd0ba1ac82e5fc60003155e632</x:v>
+      </x:c>
+      <x:c r="D9" s="22" t="str">
+        <x:v>contracts/0x1a0a086a6ecc74dd0ba1ac82e5fc60003155e632/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E9" s="22" t="str">
+        <x:v>6db28d8e682473f8b190b7e1f3ed20dcf1ba6998ebf8bc8ea193a40104c3aee9</x:v>
+      </x:c>
+      <x:c r="F9" s="20" t="n">
+        <x:v>24451</x:v>
+      </x:c>
+      <x:c r="G9" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I9" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J9" s="20" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K9" s="22" t="str">
+        <x:v>FreaksNGuildsMigrated</x:v>
+      </x:c>
+      <x:c r="L9" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M9" s="22" t="str">
+        <x:v>0.8.11+commit.d7f03943</x:v>
+      </x:c>
+      <x:c r="N9" s="22" t="str">
+        <x:v>contracts/0x1a0a086a6ecc74dd0ba1ac82e5fc60003155e632/abi.json</x:v>
+      </x:c>
+      <x:c r="O9" s="22" t="str">
+        <x:v>contracts/0x1a0a086a6ecc74dd0ba1ac82e5fc60003155e632/metadata.json</x:v>
+      </x:c>
+      <x:c r="P9" s="22" t="str">
+        <x:v>contracts/0x1a0a086a6ecc74dd0ba1ac82e5fc60003155e632/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q9" s="22" t="str">
+        <x:v>contracts/0x1a0a086a6ecc74dd0ba1ac82e5fc60003155e632/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R9" s="22" t="str">
+        <x:v>contracts/0x1a0a086a6ecc74dd0ba1ac82e5fc60003155e632/verification.json</x:v>
+      </x:c>
+      <x:c r="S9" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x1a0a086a6ecc74dd0ba1ac82e5fc60003155e632?fields=all</x:v>
+      </x:c>
+      <x:c r="T9" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="18" customHeight="1">
+      <x:c r="A10" s="22" t="str">
+        <x:v>0x1b3efa9a64af24781f4c4e36576c73dbea2ebfdf</x:v>
+      </x:c>
+      <x:c r="B10" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="22" t="str">
+        <x:v>contracts/0x1b3efa9a64af24781f4c4e36576c73dbea2ebfdf</x:v>
+      </x:c>
+      <x:c r="D10" s="22" t="str">
+        <x:v>contracts/0x1b3efa9a64af24781f4c4e36576c73dbea2ebfdf/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E10" s="22" t="str">
+        <x:v>59528f03b01b193602c7bd2346e3ebc9a57b48426dcffb3dc8c1af73cd642a8f</x:v>
+      </x:c>
+      <x:c r="F10" s="20" t="n">
+        <x:v>9063</x:v>
+      </x:c>
+      <x:c r="G10" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H10" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I10" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J10" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K10" s="22" t="str"/>
+      <x:c r="L10" s="22" t="str"/>
+      <x:c r="M10" s="22" t="str"/>
+      <x:c r="N10" s="22" t="str"/>
+      <x:c r="O10" s="22" t="str"/>
+      <x:c r="P10" s="22" t="str"/>
+      <x:c r="Q10" s="22" t="str"/>
+      <x:c r="R10" s="22" t="str">
+        <x:v>contracts/0x1b3efa9a64af24781f4c4e36576c73dbea2ebfdf/verification.json</x:v>
+      </x:c>
+      <x:c r="S10" s="22" t="str"/>
+      <x:c r="T10" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="18" customHeight="1">
+      <x:c r="A11" s="22" t="str">
+        <x:v>0x1b48d2ea2f9b868ea2f276b431f49879ae58082d</x:v>
+      </x:c>
+      <x:c r="B11" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="str">
+        <x:v>contracts/0x1b48d2ea2f9b868ea2f276b431f49879ae58082d</x:v>
+      </x:c>
+      <x:c r="D11" s="22" t="str">
+        <x:v>contracts/0x1b48d2ea2f9b868ea2f276b431f49879ae58082d/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E11" s="22" t="str">
+        <x:v>548acc6046d2bffdef4feb95ffe5446668c87c6d0c9eccff863540a8be64b841</x:v>
+      </x:c>
+      <x:c r="F11" s="20" t="n">
+        <x:v>17361</x:v>
+      </x:c>
+      <x:c r="G11" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H11" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I11" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J11" s="20" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="22" t="str">
+        <x:v>VesperWBTCPlus</x:v>
+      </x:c>
+      <x:c r="L11" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M11" s="22" t="str">
+        <x:v>0.8.0+commit.c7dfd78e</x:v>
+      </x:c>
+      <x:c r="N11" s="22" t="str">
+        <x:v>contracts/0x1b48d2ea2f9b868ea2f276b431f49879ae58082d/abi.json</x:v>
+      </x:c>
+      <x:c r="O11" s="22" t="str">
+        <x:v>contracts/0x1b48d2ea2f9b868ea2f276b431f49879ae58082d/metadata.json</x:v>
+      </x:c>
+      <x:c r="P11" s="22" t="str">
+        <x:v>contracts/0x1b48d2ea2f9b868ea2f276b431f49879ae58082d/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q11" s="22" t="str">
+        <x:v>contracts/0x1b48d2ea2f9b868ea2f276b431f49879ae58082d/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R11" s="22" t="str">
+        <x:v>contracts/0x1b48d2ea2f9b868ea2f276b431f49879ae58082d/verification.json</x:v>
+      </x:c>
+      <x:c r="S11" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x1b48d2ea2f9b868ea2f276b431f49879ae58082d?fields=all</x:v>
+      </x:c>
+      <x:c r="T11" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="18" customHeight="1">
+      <x:c r="A12" s="22" t="str">
+        <x:v>0x1e8fe97b27db8d16e69e1f15069c61fdbe66b66d</x:v>
+      </x:c>
+      <x:c r="B12" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="str">
+        <x:v>contracts/0x1e8fe97b27db8d16e69e1f15069c61fdbe66b66d</x:v>
+      </x:c>
+      <x:c r="D12" s="22" t="str">
+        <x:v>contracts/0x1e8fe97b27db8d16e69e1f15069c61fdbe66b66d/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E12" s="22" t="str">
+        <x:v>6581cda9aad54b5603d1e82fd8cdf5c4383ea0c8f9dfda0c5aba521abc2d0675</x:v>
+      </x:c>
+      <x:c r="F12" s="20" t="n">
+        <x:v>10854</x:v>
+      </x:c>
+      <x:c r="G12" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H12" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I12" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J12" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K12" s="22" t="str"/>
+      <x:c r="L12" s="22" t="str"/>
+      <x:c r="M12" s="22" t="str"/>
+      <x:c r="N12" s="22" t="str"/>
+      <x:c r="O12" s="22" t="str"/>
+      <x:c r="P12" s="22" t="str"/>
+      <x:c r="Q12" s="22" t="str"/>
+      <x:c r="R12" s="22" t="str">
+        <x:v>contracts/0x1e8fe97b27db8d16e69e1f15069c61fdbe66b66d/verification.json</x:v>
+      </x:c>
+      <x:c r="S12" s="22" t="str"/>
+      <x:c r="T12" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="18" customHeight="1">
+      <x:c r="A13" s="22" t="str">
+        <x:v>0x204d0e6a1be0d11d88dcb48c69f3180b0f772ce2</x:v>
+      </x:c>
+      <x:c r="B13" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="str">
+        <x:v>contracts/0x204d0e6a1be0d11d88dcb48c69f3180b0f772ce2</x:v>
+      </x:c>
+      <x:c r="D13" s="22" t="str">
+        <x:v>contracts/0x204d0e6a1be0d11d88dcb48c69f3180b0f772ce2/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E13" s="22" t="str">
+        <x:v>0844aee005703f50a8d789c4b6227e877a22d20a29fb58b04a6af7a3626cbb20</x:v>
+      </x:c>
+      <x:c r="F13" s="20" t="n">
+        <x:v>23931</x:v>
+      </x:c>
+      <x:c r="G13" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H13" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I13" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J13" s="20" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K13" s="22" t="str">
+        <x:v>Minter</x:v>
+      </x:c>
+      <x:c r="L13" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M13" s="22" t="str">
+        <x:v>0.8.7+commit.e28d00a7</x:v>
+      </x:c>
+      <x:c r="N13" s="22" t="str">
+        <x:v>contracts/0x204d0e6a1be0d11d88dcb48c69f3180b0f772ce2/abi.json</x:v>
+      </x:c>
+      <x:c r="O13" s="22" t="str">
+        <x:v>contracts/0x204d0e6a1be0d11d88dcb48c69f3180b0f772ce2/metadata.json</x:v>
+      </x:c>
+      <x:c r="P13" s="22" t="str">
+        <x:v>contracts/0x204d0e6a1be0d11d88dcb48c69f3180b0f772ce2/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q13" s="22" t="str">
+        <x:v>contracts/0x204d0e6a1be0d11d88dcb48c69f3180b0f772ce2/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R13" s="22" t="str">
+        <x:v>contracts/0x204d0e6a1be0d11d88dcb48c69f3180b0f772ce2/verification.json</x:v>
+      </x:c>
+      <x:c r="S13" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x204d0e6a1be0d11d88dcb48c69f3180b0f772ce2?fields=all</x:v>
+      </x:c>
+      <x:c r="T13" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="18" customHeight="1">
+      <x:c r="A14" s="22" t="str">
+        <x:v>0x2239eb2fc8b94db19dcae519a93445b97c0a5e22</x:v>
+      </x:c>
+      <x:c r="B14" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="str">
+        <x:v>contracts/0x2239eb2fc8b94db19dcae519a93445b97c0a5e22</x:v>
+      </x:c>
+      <x:c r="D14" s="22" t="str">
+        <x:v>contracts/0x2239eb2fc8b94db19dcae519a93445b97c0a5e22/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E14" s="22" t="str">
+        <x:v>12a4507ec38ebad8e594b2d7eb8c675ac1ea19a3a2f45873284ebe4ec35afec0</x:v>
+      </x:c>
+      <x:c r="F14" s="20" t="n">
+        <x:v>3828</x:v>
+      </x:c>
+      <x:c r="G14" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H14" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I14" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J14" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14" s="22" t="str"/>
+      <x:c r="L14" s="22" t="str"/>
+      <x:c r="M14" s="22" t="str"/>
+      <x:c r="N14" s="22" t="str"/>
+      <x:c r="O14" s="22" t="str"/>
+      <x:c r="P14" s="22" t="str"/>
+      <x:c r="Q14" s="22" t="str"/>
+      <x:c r="R14" s="22" t="str">
+        <x:v>contracts/0x2239eb2fc8b94db19dcae519a93445b97c0a5e22/verification.json</x:v>
+      </x:c>
+      <x:c r="S14" s="22" t="str"/>
+      <x:c r="T14" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="18" customHeight="1">
+      <x:c r="A15" s="22" t="str">
+        <x:v>0x26daa1a88c9b2bcda8b0c928e0024130ede7ca0b</x:v>
+      </x:c>
+      <x:c r="B15" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="str">
+        <x:v>contracts/0x26daa1a88c9b2bcda8b0c928e0024130ede7ca0b</x:v>
+      </x:c>
+      <x:c r="D15" s="22" t="str">
+        <x:v>contracts/0x26daa1a88c9b2bcda8b0c928e0024130ede7ca0b/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E15" s="22" t="str">
+        <x:v>8c64658bd56ad582c890a0f037d76a57ed0ebb8f2115a1bc7142e31f9dff91aa</x:v>
+      </x:c>
+      <x:c r="F15" s="20" t="n">
+        <x:v>20111</x:v>
+      </x:c>
+      <x:c r="G15" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H15" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I15" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J15" s="20" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K15" s="22" t="str">
+        <x:v>MegaForceSentinels</x:v>
+      </x:c>
+      <x:c r="L15" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M15" s="22" t="str">
+        <x:v>0.8.17+commit.8df45f5f</x:v>
+      </x:c>
+      <x:c r="N15" s="22" t="str">
+        <x:v>contracts/0x26daa1a88c9b2bcda8b0c928e0024130ede7ca0b/abi.json</x:v>
+      </x:c>
+      <x:c r="O15" s="22" t="str">
+        <x:v>contracts/0x26daa1a88c9b2bcda8b0c928e0024130ede7ca0b/metadata.json</x:v>
+      </x:c>
+      <x:c r="P15" s="22" t="str">
+        <x:v>contracts/0x26daa1a88c9b2bcda8b0c928e0024130ede7ca0b/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q15" s="22" t="str">
+        <x:v>contracts/0x26daa1a88c9b2bcda8b0c928e0024130ede7ca0b/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R15" s="22" t="str">
+        <x:v>contracts/0x26daa1a88c9b2bcda8b0c928e0024130ede7ca0b/verification.json</x:v>
+      </x:c>
+      <x:c r="S15" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x26daa1a88c9b2bcda8b0c928e0024130ede7ca0b?fields=all</x:v>
+      </x:c>
+      <x:c r="T15" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="18" customHeight="1">
+      <x:c r="A16" s="22" t="str">
+        <x:v>0x28546ea0c2894e4b83f91dc6db52c83d0ca61f0e</x:v>
+      </x:c>
+      <x:c r="B16" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="str">
+        <x:v>contracts/0x28546ea0c2894e4b83f91dc6db52c83d0ca61f0e</x:v>
+      </x:c>
+      <x:c r="D16" s="22" t="str">
+        <x:v>contracts/0x28546ea0c2894e4b83f91dc6db52c83d0ca61f0e/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E16" s="22" t="str">
+        <x:v>190d1589c3f735c9774b126f56f75e7a802f992916939b0653738d0b0eb37c05</x:v>
+      </x:c>
+      <x:c r="F16" s="20" t="n">
+        <x:v>24195</x:v>
+      </x:c>
+      <x:c r="G16" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H16" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I16" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J16" s="20" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K16" s="22" t="str">
+        <x:v>DaoMarketPlace</x:v>
+      </x:c>
+      <x:c r="L16" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M16" s="22" t="str">
+        <x:v>0.8.13+commit.abaa5c0e</x:v>
+      </x:c>
+      <x:c r="N16" s="22" t="str">
+        <x:v>contracts/0x28546ea0c2894e4b83f91dc6db52c83d0ca61f0e/abi.json</x:v>
+      </x:c>
+      <x:c r="O16" s="22" t="str">
+        <x:v>contracts/0x28546ea0c2894e4b83f91dc6db52c83d0ca61f0e/metadata.json</x:v>
+      </x:c>
+      <x:c r="P16" s="22" t="str">
+        <x:v>contracts/0x28546ea0c2894e4b83f91dc6db52c83d0ca61f0e/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q16" s="22" t="str">
+        <x:v>contracts/0x28546ea0c2894e4b83f91dc6db52c83d0ca61f0e/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R16" s="22" t="str">
+        <x:v>contracts/0x28546ea0c2894e4b83f91dc6db52c83d0ca61f0e/verification.json</x:v>
+      </x:c>
+      <x:c r="S16" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x28546ea0c2894e4b83f91dc6db52c83d0ca61f0e?fields=all</x:v>
+      </x:c>
+      <x:c r="T16" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="18" customHeight="1">
+      <x:c r="A17" s="22" t="str">
+        <x:v>0x28ecb9b0fb44873106fc1b31bc9189b3f82cf517</x:v>
+      </x:c>
+      <x:c r="B17" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="str">
+        <x:v>contracts/0x28ecb9b0fb44873106fc1b31bc9189b3f82cf517</x:v>
+      </x:c>
+      <x:c r="D17" s="22" t="str">
+        <x:v>contracts/0x28ecb9b0fb44873106fc1b31bc9189b3f82cf517/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E17" s="22" t="str">
+        <x:v>6b8f14e6e1dad26aeadbcee7f2117c99139c353184385d16704116148fbf92c4</x:v>
+      </x:c>
+      <x:c r="F17" s="20" t="n">
+        <x:v>10812</x:v>
+      </x:c>
+      <x:c r="G17" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H17" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I17" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J17" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K17" s="22" t="str">
+        <x:v>CrossDelegate</x:v>
+      </x:c>
+      <x:c r="L17" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M17" s="22" t="str">
+        <x:v>0.4.26+commit.4563c3fc</x:v>
+      </x:c>
+      <x:c r="N17" s="22" t="str">
+        <x:v>contracts/0x28ecb9b0fb44873106fc1b31bc9189b3f82cf517/abi.json</x:v>
+      </x:c>
+      <x:c r="O17" s="22" t="str">
+        <x:v>contracts/0x28ecb9b0fb44873106fc1b31bc9189b3f82cf517/metadata.json</x:v>
+      </x:c>
+      <x:c r="P17" s="22" t="str">
+        <x:v>contracts/0x28ecb9b0fb44873106fc1b31bc9189b3f82cf517/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q17" s="22" t="str"/>
+      <x:c r="R17" s="22" t="str">
+        <x:v>contracts/0x28ecb9b0fb44873106fc1b31bc9189b3f82cf517/verification.json</x:v>
+      </x:c>
+      <x:c r="S17" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x28ecb9b0fb44873106fc1b31bc9189b3f82cf517?fields=all</x:v>
+      </x:c>
+      <x:c r="T17" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="18" customHeight="1">
+      <x:c r="A18" s="22" t="str">
+        <x:v>0x2c39cfa826c139ebc98e9ec2cd8a67ea76dba006</x:v>
+      </x:c>
+      <x:c r="B18" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="str">
+        <x:v>contracts/0x2c39cfa826c139ebc98e9ec2cd8a67ea76dba006</x:v>
+      </x:c>
+      <x:c r="D18" s="22" t="str">
+        <x:v>contracts/0x2c39cfa826c139ebc98e9ec2cd8a67ea76dba006/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E18" s="22" t="str">
+        <x:v>689bf3780b95ecf63e12074bfbdd5898a6fb2ebeebec9c7ceb9f1f94ecdfd089</x:v>
+      </x:c>
+      <x:c r="F18" s="20" t="n">
+        <x:v>2464</x:v>
+      </x:c>
+      <x:c r="G18" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H18" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I18" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J18" s="20" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K18" s="22" t="str">
+        <x:v>ProfitRecord</x:v>
+      </x:c>
+      <x:c r="L18" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M18" s="22" t="str">
+        <x:v>0.8.9+commit.e5eed63a</x:v>
+      </x:c>
+      <x:c r="N18" s="22" t="str">
+        <x:v>contracts/0x2c39cfa826c139ebc98e9ec2cd8a67ea76dba006/abi.json</x:v>
+      </x:c>
+      <x:c r="O18" s="22" t="str">
+        <x:v>contracts/0x2c39cfa826c139ebc98e9ec2cd8a67ea76dba006/metadata.json</x:v>
+      </x:c>
+      <x:c r="P18" s="22" t="str">
+        <x:v>contracts/0x2c39cfa826c139ebc98e9ec2cd8a67ea76dba006/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q18" s="22" t="str">
+        <x:v>contracts/0x2c39cfa826c139ebc98e9ec2cd8a67ea76dba006/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R18" s="22" t="str">
+        <x:v>contracts/0x2c39cfa826c139ebc98e9ec2cd8a67ea76dba006/verification.json</x:v>
+      </x:c>
+      <x:c r="S18" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x2c39cfa826c139ebc98e9ec2cd8a67ea76dba006?fields=all</x:v>
+      </x:c>
+      <x:c r="T18" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="18" customHeight="1">
+      <x:c r="A19" s="22" t="str">
+        <x:v>0x2d897534673be5d5b801a7a6be3dab29f8a17e83</x:v>
+      </x:c>
+      <x:c r="B19" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C19" s="22" t="str">
+        <x:v>contracts/0x2d897534673be5d5b801a7a6be3dab29f8a17e83</x:v>
+      </x:c>
+      <x:c r="D19" s="22" t="str">
+        <x:v>contracts/0x2d897534673be5d5b801a7a6be3dab29f8a17e83/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E19" s="22" t="str">
+        <x:v>73ce5735c10c0acfcc5f3853374b60ca24f9d8bb94efc83b0b393a56bd52422b</x:v>
+      </x:c>
+      <x:c r="F19" s="20" t="n">
+        <x:v>13824</x:v>
+      </x:c>
+      <x:c r="G19" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I19" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J19" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K19" s="22" t="str"/>
+      <x:c r="L19" s="22" t="str"/>
+      <x:c r="M19" s="22" t="str"/>
+      <x:c r="N19" s="22" t="str"/>
+      <x:c r="O19" s="22" t="str"/>
+      <x:c r="P19" s="22" t="str"/>
+      <x:c r="Q19" s="22" t="str"/>
+      <x:c r="R19" s="22" t="str">
+        <x:v>contracts/0x2d897534673be5d5b801a7a6be3dab29f8a17e83/verification.json</x:v>
+      </x:c>
+      <x:c r="S19" s="22" t="str"/>
+      <x:c r="T19" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="18" customHeight="1">
+      <x:c r="A20" s="22" t="str">
+        <x:v>0x2fe3b082c28df92d7e2f9c726a7d0e6cd2c8a061</x:v>
+      </x:c>
+      <x:c r="B20" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C20" s="22" t="str">
+        <x:v>contracts/0x2fe3b082c28df92d7e2f9c726a7d0e6cd2c8a061</x:v>
+      </x:c>
+      <x:c r="D20" s="22" t="str">
+        <x:v>contracts/0x2fe3b082c28df92d7e2f9c726a7d0e6cd2c8a061/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E20" s="22" t="str">
+        <x:v>6c78e0cfbc0ce137dad3efcb2c70a273c9ff2d357d49f40544c1a4be9b1dcb0a</x:v>
+      </x:c>
+      <x:c r="F20" s="20" t="n">
+        <x:v>13004</x:v>
+      </x:c>
+      <x:c r="G20" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H20" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I20" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J20" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K20" s="22" t="str"/>
+      <x:c r="L20" s="22" t="str"/>
+      <x:c r="M20" s="22" t="str"/>
+      <x:c r="N20" s="22" t="str"/>
+      <x:c r="O20" s="22" t="str"/>
+      <x:c r="P20" s="22" t="str"/>
+      <x:c r="Q20" s="22" t="str"/>
+      <x:c r="R20" s="22" t="str">
+        <x:v>contracts/0x2fe3b082c28df92d7e2f9c726a7d0e6cd2c8a061/verification.json</x:v>
+      </x:c>
+      <x:c r="S20" s="22" t="str"/>
+      <x:c r="T20" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="18" customHeight="1">
+      <x:c r="A21" s="22" t="str">
+        <x:v>0x33beeb42544f6276c51e4d29c5d62e226fb337fa</x:v>
+      </x:c>
+      <x:c r="B21" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C21" s="22" t="str">
+        <x:v>contracts/0x33beeb42544f6276c51e4d29c5d62e226fb337fa</x:v>
+      </x:c>
+      <x:c r="D21" s="22" t="str">
+        <x:v>contracts/0x33beeb42544f6276c51e4d29c5d62e226fb337fa/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E21" s="22" t="str">
+        <x:v>1102918538cf772a2f43a5bc7a107b50033280ae6a7e3505fe0fc6a1e93581b5</x:v>
+      </x:c>
+      <x:c r="F21" s="20" t="n">
+        <x:v>4902</x:v>
+      </x:c>
+      <x:c r="G21" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H21" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I21" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J21" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K21" s="22" t="str"/>
+      <x:c r="L21" s="22" t="str"/>
+      <x:c r="M21" s="22" t="str"/>
+      <x:c r="N21" s="22" t="str"/>
+      <x:c r="O21" s="22" t="str"/>
+      <x:c r="P21" s="22" t="str"/>
+      <x:c r="Q21" s="22" t="str"/>
+      <x:c r="R21" s="22" t="str">
+        <x:v>contracts/0x33beeb42544f6276c51e4d29c5d62e226fb337fa/verification.json</x:v>
+      </x:c>
+      <x:c r="S21" s="22" t="str"/>
+      <x:c r="T21" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="18" customHeight="1">
+      <x:c r="A22" s="22" t="str">
+        <x:v>0x3592d5037865f425628583ca1ca3bdc069dfcdd8</x:v>
+      </x:c>
+      <x:c r="B22" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C22" s="22" t="str">
+        <x:v>contracts/0x3592d5037865f425628583ca1ca3bdc069dfcdd8</x:v>
+      </x:c>
+      <x:c r="D22" s="22" t="str">
+        <x:v>contracts/0x3592d5037865f425628583ca1ca3bdc069dfcdd8/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E22" s="22" t="str">
+        <x:v>f26b82009f29edce69ba73bd69d8c0bf1dfe658c3d2044dbf4e5e79f0e3fb50d</x:v>
+      </x:c>
+      <x:c r="F22" s="20" t="n">
+        <x:v>13804</x:v>
+      </x:c>
+      <x:c r="G22" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H22" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I22" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J22" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K22" s="22" t="str">
+        <x:v>TrueAUDMock</x:v>
+      </x:c>
+      <x:c r="L22" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M22" s="22" t="str">
+        <x:v>0.4.23+commit.124ca40d</x:v>
+      </x:c>
+      <x:c r="N22" s="22" t="str">
+        <x:v>contracts/0x3592d5037865f425628583ca1ca3bdc069dfcdd8/abi.json</x:v>
+      </x:c>
+      <x:c r="O22" s="22" t="str">
+        <x:v>contracts/0x3592d5037865f425628583ca1ca3bdc069dfcdd8/metadata.json</x:v>
+      </x:c>
+      <x:c r="P22" s="22" t="str">
+        <x:v>contracts/0x3592d5037865f425628583ca1ca3bdc069dfcdd8/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q22" s="22" t="str"/>
+      <x:c r="R22" s="22" t="str">
+        <x:v>contracts/0x3592d5037865f425628583ca1ca3bdc069dfcdd8/verification.json</x:v>
+      </x:c>
+      <x:c r="S22" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x3592d5037865f425628583ca1ca3bdc069dfcdd8?fields=all</x:v>
+      </x:c>
+      <x:c r="T22" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="18" customHeight="1">
+      <x:c r="A23" s="22" t="str">
+        <x:v>0x3747f235d1e7ae96ebd54bc049cc68b2714d7586</x:v>
+      </x:c>
+      <x:c r="B23" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C23" s="22" t="str">
+        <x:v>contracts/0x3747f235d1e7ae96ebd54bc049cc68b2714d7586</x:v>
+      </x:c>
+      <x:c r="D23" s="22" t="str">
+        <x:v>contracts/0x3747f235d1e7ae96ebd54bc049cc68b2714d7586/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E23" s="22" t="str">
+        <x:v>e06a8436398dea9deb1fb77a0de082c985002372c461fac81b2f4109db3a9170</x:v>
+      </x:c>
+      <x:c r="F23" s="20" t="n">
+        <x:v>15447</x:v>
+      </x:c>
+      <x:c r="G23" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H23" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I23" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J23" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K23" s="22" t="str">
+        <x:v>Vesting</x:v>
+      </x:c>
+      <x:c r="L23" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M23" s="22" t="str">
+        <x:v>0.5.8+commit.23d335f2</x:v>
+      </x:c>
+      <x:c r="N23" s="22" t="str">
+        <x:v>contracts/0x3747f235d1e7ae96ebd54bc049cc68b2714d7586/abi.json</x:v>
+      </x:c>
+      <x:c r="O23" s="22" t="str">
+        <x:v>contracts/0x3747f235d1e7ae96ebd54bc049cc68b2714d7586/metadata.json</x:v>
+      </x:c>
+      <x:c r="P23" s="22" t="str">
+        <x:v>contracts/0x3747f235d1e7ae96ebd54bc049cc68b2714d7586/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q23" s="22" t="str"/>
+      <x:c r="R23" s="22" t="str">
+        <x:v>contracts/0x3747f235d1e7ae96ebd54bc049cc68b2714d7586/verification.json</x:v>
+      </x:c>
+      <x:c r="S23" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x3747f235d1e7ae96ebd54bc049cc68b2714d7586?fields=all</x:v>
+      </x:c>
+      <x:c r="T23" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="18" customHeight="1">
+      <x:c r="A24" s="22" t="str">
+        <x:v>0x3883f75b2be639f9236ed230dd7202f31eaf38d5</x:v>
+      </x:c>
+      <x:c r="B24" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C24" s="22" t="str">
+        <x:v>contracts/0x3883f75b2be639f9236ed230dd7202f31eaf38d5</x:v>
+      </x:c>
+      <x:c r="D24" s="22" t="str">
+        <x:v>contracts/0x3883f75b2be639f9236ed230dd7202f31eaf38d5/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E24" s="22" t="str">
+        <x:v>95ffc79cd5015cc5c586f14057b7c2cb170fd7a4182cb69837a0934e5a1733c0</x:v>
+      </x:c>
+      <x:c r="F24" s="20" t="n">
+        <x:v>6682</x:v>
+      </x:c>
+      <x:c r="G24" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H24" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I24" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J24" s="20" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="K24" s="22" t="str">
+        <x:v>LockTOSv2Proxy</x:v>
+      </x:c>
+      <x:c r="L24" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M24" s="22" t="str">
+        <x:v>0.7.6+commit.7338295f</x:v>
+      </x:c>
+      <x:c r="N24" s="22" t="str">
+        <x:v>contracts/0x3883f75b2be639f9236ed230dd7202f31eaf38d5/abi.json</x:v>
+      </x:c>
+      <x:c r="O24" s="22" t="str">
+        <x:v>contracts/0x3883f75b2be639f9236ed230dd7202f31eaf38d5/metadata.json</x:v>
+      </x:c>
+      <x:c r="P24" s="22" t="str">
+        <x:v>contracts/0x3883f75b2be639f9236ed230dd7202f31eaf38d5/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q24" s="22" t="str">
+        <x:v>contracts/0x3883f75b2be639f9236ed230dd7202f31eaf38d5/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R24" s="22" t="str">
+        <x:v>contracts/0x3883f75b2be639f9236ed230dd7202f31eaf38d5/verification.json</x:v>
+      </x:c>
+      <x:c r="S24" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x3883f75b2be639f9236ed230dd7202f31eaf38d5?fields=all</x:v>
+      </x:c>
+      <x:c r="T24" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="18" customHeight="1">
+      <x:c r="A25" s="22" t="str">
+        <x:v>0x3884d9ed20b76af88c93f39cf65546f866195b54</x:v>
+      </x:c>
+      <x:c r="B25" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C25" s="22" t="str">
+        <x:v>contracts/0x3884d9ed20b76af88c93f39cf65546f866195b54</x:v>
+      </x:c>
+      <x:c r="D25" s="22" t="str">
+        <x:v>contracts/0x3884d9ed20b76af88c93f39cf65546f866195b54/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E25" s="22" t="str">
+        <x:v>140183a242c62b068faba3ec1c88584511c87a170ea59df589101b093d6185f7</x:v>
+      </x:c>
+      <x:c r="F25" s="20" t="n">
+        <x:v>12585</x:v>
+      </x:c>
+      <x:c r="G25" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H25" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I25" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J25" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K25" s="22" t="str"/>
+      <x:c r="L25" s="22" t="str"/>
+      <x:c r="M25" s="22" t="str"/>
+      <x:c r="N25" s="22" t="str"/>
+      <x:c r="O25" s="22" t="str"/>
+      <x:c r="P25" s="22" t="str"/>
+      <x:c r="Q25" s="22" t="str"/>
+      <x:c r="R25" s="22" t="str">
+        <x:v>contracts/0x3884d9ed20b76af88c93f39cf65546f866195b54/verification.json</x:v>
+      </x:c>
+      <x:c r="S25" s="22" t="str"/>
+      <x:c r="T25" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="18" customHeight="1">
+      <x:c r="A26" s="22" t="str">
+        <x:v>0x4394271f0fa7b20b4a2378269b1ef99ddd4ed543</x:v>
+      </x:c>
+      <x:c r="B26" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C26" s="22" t="str">
+        <x:v>contracts/0x4394271f0fa7b20b4a2378269b1ef99ddd4ed543</x:v>
+      </x:c>
+      <x:c r="D26" s="22" t="str">
+        <x:v>contracts/0x4394271f0fa7b20b4a2378269b1ef99ddd4ed543/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E26" s="22" t="str">
+        <x:v>96acce99823b437d80be0cc9c24c1041cdae76f338cee37ffefcce041cd8df19</x:v>
+      </x:c>
+      <x:c r="F26" s="20" t="n">
+        <x:v>10086</x:v>
+      </x:c>
+      <x:c r="G26" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I26" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J26" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K26" s="22" t="str"/>
+      <x:c r="L26" s="22" t="str"/>
+      <x:c r="M26" s="22" t="str"/>
+      <x:c r="N26" s="22" t="str"/>
+      <x:c r="O26" s="22" t="str"/>
+      <x:c r="P26" s="22" t="str"/>
+      <x:c r="Q26" s="22" t="str"/>
+      <x:c r="R26" s="22" t="str">
+        <x:v>contracts/0x4394271f0fa7b20b4a2378269b1ef99ddd4ed543/verification.json</x:v>
+      </x:c>
+      <x:c r="S26" s="22" t="str"/>
+      <x:c r="T26" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="18" customHeight="1">
+      <x:c r="A27" s="22" t="str">
+        <x:v>0x43cfeaa64013071d5505acf98b137f74c8ccd423</x:v>
+      </x:c>
+      <x:c r="B27" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C27" s="22" t="str">
+        <x:v>contracts/0x43cfeaa64013071d5505acf98b137f74c8ccd423</x:v>
+      </x:c>
+      <x:c r="D27" s="22" t="str">
+        <x:v>contracts/0x43cfeaa64013071d5505acf98b137f74c8ccd423/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E27" s="22" t="str">
+        <x:v>8761e354790a2dceafe50fcab6a6e1bab794a6e8474c91db97ecd9652a64fd3f</x:v>
+      </x:c>
+      <x:c r="F27" s="20" t="n">
+        <x:v>22911</x:v>
+      </x:c>
+      <x:c r="G27" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H27" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I27" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J27" s="20" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K27" s="22" t="str">
+        <x:v>RibbonThetaVault</x:v>
+      </x:c>
+      <x:c r="L27" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M27" s="22" t="str">
+        <x:v>0.7.3+commit.9bfce1f6</x:v>
+      </x:c>
+      <x:c r="N27" s="22" t="str">
+        <x:v>contracts/0x43cfeaa64013071d5505acf98b137f74c8ccd423/abi.json</x:v>
+      </x:c>
+      <x:c r="O27" s="22" t="str">
+        <x:v>contracts/0x43cfeaa64013071d5505acf98b137f74c8ccd423/metadata.json</x:v>
+      </x:c>
+      <x:c r="P27" s="22" t="str">
+        <x:v>contracts/0x43cfeaa64013071d5505acf98b137f74c8ccd423/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q27" s="22" t="str">
+        <x:v>contracts/0x43cfeaa64013071d5505acf98b137f74c8ccd423/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R27" s="22" t="str">
+        <x:v>contracts/0x43cfeaa64013071d5505acf98b137f74c8ccd423/verification.json</x:v>
+      </x:c>
+      <x:c r="S27" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x43cfeaa64013071d5505acf98b137f74c8ccd423?fields=all</x:v>
+      </x:c>
+      <x:c r="T27" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="18" customHeight="1">
+      <x:c r="A28" s="22" t="str">
+        <x:v>0x4794387af607b5eb8d65d0ad044d60033c2f1196</x:v>
+      </x:c>
+      <x:c r="B28" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C28" s="22" t="str">
+        <x:v>contracts/0x4794387af607b5eb8d65d0ad044d60033c2f1196</x:v>
+      </x:c>
+      <x:c r="D28" s="22" t="str">
+        <x:v>contracts/0x4794387af607b5eb8d65d0ad044d60033c2f1196/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E28" s="22" t="str">
+        <x:v>4eb19f8c989b6b1f8fd092922eb416afafc9aba0358f276b2b9157ae512a8bf1</x:v>
+      </x:c>
+      <x:c r="F28" s="20" t="n">
+        <x:v>21677</x:v>
+      </x:c>
+      <x:c r="G28" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H28" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I28" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J28" s="20" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K28" s="22" t="str">
+        <x:v>CurveBTCPlus</x:v>
+      </x:c>
+      <x:c r="L28" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M28" s="22" t="str">
+        <x:v>0.8.0+commit.c7dfd78e</x:v>
+      </x:c>
+      <x:c r="N28" s="22" t="str">
+        <x:v>contracts/0x4794387af607b5eb8d65d0ad044d60033c2f1196/abi.json</x:v>
+      </x:c>
+      <x:c r="O28" s="22" t="str">
+        <x:v>contracts/0x4794387af607b5eb8d65d0ad044d60033c2f1196/metadata.json</x:v>
+      </x:c>
+      <x:c r="P28" s="22" t="str">
+        <x:v>contracts/0x4794387af607b5eb8d65d0ad044d60033c2f1196/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q28" s="22" t="str">
+        <x:v>contracts/0x4794387af607b5eb8d65d0ad044d60033c2f1196/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R28" s="22" t="str">
+        <x:v>contracts/0x4794387af607b5eb8d65d0ad044d60033c2f1196/verification.json</x:v>
+      </x:c>
+      <x:c r="S28" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x4794387af607b5eb8d65d0ad044d60033c2f1196?fields=all</x:v>
+      </x:c>
+      <x:c r="T28" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="18" customHeight="1">
+      <x:c r="A29" s="22" t="str">
+        <x:v>0x49d82927e32138d8d6cedea634231443ee26e00e</x:v>
+      </x:c>
+      <x:c r="B29" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C29" s="22" t="str">
+        <x:v>contracts/0x49d82927e32138d8d6cedea634231443ee26e00e</x:v>
+      </x:c>
+      <x:c r="D29" s="22" t="str">
+        <x:v>contracts/0x49d82927e32138d8d6cedea634231443ee26e00e/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E29" s="22" t="str">
+        <x:v>dc43c0f2b51d497248db0995388b2ef669e38dee3b40d7264f2983b648ce9c88</x:v>
+      </x:c>
+      <x:c r="F29" s="20" t="n">
+        <x:v>9452</x:v>
+      </x:c>
+      <x:c r="G29" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H29" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I29" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J29" s="20" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K29" s="22" t="str">
+        <x:v>QuirklingsImplementationV2</x:v>
+      </x:c>
+      <x:c r="L29" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M29" s="22" t="str">
+        <x:v>0.8.17+commit.8df45f5f</x:v>
+      </x:c>
+      <x:c r="N29" s="22" t="str">
+        <x:v>contracts/0x49d82927e32138d8d6cedea634231443ee26e00e/abi.json</x:v>
+      </x:c>
+      <x:c r="O29" s="22" t="str">
+        <x:v>contracts/0x49d82927e32138d8d6cedea634231443ee26e00e/metadata.json</x:v>
+      </x:c>
+      <x:c r="P29" s="22" t="str">
+        <x:v>contracts/0x49d82927e32138d8d6cedea634231443ee26e00e/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q29" s="22" t="str">
+        <x:v>contracts/0x49d82927e32138d8d6cedea634231443ee26e00e/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R29" s="22" t="str">
+        <x:v>contracts/0x49d82927e32138d8d6cedea634231443ee26e00e/verification.json</x:v>
+      </x:c>
+      <x:c r="S29" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x49d82927e32138d8d6cedea634231443ee26e00e?fields=all</x:v>
+      </x:c>
+      <x:c r="T29" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="18" customHeight="1">
+      <x:c r="A30" s="22" t="str">
+        <x:v>0x514aabfe54f63d5dc4719d2d26ae9895a1b6350d</x:v>
+      </x:c>
+      <x:c r="B30" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C30" s="22" t="str">
+        <x:v>contracts/0x514aabfe54f63d5dc4719d2d26ae9895a1b6350d</x:v>
+      </x:c>
+      <x:c r="D30" s="22" t="str">
+        <x:v>contracts/0x514aabfe54f63d5dc4719d2d26ae9895a1b6350d/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E30" s="22" t="str">
+        <x:v>3b8c333954da96a4caa5ed6bd32ad17490614e7550c9ad9adce96a549559be17</x:v>
+      </x:c>
+      <x:c r="F30" s="20" t="n">
+        <x:v>20274</x:v>
+      </x:c>
+      <x:c r="G30" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H30" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I30" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J30" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K30" s="22" t="str"/>
+      <x:c r="L30" s="22" t="str"/>
+      <x:c r="M30" s="22" t="str"/>
+      <x:c r="N30" s="22" t="str"/>
+      <x:c r="O30" s="22" t="str"/>
+      <x:c r="P30" s="22" t="str"/>
+      <x:c r="Q30" s="22" t="str"/>
+      <x:c r="R30" s="22" t="str">
+        <x:v>contracts/0x514aabfe54f63d5dc4719d2d26ae9895a1b6350d/verification.json</x:v>
+      </x:c>
+      <x:c r="S30" s="22" t="str"/>
+      <x:c r="T30" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="18" customHeight="1">
+      <x:c r="A31" s="22" t="str">
+        <x:v>0x535640946c6f47806faf036f14d23e85a42c5544</x:v>
+      </x:c>
+      <x:c r="B31" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C31" s="22" t="str">
+        <x:v>contracts/0x535640946c6f47806faf036f14d23e85a42c5544</x:v>
+      </x:c>
+      <x:c r="D31" s="22" t="str">
+        <x:v>contracts/0x535640946c6f47806faf036f14d23e85a42c5544/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E31" s="22" t="str">
+        <x:v>cc126d154b32ceb9c242b6f807f4a826ec95b2c40bfc2ca37fc57c17c90d64d1</x:v>
+      </x:c>
+      <x:c r="F31" s="20" t="n">
+        <x:v>10570</x:v>
+      </x:c>
+      <x:c r="G31" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H31" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I31" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J31" s="20" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K31" s="22" t="str">
+        <x:v>ENSAvatarMirror</x:v>
+      </x:c>
+      <x:c r="L31" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M31" s="22" t="str">
+        <x:v>0.8.17+commit.8df45f5f</x:v>
+      </x:c>
+      <x:c r="N31" s="22" t="str">
+        <x:v>contracts/0x535640946c6f47806faf036f14d23e85a42c5544/abi.json</x:v>
+      </x:c>
+      <x:c r="O31" s="22" t="str">
+        <x:v>contracts/0x535640946c6f47806faf036f14d23e85a42c5544/metadata.json</x:v>
+      </x:c>
+      <x:c r="P31" s="22" t="str">
+        <x:v>contracts/0x535640946c6f47806faf036f14d23e85a42c5544/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q31" s="22" t="str">
+        <x:v>contracts/0x535640946c6f47806faf036f14d23e85a42c5544/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R31" s="22" t="str">
+        <x:v>contracts/0x535640946c6f47806faf036f14d23e85a42c5544/verification.json</x:v>
+      </x:c>
+      <x:c r="S31" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x535640946c6f47806faf036f14d23e85a42c5544?fields=all</x:v>
+      </x:c>
+      <x:c r="T31" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="18" customHeight="1">
+      <x:c r="A32" s="22" t="str">
+        <x:v>0x55429d416d5b2909454cbdce542fc1577f2d2acd</x:v>
+      </x:c>
+      <x:c r="B32" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C32" s="22" t="str">
+        <x:v>contracts/0x55429d416d5b2909454cbdce542fc1577f2d2acd</x:v>
+      </x:c>
+      <x:c r="D32" s="22" t="str">
+        <x:v>contracts/0x55429d416d5b2909454cbdce542fc1577f2d2acd/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E32" s="22" t="str">
+        <x:v>138b45e27568ac06d3b8ee6ede9c31ef093f53d3d824ef8d237790eef2f61280</x:v>
+      </x:c>
+      <x:c r="F32" s="20" t="n">
+        <x:v>9197</x:v>
+      </x:c>
+      <x:c r="G32" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H32" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I32" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J32" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K32" s="22" t="str"/>
+      <x:c r="L32" s="22" t="str"/>
+      <x:c r="M32" s="22" t="str"/>
+      <x:c r="N32" s="22" t="str"/>
+      <x:c r="O32" s="22" t="str"/>
+      <x:c r="P32" s="22" t="str"/>
+      <x:c r="Q32" s="22" t="str"/>
+      <x:c r="R32" s="22" t="str">
+        <x:v>contracts/0x55429d416d5b2909454cbdce542fc1577f2d2acd/verification.json</x:v>
+      </x:c>
+      <x:c r="S32" s="22" t="str"/>
+      <x:c r="T32" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="18" customHeight="1">
+      <x:c r="A33" s="22" t="str">
+        <x:v>0x5a48866c0faa3947838bd945e85d550d94530ee7</x:v>
+      </x:c>
+      <x:c r="B33" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C33" s="22" t="str">
+        <x:v>contracts/0x5a48866c0faa3947838bd945e85d550d94530ee7</x:v>
+      </x:c>
+      <x:c r="D33" s="22" t="str">
+        <x:v>contracts/0x5a48866c0faa3947838bd945e85d550d94530ee7/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E33" s="22" t="str">
+        <x:v>6417b8cfb297bd350f33cbffbaee9cc6bb3db506818d255ee5139a6c4064cc86</x:v>
+      </x:c>
+      <x:c r="F33" s="20" t="n">
+        <x:v>3929</x:v>
+      </x:c>
+      <x:c r="G33" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H33" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I33" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J33" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K33" s="22" t="str">
+        <x:v>ShareholderVomer</x:v>
+      </x:c>
+      <x:c r="L33" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M33" s="22" t="str">
+        <x:v>0.5.17+commit.d19bba13</x:v>
+      </x:c>
+      <x:c r="N33" s="22" t="str">
+        <x:v>contracts/0x5a48866c0faa3947838bd945e85d550d94530ee7/abi.json</x:v>
+      </x:c>
+      <x:c r="O33" s="22" t="str">
+        <x:v>contracts/0x5a48866c0faa3947838bd945e85d550d94530ee7/metadata.json</x:v>
+      </x:c>
+      <x:c r="P33" s="22" t="str">
+        <x:v>contracts/0x5a48866c0faa3947838bd945e85d550d94530ee7/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q33" s="22" t="str">
+        <x:v>contracts/0x5a48866c0faa3947838bd945e85d550d94530ee7/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R33" s="22" t="str">
+        <x:v>contracts/0x5a48866c0faa3947838bd945e85d550d94530ee7/verification.json</x:v>
+      </x:c>
+      <x:c r="S33" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x5a48866c0faa3947838bd945e85d550d94530ee7?fields=all</x:v>
+      </x:c>
+      <x:c r="T33" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="18" customHeight="1">
+      <x:c r="A34" s="22" t="str">
+        <x:v>0x5bfe46a07ce43644e590ad50d1cd0edd23951538</x:v>
+      </x:c>
+      <x:c r="B34" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C34" s="22" t="str">
+        <x:v>contracts/0x5bfe46a07ce43644e590ad50d1cd0edd23951538</x:v>
+      </x:c>
+      <x:c r="D34" s="22" t="str">
+        <x:v>contracts/0x5bfe46a07ce43644e590ad50d1cd0edd23951538/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E34" s="22" t="str">
+        <x:v>d81a72901cdf4043a17ed8a5d5d43e6ae97083c6839e088bf7a8e3853ca94d9c</x:v>
+      </x:c>
+      <x:c r="F34" s="20" t="n">
+        <x:v>16193</x:v>
+      </x:c>
+      <x:c r="G34" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H34" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I34" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J34" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K34" s="22" t="str">
+        <x:v>EdgeTokenConstructorUpgrade</x:v>
+      </x:c>
+      <x:c r="L34" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M34" s="22" t="str">
+        <x:v>0.5.0+commit.1d4f565a</x:v>
+      </x:c>
+      <x:c r="N34" s="22" t="str">
+        <x:v>contracts/0x5bfe46a07ce43644e590ad50d1cd0edd23951538/abi.json</x:v>
+      </x:c>
+      <x:c r="O34" s="22" t="str">
+        <x:v>contracts/0x5bfe46a07ce43644e590ad50d1cd0edd23951538/metadata.json</x:v>
+      </x:c>
+      <x:c r="P34" s="22" t="str">
+        <x:v>contracts/0x5bfe46a07ce43644e590ad50d1cd0edd23951538/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q34" s="22" t="str"/>
+      <x:c r="R34" s="22" t="str">
+        <x:v>contracts/0x5bfe46a07ce43644e590ad50d1cd0edd23951538/verification.json</x:v>
+      </x:c>
+      <x:c r="S34" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x5bfe46a07ce43644e590ad50d1cd0edd23951538?fields=all</x:v>
+      </x:c>
+      <x:c r="T34" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="18" customHeight="1">
+      <x:c r="A35" s="22" t="str">
+        <x:v>0x5dba7dfcdbfb8812d30fdd99d9441f8b7a605621</x:v>
+      </x:c>
+      <x:c r="B35" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C35" s="22" t="str">
+        <x:v>contracts/0x5dba7dfcdbfb8812d30fdd99d9441f8b7a605621</x:v>
+      </x:c>
+      <x:c r="D35" s="22" t="str">
+        <x:v>contracts/0x5dba7dfcdbfb8812d30fdd99d9441f8b7a605621/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E35" s="22" t="str">
+        <x:v>c3c3e0bdb6f52cae35d2e69d4e0d042ab5d1fc55c045ad8c5f3b4732ea9a6fba</x:v>
+      </x:c>
+      <x:c r="F35" s="20" t="n">
+        <x:v>14228</x:v>
+      </x:c>
+      <x:c r="G35" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H35" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I35" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J35" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K35" s="22" t="str">
+        <x:v>OKBImplementation</x:v>
+      </x:c>
+      <x:c r="L35" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M35" s="22" t="str">
+        <x:v>0.4.24+commit.e67f0147</x:v>
+      </x:c>
+      <x:c r="N35" s="22" t="str">
+        <x:v>contracts/0x5dba7dfcdbfb8812d30fdd99d9441f8b7a605621/abi.json</x:v>
+      </x:c>
+      <x:c r="O35" s="22" t="str">
+        <x:v>contracts/0x5dba7dfcdbfb8812d30fdd99d9441f8b7a605621/metadata.json</x:v>
+      </x:c>
+      <x:c r="P35" s="22" t="str">
+        <x:v>contracts/0x5dba7dfcdbfb8812d30fdd99d9441f8b7a605621/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q35" s="22" t="str"/>
+      <x:c r="R35" s="22" t="str">
+        <x:v>contracts/0x5dba7dfcdbfb8812d30fdd99d9441f8b7a605621/verification.json</x:v>
+      </x:c>
+      <x:c r="S35" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x5dba7dfcdbfb8812d30fdd99d9441f8b7a605621?fields=all</x:v>
+      </x:c>
+      <x:c r="T35" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="18" customHeight="1">
+      <x:c r="A36" s="22" t="str">
+        <x:v>0x5eb5babcefea846b220c82f222f00df95934f5f0</x:v>
+      </x:c>
+      <x:c r="B36" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C36" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0</x:v>
+      </x:c>
+      <x:c r="D36" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E36" s="22" t="str">
+        <x:v>6a1b7f749b21e2e90ad971d8988746fcde9e50f955ee8ba11f8d6461f2d0658d</x:v>
+      </x:c>
+      <x:c r="F36" s="20" t="n">
+        <x:v>24493</x:v>
+      </x:c>
+      <x:c r="G36" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H36" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I36" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J36" s="20" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="K36" s="22" t="str">
+        <x:v>ERC721Drop</x:v>
+      </x:c>
+      <x:c r="L36" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M36" s="22" t="str">
+        <x:v>0.8.17+commit.8df45f5f</x:v>
+      </x:c>
+      <x:c r="N36" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0/abi.json</x:v>
+      </x:c>
+      <x:c r="O36" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0/metadata.json</x:v>
+      </x:c>
+      <x:c r="P36" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q36" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R36" s="22" t="str">
+        <x:v>contracts/0x5eb5babcefea846b220c82f222f00df95934f5f0/verification.json</x:v>
+      </x:c>
+      <x:c r="S36" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x5eb5babcefea846b220c82f222f00df95934f5f0?fields=all</x:v>
+      </x:c>
+      <x:c r="T36" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="18" customHeight="1">
+      <x:c r="A37" s="22" t="str">
+        <x:v>0x62e269cfd1951498d93db8be9003c3f454a126f9</x:v>
+      </x:c>
+      <x:c r="B37" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C37" s="22" t="str">
+        <x:v>contracts/0x62e269cfd1951498d93db8be9003c3f454a126f9</x:v>
+      </x:c>
+      <x:c r="D37" s="22" t="str">
+        <x:v>contracts/0x62e269cfd1951498d93db8be9003c3f454a126f9/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E37" s="22" t="str">
+        <x:v>c85abbf1f71007e393059a73164a5871d732621f4ea31578d819527349d95fcd</x:v>
+      </x:c>
+      <x:c r="F37" s="20" t="n">
+        <x:v>9809</x:v>
+      </x:c>
+      <x:c r="G37" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H37" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I37" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J37" s="20" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K37" s="22" t="str">
+        <x:v>BibizStakeUpgradeable</x:v>
+      </x:c>
+      <x:c r="L37" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M37" s="22" t="str">
+        <x:v>0.8.13+commit.abaa5c0e</x:v>
+      </x:c>
+      <x:c r="N37" s="22" t="str">
+        <x:v>contracts/0x62e269cfd1951498d93db8be9003c3f454a126f9/abi.json</x:v>
+      </x:c>
+      <x:c r="O37" s="22" t="str">
+        <x:v>contracts/0x62e269cfd1951498d93db8be9003c3f454a126f9/metadata.json</x:v>
+      </x:c>
+      <x:c r="P37" s="22" t="str">
+        <x:v>contracts/0x62e269cfd1951498d93db8be9003c3f454a126f9/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q37" s="22" t="str">
+        <x:v>contracts/0x62e269cfd1951498d93db8be9003c3f454a126f9/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R37" s="22" t="str">
+        <x:v>contracts/0x62e269cfd1951498d93db8be9003c3f454a126f9/verification.json</x:v>
+      </x:c>
+      <x:c r="S37" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x62e269cfd1951498d93db8be9003c3f454a126f9?fields=all</x:v>
+      </x:c>
+      <x:c r="T37" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="18" customHeight="1">
+      <x:c r="A38" s="22" t="str">
+        <x:v>0x6564fe0809e8b520a0e26ee644d98c4ea2c6fb45</x:v>
+      </x:c>
+      <x:c r="B38" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C38" s="22" t="str">
+        <x:v>contracts/0x6564fe0809e8b520a0e26ee644d98c4ea2c6fb45</x:v>
+      </x:c>
+      <x:c r="D38" s="22" t="str">
+        <x:v>contracts/0x6564fe0809e8b520a0e26ee644d98c4ea2c6fb45/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E38" s="22" t="str">
+        <x:v>959375847291ac4d49306b512acad984d4ee429c03c5ef15d6e20db1b2b289d2</x:v>
+      </x:c>
+      <x:c r="F38" s="20" t="n">
+        <x:v>6998</x:v>
+      </x:c>
+      <x:c r="G38" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H38" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I38" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J38" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K38" s="22" t="str">
+        <x:v>OperatorVault</x:v>
+      </x:c>
+      <x:c r="L38" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M38" s="22" t="str">
+        <x:v>0.8.15+commit.e14f2714</x:v>
+      </x:c>
+      <x:c r="N38" s="22" t="str">
+        <x:v>contracts/0x6564fe0809e8b520a0e26ee644d98c4ea2c6fb45/abi.json</x:v>
+      </x:c>
+      <x:c r="O38" s="22" t="str">
+        <x:v>contracts/0x6564fe0809e8b520a0e26ee644d98c4ea2c6fb45/metadata.json</x:v>
+      </x:c>
+      <x:c r="P38" s="22" t="str">
+        <x:v>contracts/0x6564fe0809e8b520a0e26ee644d98c4ea2c6fb45/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q38" s="22" t="str">
+        <x:v>contracts/0x6564fe0809e8b520a0e26ee644d98c4ea2c6fb45/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R38" s="22" t="str">
+        <x:v>contracts/0x6564fe0809e8b520a0e26ee644d98c4ea2c6fb45/verification.json</x:v>
+      </x:c>
+      <x:c r="S38" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x6564fe0809e8b520a0e26ee644d98c4ea2c6fb45?fields=all</x:v>
+      </x:c>
+      <x:c r="T38" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="18" customHeight="1">
+      <x:c r="A39" s="22" t="str">
+        <x:v>0x67d6897ec4e903e4163649ac064ae1020635e379</x:v>
+      </x:c>
+      <x:c r="B39" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C39" s="22" t="str">
+        <x:v>contracts/0x67d6897ec4e903e4163649ac064ae1020635e379</x:v>
+      </x:c>
+      <x:c r="D39" s="22" t="str">
+        <x:v>contracts/0x67d6897ec4e903e4163649ac064ae1020635e379/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E39" s="22" t="str">
+        <x:v>118560776779d79e5de2d2ed1ee07f858c9bb5508be3d626d7a9ecfa9f8d1bb6</x:v>
+      </x:c>
+      <x:c r="F39" s="20" t="n">
+        <x:v>2905</x:v>
+      </x:c>
+      <x:c r="G39" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H39" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I39" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J39" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K39" s="22" t="str"/>
+      <x:c r="L39" s="22" t="str"/>
+      <x:c r="M39" s="22" t="str"/>
+      <x:c r="N39" s="22" t="str"/>
+      <x:c r="O39" s="22" t="str"/>
+      <x:c r="P39" s="22" t="str"/>
+      <x:c r="Q39" s="22" t="str"/>
+      <x:c r="R39" s="22" t="str">
+        <x:v>contracts/0x67d6897ec4e903e4163649ac064ae1020635e379/verification.json</x:v>
+      </x:c>
+      <x:c r="S39" s="22" t="str"/>
+      <x:c r="T39" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="18" customHeight="1">
+      <x:c r="A40" s="22" t="str">
+        <x:v>0x72a3409af79fb55c7612304b7ce3e56731ab615d</x:v>
+      </x:c>
+      <x:c r="B40" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C40" s="22" t="str">
+        <x:v>contracts/0x72a3409af79fb55c7612304b7ce3e56731ab615d</x:v>
+      </x:c>
+      <x:c r="D40" s="22" t="str">
+        <x:v>contracts/0x72a3409af79fb55c7612304b7ce3e56731ab615d/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E40" s="22" t="str">
+        <x:v>772de4867a745cf96b190e47a67e8e7e534689c72f62fa3c1b417ba327839b15</x:v>
+      </x:c>
+      <x:c r="F40" s="20" t="n">
+        <x:v>13481</x:v>
+      </x:c>
+      <x:c r="G40" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H40" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I40" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J40" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K40" s="22" t="str"/>
+      <x:c r="L40" s="22" t="str"/>
+      <x:c r="M40" s="22" t="str"/>
+      <x:c r="N40" s="22" t="str"/>
+      <x:c r="O40" s="22" t="str"/>
+      <x:c r="P40" s="22" t="str"/>
+      <x:c r="Q40" s="22" t="str"/>
+      <x:c r="R40" s="22" t="str">
+        <x:v>contracts/0x72a3409af79fb55c7612304b7ce3e56731ab615d/verification.json</x:v>
+      </x:c>
+      <x:c r="S40" s="22" t="str"/>
+      <x:c r="T40" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="18" customHeight="1">
+      <x:c r="A41" s="22" t="str">
+        <x:v>0x76e28a61d9bd58c5ec598a6bc25d8279aea8d2cf</x:v>
+      </x:c>
+      <x:c r="B41" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C41" s="22" t="str">
+        <x:v>contracts/0x76e28a61d9bd58c5ec598a6bc25d8279aea8d2cf</x:v>
+      </x:c>
+      <x:c r="D41" s="22" t="str">
+        <x:v>contracts/0x76e28a61d9bd58c5ec598a6bc25d8279aea8d2cf/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E41" s="22" t="str">
+        <x:v>853c944c49743d21e8cb2599f1e8fa84fd0b48140507e594d1e300a3b76f8ffa</x:v>
+      </x:c>
+      <x:c r="F41" s="20" t="n">
+        <x:v>16358</x:v>
+      </x:c>
+      <x:c r="G41" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H41" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I41" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J41" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K41" s="22" t="str">
+        <x:v>TrueFiPool</x:v>
+      </x:c>
+      <x:c r="L41" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M41" s="22" t="str">
+        <x:v>0.6.10+commit.00c0fcaf</x:v>
+      </x:c>
+      <x:c r="N41" s="22" t="str">
+        <x:v>contracts/0x76e28a61d9bd58c5ec598a6bc25d8279aea8d2cf/abi.json</x:v>
+      </x:c>
+      <x:c r="O41" s="22" t="str">
+        <x:v>contracts/0x76e28a61d9bd58c5ec598a6bc25d8279aea8d2cf/metadata.json</x:v>
+      </x:c>
+      <x:c r="P41" s="22" t="str">
+        <x:v>contracts/0x76e28a61d9bd58c5ec598a6bc25d8279aea8d2cf/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q41" s="22" t="str">
+        <x:v>contracts/0x76e28a61d9bd58c5ec598a6bc25d8279aea8d2cf/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R41" s="22" t="str">
+        <x:v>contracts/0x76e28a61d9bd58c5ec598a6bc25d8279aea8d2cf/verification.json</x:v>
+      </x:c>
+      <x:c r="S41" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x76e28a61d9bd58c5ec598a6bc25d8279aea8d2cf?fields=all</x:v>
+      </x:c>
+      <x:c r="T41" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="18" customHeight="1">
+      <x:c r="A42" s="22" t="str">
+        <x:v>0x77521046edd9eb81cffecf55f3aec9bc000d05b2</x:v>
+      </x:c>
+      <x:c r="B42" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C42" s="22" t="str">
+        <x:v>contracts/0x77521046edd9eb81cffecf55f3aec9bc000d05b2</x:v>
+      </x:c>
+      <x:c r="D42" s="22" t="str">
+        <x:v>contracts/0x77521046edd9eb81cffecf55f3aec9bc000d05b2/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E42" s="22" t="str">
+        <x:v>d767b43b0f1b24ab5087745de335905dd3a4cc2430b32f9290844982e95ad15f</x:v>
+      </x:c>
+      <x:c r="F42" s="20" t="n">
+        <x:v>11970</x:v>
+      </x:c>
+      <x:c r="G42" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H42" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I42" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J42" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K42" s="22" t="str"/>
+      <x:c r="L42" s="22" t="str"/>
+      <x:c r="M42" s="22" t="str"/>
+      <x:c r="N42" s="22" t="str"/>
+      <x:c r="O42" s="22" t="str"/>
+      <x:c r="P42" s="22" t="str"/>
+      <x:c r="Q42" s="22" t="str"/>
+      <x:c r="R42" s="22" t="str">
+        <x:v>contracts/0x77521046edd9eb81cffecf55f3aec9bc000d05b2/verification.json</x:v>
+      </x:c>
+      <x:c r="S42" s="22" t="str"/>
+      <x:c r="T42" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="18" customHeight="1">
+      <x:c r="A43" s="22" t="str">
+        <x:v>0x7baad50a656c484330f9e9ae720798edcd739c83</x:v>
+      </x:c>
+      <x:c r="B43" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C43" s="22" t="str">
+        <x:v>contracts/0x7baad50a656c484330f9e9ae720798edcd739c83</x:v>
+      </x:c>
+      <x:c r="D43" s="22" t="str">
+        <x:v>contracts/0x7baad50a656c484330f9e9ae720798edcd739c83/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E43" s="22" t="str">
+        <x:v>0fe92e8aea127a4d9de01a89c4ed217557fd29dc74adfa87b1da751936a7bfa0</x:v>
+      </x:c>
+      <x:c r="F43" s="20" t="n">
+        <x:v>3851</x:v>
+      </x:c>
+      <x:c r="G43" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H43" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I43" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J43" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K43" s="22" t="str"/>
+      <x:c r="L43" s="22" t="str"/>
+      <x:c r="M43" s="22" t="str"/>
+      <x:c r="N43" s="22" t="str"/>
+      <x:c r="O43" s="22" t="str"/>
+      <x:c r="P43" s="22" t="str"/>
+      <x:c r="Q43" s="22" t="str"/>
+      <x:c r="R43" s="22" t="str">
+        <x:v>contracts/0x7baad50a656c484330f9e9ae720798edcd739c83/verification.json</x:v>
+      </x:c>
+      <x:c r="S43" s="22" t="str"/>
+      <x:c r="T43" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="18" customHeight="1">
+      <x:c r="A44" s="22" t="str">
+        <x:v>0x7f1d120750ca4154f0edb37efbf57982ff7a6a5e</x:v>
+      </x:c>
+      <x:c r="B44" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C44" s="22" t="str">
+        <x:v>contracts/0x7f1d120750ca4154f0edb37efbf57982ff7a6a5e</x:v>
+      </x:c>
+      <x:c r="D44" s="22" t="str">
+        <x:v>contracts/0x7f1d120750ca4154f0edb37efbf57982ff7a6a5e/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E44" s="22" t="str">
+        <x:v>cf0d78cce945aefe553064c6e16baa59900c4c213e5b9157cdf0511d8e6f9628</x:v>
+      </x:c>
+      <x:c r="F44" s="20" t="n">
+        <x:v>16880</x:v>
+      </x:c>
+      <x:c r="G44" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H44" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I44" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J44" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K44" s="22" t="str">
+        <x:v>OptionFactory</x:v>
+      </x:c>
+      <x:c r="L44" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M44" s="22" t="str">
+        <x:v>0.6.12+commit.27d51765</x:v>
+      </x:c>
+      <x:c r="N44" s="22" t="str">
+        <x:v>contracts/0x7f1d120750ca4154f0edb37efbf57982ff7a6a5e/abi.json</x:v>
+      </x:c>
+      <x:c r="O44" s="22" t="str">
+        <x:v>contracts/0x7f1d120750ca4154f0edb37efbf57982ff7a6a5e/metadata.json</x:v>
+      </x:c>
+      <x:c r="P44" s="22" t="str">
+        <x:v>contracts/0x7f1d120750ca4154f0edb37efbf57982ff7a6a5e/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q44" s="22" t="str">
+        <x:v>contracts/0x7f1d120750ca4154f0edb37efbf57982ff7a6a5e/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R44" s="22" t="str">
+        <x:v>contracts/0x7f1d120750ca4154f0edb37efbf57982ff7a6a5e/verification.json</x:v>
+      </x:c>
+      <x:c r="S44" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x7f1d120750ca4154f0edb37efbf57982ff7a6a5e?fields=all</x:v>
+      </x:c>
+      <x:c r="T44" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="18" customHeight="1">
+      <x:c r="A45" s="22" t="str">
+        <x:v>0x81e66a89696c65d4cb1c17cc477afd6be3348c9f</x:v>
+      </x:c>
+      <x:c r="B45" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C45" s="22" t="str">
+        <x:v>contracts/0x81e66a89696c65d4cb1c17cc477afd6be3348c9f</x:v>
+      </x:c>
+      <x:c r="D45" s="22" t="str">
+        <x:v>contracts/0x81e66a89696c65d4cb1c17cc477afd6be3348c9f/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E45" s="22" t="str">
+        <x:v>19279e531c3d5584444bbddd9af48055d2a8b31c6c7a212cb5327de4ca0c5432</x:v>
+      </x:c>
+      <x:c r="F45" s="20" t="n">
+        <x:v>1305</x:v>
+      </x:c>
+      <x:c r="G45" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H45" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I45" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J45" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K45" s="22" t="str"/>
+      <x:c r="L45" s="22" t="str"/>
+      <x:c r="M45" s="22" t="str"/>
+      <x:c r="N45" s="22" t="str"/>
+      <x:c r="O45" s="22" t="str"/>
+      <x:c r="P45" s="22" t="str"/>
+      <x:c r="Q45" s="22" t="str"/>
+      <x:c r="R45" s="22" t="str">
+        <x:v>contracts/0x81e66a89696c65d4cb1c17cc477afd6be3348c9f/verification.json</x:v>
+      </x:c>
+      <x:c r="S45" s="22" t="str"/>
+      <x:c r="T45" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="18" customHeight="1">
+      <x:c r="A46" s="22" t="str">
+        <x:v>0x8342c92235d044aadebd3c4de858e26696b8a602</x:v>
+      </x:c>
+      <x:c r="B46" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C46" s="22" t="str">
+        <x:v>contracts/0x8342c92235d044aadebd3c4de858e26696b8a602</x:v>
+      </x:c>
+      <x:c r="D46" s="22" t="str">
+        <x:v>contracts/0x8342c92235d044aadebd3c4de858e26696b8a602/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E46" s="22" t="str">
+        <x:v>4e73a98645973afedb2cbcd7d7384bead286a3342c8d8bee989987c0b44c3a17</x:v>
+      </x:c>
+      <x:c r="F46" s="20" t="n">
+        <x:v>16590</x:v>
+      </x:c>
+      <x:c r="G46" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H46" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I46" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J46" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K46" s="22" t="str"/>
+      <x:c r="L46" s="22" t="str"/>
+      <x:c r="M46" s="22" t="str"/>
+      <x:c r="N46" s="22" t="str"/>
+      <x:c r="O46" s="22" t="str"/>
+      <x:c r="P46" s="22" t="str"/>
+      <x:c r="Q46" s="22" t="str"/>
+      <x:c r="R46" s="22" t="str">
+        <x:v>contracts/0x8342c92235d044aadebd3c4de858e26696b8a602/verification.json</x:v>
+      </x:c>
+      <x:c r="S46" s="22" t="str"/>
+      <x:c r="T46" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="18" customHeight="1">
+      <x:c r="A47" s="22" t="str">
+        <x:v>0x8b5c19cdb8afb458bbb3ce53bf1ef1754df09b88</x:v>
+      </x:c>
+      <x:c r="B47" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C47" s="22" t="str">
+        <x:v>contracts/0x8b5c19cdb8afb458bbb3ce53bf1ef1754df09b88</x:v>
+      </x:c>
+      <x:c r="D47" s="22" t="str">
+        <x:v>contracts/0x8b5c19cdb8afb458bbb3ce53bf1ef1754df09b88/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E47" s="22" t="str">
+        <x:v>203a60b87444d9baab66478dc8c6909188fc1b0429e3025d3925dbf400a8b288</x:v>
+      </x:c>
+      <x:c r="F47" s="20" t="n">
+        <x:v>16642</x:v>
+      </x:c>
+      <x:c r="G47" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H47" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I47" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J47" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K47" s="22" t="str">
+        <x:v>EGT</x:v>
+      </x:c>
+      <x:c r="L47" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M47" s="22" t="str">
+        <x:v>0.8.12+commit.f00d7308</x:v>
+      </x:c>
+      <x:c r="N47" s="22" t="str">
+        <x:v>contracts/0x8b5c19cdb8afb458bbb3ce53bf1ef1754df09b88/abi.json</x:v>
+      </x:c>
+      <x:c r="O47" s="22" t="str">
+        <x:v>contracts/0x8b5c19cdb8afb458bbb3ce53bf1ef1754df09b88/metadata.json</x:v>
+      </x:c>
+      <x:c r="P47" s="22" t="str">
+        <x:v>contracts/0x8b5c19cdb8afb458bbb3ce53bf1ef1754df09b88/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q47" s="22" t="str">
+        <x:v>contracts/0x8b5c19cdb8afb458bbb3ce53bf1ef1754df09b88/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R47" s="22" t="str">
+        <x:v>contracts/0x8b5c19cdb8afb458bbb3ce53bf1ef1754df09b88/verification.json</x:v>
+      </x:c>
+      <x:c r="S47" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x8b5c19cdb8afb458bbb3ce53bf1ef1754df09b88?fields=all</x:v>
+      </x:c>
+      <x:c r="T47" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="18" customHeight="1">
+      <x:c r="A48" s="22" t="str">
+        <x:v>0x8c1bb096b14cf48ab46a1fe7c8e0c57053ea4519</x:v>
+      </x:c>
+      <x:c r="B48" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C48" s="22" t="str">
+        <x:v>contracts/0x8c1bb096b14cf48ab46a1fe7c8e0c57053ea4519</x:v>
+      </x:c>
+      <x:c r="D48" s="22" t="str">
+        <x:v>contracts/0x8c1bb096b14cf48ab46a1fe7c8e0c57053ea4519/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E48" s="22" t="str">
+        <x:v>a9585cc32a70fddb13d3b2bd043fd3c9d1fd26d422c6e485634f24f2451dd2a6</x:v>
+      </x:c>
+      <x:c r="F48" s="20" t="n">
+        <x:v>17650</x:v>
+      </x:c>
+      <x:c r="G48" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H48" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I48" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J48" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K48" s="22" t="str">
+        <x:v>Sales721ForEth</x:v>
+      </x:c>
+      <x:c r="L48" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M48" s="22" t="str">
+        <x:v>0.6.12+commit.27d51765</x:v>
+      </x:c>
+      <x:c r="N48" s="22" t="str">
+        <x:v>contracts/0x8c1bb096b14cf48ab46a1fe7c8e0c57053ea4519/abi.json</x:v>
+      </x:c>
+      <x:c r="O48" s="22" t="str">
+        <x:v>contracts/0x8c1bb096b14cf48ab46a1fe7c8e0c57053ea4519/metadata.json</x:v>
+      </x:c>
+      <x:c r="P48" s="22" t="str">
+        <x:v>contracts/0x8c1bb096b14cf48ab46a1fe7c8e0c57053ea4519/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q48" s="22" t="str">
+        <x:v>contracts/0x8c1bb096b14cf48ab46a1fe7c8e0c57053ea4519/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R48" s="22" t="str">
+        <x:v>contracts/0x8c1bb096b14cf48ab46a1fe7c8e0c57053ea4519/verification.json</x:v>
+      </x:c>
+      <x:c r="S48" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x8c1bb096b14cf48ab46a1fe7c8e0c57053ea4519?fields=all</x:v>
+      </x:c>
+      <x:c r="T48" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="18" customHeight="1">
+      <x:c r="A49" s="22" t="str">
+        <x:v>0x8ee68e86e9f4b7c167e20b198638bec8c46059c2</x:v>
+      </x:c>
+      <x:c r="B49" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C49" s="22" t="str">
+        <x:v>contracts/0x8ee68e86e9f4b7c167e20b198638bec8c46059c2</x:v>
+      </x:c>
+      <x:c r="D49" s="22" t="str">
+        <x:v>contracts/0x8ee68e86e9f4b7c167e20b198638bec8c46059c2/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E49" s="22" t="str">
+        <x:v>09a5f0e2b744bf40c93ebeb04f9afb565208db2a990d46d6ff2618051cba9af8</x:v>
+      </x:c>
+      <x:c r="F49" s="20" t="n">
+        <x:v>9437</x:v>
+      </x:c>
+      <x:c r="G49" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H49" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I49" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J49" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K49" s="22" t="str"/>
+      <x:c r="L49" s="22" t="str"/>
+      <x:c r="M49" s="22" t="str"/>
+      <x:c r="N49" s="22" t="str"/>
+      <x:c r="O49" s="22" t="str"/>
+      <x:c r="P49" s="22" t="str"/>
+      <x:c r="Q49" s="22" t="str"/>
+      <x:c r="R49" s="22" t="str">
+        <x:v>contracts/0x8ee68e86e9f4b7c167e20b198638bec8c46059c2/verification.json</x:v>
+      </x:c>
+      <x:c r="S49" s="22" t="str"/>
+      <x:c r="T49" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="18" customHeight="1">
+      <x:c r="A50" s="22" t="str">
+        <x:v>0x943d71ed2a27e2cab27bb2c79488eec3cd2db33b</x:v>
+      </x:c>
+      <x:c r="B50" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C50" s="22" t="str">
+        <x:v>contracts/0x943d71ed2a27e2cab27bb2c79488eec3cd2db33b</x:v>
+      </x:c>
+      <x:c r="D50" s="22" t="str">
+        <x:v>contracts/0x943d71ed2a27e2cab27bb2c79488eec3cd2db33b/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E50" s="22" t="str">
+        <x:v>857dc0fab6141b601ed1c8b3a47a3b5f2ed2286db76be425ddd2245e7467ffd3</x:v>
+      </x:c>
+      <x:c r="F50" s="20" t="n">
+        <x:v>18031</x:v>
+      </x:c>
+      <x:c r="G50" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H50" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I50" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J50" s="20" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K50" s="22" t="str">
+        <x:v>Fibswap</x:v>
+      </x:c>
+      <x:c r="L50" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M50" s="22" t="str">
+        <x:v>0.8.11+commit.d7f03943</x:v>
+      </x:c>
+      <x:c r="N50" s="22" t="str">
+        <x:v>contracts/0x943d71ed2a27e2cab27bb2c79488eec3cd2db33b/abi.json</x:v>
+      </x:c>
+      <x:c r="O50" s="22" t="str">
+        <x:v>contracts/0x943d71ed2a27e2cab27bb2c79488eec3cd2db33b/metadata.json</x:v>
+      </x:c>
+      <x:c r="P50" s="22" t="str">
+        <x:v>contracts/0x943d71ed2a27e2cab27bb2c79488eec3cd2db33b/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q50" s="22" t="str">
+        <x:v>contracts/0x943d71ed2a27e2cab27bb2c79488eec3cd2db33b/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R50" s="22" t="str">
+        <x:v>contracts/0x943d71ed2a27e2cab27bb2c79488eec3cd2db33b/verification.json</x:v>
+      </x:c>
+      <x:c r="S50" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x943d71ed2a27e2cab27bb2c79488eec3cd2db33b?fields=all</x:v>
+      </x:c>
+      <x:c r="T50" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="18" customHeight="1">
+      <x:c r="A51" s="22" t="str">
+        <x:v>0x95235173ce34c35e050a97e89ac0d8d7053406ea</x:v>
+      </x:c>
+      <x:c r="B51" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C51" s="22" t="str">
+        <x:v>contracts/0x95235173ce34c35e050a97e89ac0d8d7053406ea</x:v>
+      </x:c>
+      <x:c r="D51" s="22" t="str">
+        <x:v>contracts/0x95235173ce34c35e050a97e89ac0d8d7053406ea/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E51" s="22" t="str">
+        <x:v>dc57805cbb4a8bc0f9bee823ef2ec844bad826fe9d77cb16974f8bf07d579732</x:v>
+      </x:c>
+      <x:c r="F51" s="20" t="n">
+        <x:v>7977</x:v>
+      </x:c>
+      <x:c r="G51" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H51" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I51" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J51" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K51" s="22" t="str"/>
+      <x:c r="L51" s="22" t="str"/>
+      <x:c r="M51" s="22" t="str"/>
+      <x:c r="N51" s="22" t="str"/>
+      <x:c r="O51" s="22" t="str"/>
+      <x:c r="P51" s="22" t="str"/>
+      <x:c r="Q51" s="22" t="str"/>
+      <x:c r="R51" s="22" t="str">
+        <x:v>contracts/0x95235173ce34c35e050a97e89ac0d8d7053406ea/verification.json</x:v>
+      </x:c>
+      <x:c r="S51" s="22" t="str"/>
+      <x:c r="T51" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="18" customHeight="1">
+      <x:c r="A52" s="22" t="str">
+        <x:v>0x970f1299a6a95bcace134814ebc40abb0418cdeb</x:v>
+      </x:c>
+      <x:c r="B52" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C52" s="22" t="str">
+        <x:v>contracts/0x970f1299a6a95bcace134814ebc40abb0418cdeb</x:v>
+      </x:c>
+      <x:c r="D52" s="22" t="str">
+        <x:v>contracts/0x970f1299a6a95bcace134814ebc40abb0418cdeb/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E52" s="22" t="str">
+        <x:v>25afd593c3d357dd128a5e8a2395e07f44490ab087ce24e9897709d5ec089054</x:v>
+      </x:c>
+      <x:c r="F52" s="20" t="n">
+        <x:v>7106</x:v>
+      </x:c>
+      <x:c r="G52" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H52" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I52" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J52" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K52" s="22" t="str">
+        <x:v>DfDepositToken</x:v>
+      </x:c>
+      <x:c r="L52" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M52" s="22" t="str">
+        <x:v>0.5.17+commit.d19bba13</x:v>
+      </x:c>
+      <x:c r="N52" s="22" t="str">
+        <x:v>contracts/0x970f1299a6a95bcace134814ebc40abb0418cdeb/abi.json</x:v>
+      </x:c>
+      <x:c r="O52" s="22" t="str">
+        <x:v>contracts/0x970f1299a6a95bcace134814ebc40abb0418cdeb/metadata.json</x:v>
+      </x:c>
+      <x:c r="P52" s="22" t="str">
+        <x:v>contracts/0x970f1299a6a95bcace134814ebc40abb0418cdeb/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q52" s="22" t="str">
+        <x:v>contracts/0x970f1299a6a95bcace134814ebc40abb0418cdeb/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R52" s="22" t="str">
+        <x:v>contracts/0x970f1299a6a95bcace134814ebc40abb0418cdeb/verification.json</x:v>
+      </x:c>
+      <x:c r="S52" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x970f1299a6a95bcace134814ebc40abb0418cdeb?fields=all</x:v>
+      </x:c>
+      <x:c r="T52" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="18" customHeight="1">
+      <x:c r="A53" s="22" t="str">
+        <x:v>0x97d3e5fbcf6dd93a2abfb95a00d2da7199ee3f57</x:v>
+      </x:c>
+      <x:c r="B53" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C53" s="22" t="str">
+        <x:v>contracts/0x97d3e5fbcf6dd93a2abfb95a00d2da7199ee3f57</x:v>
+      </x:c>
+      <x:c r="D53" s="22" t="str">
+        <x:v>contracts/0x97d3e5fbcf6dd93a2abfb95a00d2da7199ee3f57/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E53" s="22" t="str">
+        <x:v>309beb9b64d576c3009e99b134a09fae71ea420575879b22663cc1259ec90772</x:v>
+      </x:c>
+      <x:c r="F53" s="20" t="n">
+        <x:v>20832</x:v>
+      </x:c>
+      <x:c r="G53" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H53" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I53" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J53" s="20" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K53" s="22" t="str">
+        <x:v>QuantumSpaces</x:v>
+      </x:c>
+      <x:c r="L53" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M53" s="22" t="str">
+        <x:v>0.8.11+commit.d7f03943</x:v>
+      </x:c>
+      <x:c r="N53" s="22" t="str">
+        <x:v>contracts/0x97d3e5fbcf6dd93a2abfb95a00d2da7199ee3f57/abi.json</x:v>
+      </x:c>
+      <x:c r="O53" s="22" t="str">
+        <x:v>contracts/0x97d3e5fbcf6dd93a2abfb95a00d2da7199ee3f57/metadata.json</x:v>
+      </x:c>
+      <x:c r="P53" s="22" t="str">
+        <x:v>contracts/0x97d3e5fbcf6dd93a2abfb95a00d2da7199ee3f57/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q53" s="22" t="str">
+        <x:v>contracts/0x97d3e5fbcf6dd93a2abfb95a00d2da7199ee3f57/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R53" s="22" t="str">
+        <x:v>contracts/0x97d3e5fbcf6dd93a2abfb95a00d2da7199ee3f57/verification.json</x:v>
+      </x:c>
+      <x:c r="S53" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x97d3e5fbcf6dd93a2abfb95a00d2da7199ee3f57?fields=all</x:v>
+      </x:c>
+      <x:c r="T53" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="18" customHeight="1">
+      <x:c r="A54" s="22" t="str">
+        <x:v>0x982edd74fb8a7d04c95eda20e475fc57d92af0a9</x:v>
+      </x:c>
+      <x:c r="B54" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C54" s="22" t="str">
+        <x:v>contracts/0x982edd74fb8a7d04c95eda20e475fc57d92af0a9</x:v>
+      </x:c>
+      <x:c r="D54" s="22" t="str">
+        <x:v>contracts/0x982edd74fb8a7d04c95eda20e475fc57d92af0a9/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E54" s="22" t="str">
+        <x:v>8b0b4bbdd579b5a93b69a0756e92adb822e572d04bf54dcfe818e42f329169e5</x:v>
+      </x:c>
+      <x:c r="F54" s="20" t="n">
+        <x:v>14355</x:v>
+      </x:c>
+      <x:c r="G54" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H54" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I54" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J54" s="20" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K54" s="22" t="str">
+        <x:v>MEMEKONG</x:v>
+      </x:c>
+      <x:c r="L54" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M54" s="22" t="str">
+        <x:v>0.8.18+commit.87f61d96</x:v>
+      </x:c>
+      <x:c r="N54" s="22" t="str">
+        <x:v>contracts/0x982edd74fb8a7d04c95eda20e475fc57d92af0a9/abi.json</x:v>
+      </x:c>
+      <x:c r="O54" s="22" t="str">
+        <x:v>contracts/0x982edd74fb8a7d04c95eda20e475fc57d92af0a9/metadata.json</x:v>
+      </x:c>
+      <x:c r="P54" s="22" t="str">
+        <x:v>contracts/0x982edd74fb8a7d04c95eda20e475fc57d92af0a9/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q54" s="22" t="str">
+        <x:v>contracts/0x982edd74fb8a7d04c95eda20e475fc57d92af0a9/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R54" s="22" t="str">
+        <x:v>contracts/0x982edd74fb8a7d04c95eda20e475fc57d92af0a9/verification.json</x:v>
+      </x:c>
+      <x:c r="S54" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x982edd74fb8a7d04c95eda20e475fc57d92af0a9?fields=all</x:v>
+      </x:c>
+      <x:c r="T54" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="18" customHeight="1">
+      <x:c r="A55" s="22" t="str">
+        <x:v>0x987411b73708d5746de2c412cc234da90b1245a7</x:v>
+      </x:c>
+      <x:c r="B55" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C55" s="22" t="str">
+        <x:v>contracts/0x987411b73708d5746de2c412cc234da90b1245a7</x:v>
+      </x:c>
+      <x:c r="D55" s="22" t="str">
+        <x:v>contracts/0x987411b73708d5746de2c412cc234da90b1245a7/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E55" s="22" t="str">
+        <x:v>25f04f52ac94a9221ef0e92c413120409ced084e4bd80126d214682527d6f31b</x:v>
+      </x:c>
+      <x:c r="F55" s="20" t="n">
+        <x:v>2042</x:v>
+      </x:c>
+      <x:c r="G55" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H55" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I55" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J55" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K55" s="22" t="str"/>
+      <x:c r="L55" s="22" t="str"/>
+      <x:c r="M55" s="22" t="str"/>
+      <x:c r="N55" s="22" t="str"/>
+      <x:c r="O55" s="22" t="str"/>
+      <x:c r="P55" s="22" t="str"/>
+      <x:c r="Q55" s="22" t="str"/>
+      <x:c r="R55" s="22" t="str">
+        <x:v>contracts/0x987411b73708d5746de2c412cc234da90b1245a7/verification.json</x:v>
+      </x:c>
+      <x:c r="S55" s="22" t="str"/>
+      <x:c r="T55" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="18" customHeight="1">
+      <x:c r="A56" s="22" t="str">
+        <x:v>0x9e05d613e09e878cc14e5c25a79028b8dcff79d3</x:v>
+      </x:c>
+      <x:c r="B56" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C56" s="22" t="str">
+        <x:v>contracts/0x9e05d613e09e878cc14e5c25a79028b8dcff79d3</x:v>
+      </x:c>
+      <x:c r="D56" s="22" t="str">
+        <x:v>contracts/0x9e05d613e09e878cc14e5c25a79028b8dcff79d3/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E56" s="22" t="str">
+        <x:v>74fd1401213e2f54fe54cd960edddd010af7ab2d24d903d5aa9657afad20e24f</x:v>
+      </x:c>
+      <x:c r="F56" s="20" t="n">
+        <x:v>15769</x:v>
+      </x:c>
+      <x:c r="G56" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H56" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I56" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J56" s="20" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K56" s="22" t="str">
+        <x:v>OTCWrapper</x:v>
+      </x:c>
+      <x:c r="L56" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M56" s="22" t="str">
+        <x:v>0.8.10+commit.fc410830</x:v>
+      </x:c>
+      <x:c r="N56" s="22" t="str">
+        <x:v>contracts/0x9e05d613e09e878cc14e5c25a79028b8dcff79d3/abi.json</x:v>
+      </x:c>
+      <x:c r="O56" s="22" t="str">
+        <x:v>contracts/0x9e05d613e09e878cc14e5c25a79028b8dcff79d3/metadata.json</x:v>
+      </x:c>
+      <x:c r="P56" s="22" t="str">
+        <x:v>contracts/0x9e05d613e09e878cc14e5c25a79028b8dcff79d3/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q56" s="22" t="str">
+        <x:v>contracts/0x9e05d613e09e878cc14e5c25a79028b8dcff79d3/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R56" s="22" t="str">
+        <x:v>contracts/0x9e05d613e09e878cc14e5c25a79028b8dcff79d3/verification.json</x:v>
+      </x:c>
+      <x:c r="S56" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0x9e05d613e09e878cc14e5c25a79028b8dcff79d3?fields=all</x:v>
+      </x:c>
+      <x:c r="T56" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="18" customHeight="1">
+      <x:c r="A57" s="22" t="str">
+        <x:v>0xa8e5ea57f875d8cb5700eb270238ce52ede9cad8</x:v>
+      </x:c>
+      <x:c r="B57" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C57" s="22" t="str">
+        <x:v>contracts/0xa8e5ea57f875d8cb5700eb270238ce52ede9cad8</x:v>
+      </x:c>
+      <x:c r="D57" s="22" t="str">
+        <x:v>contracts/0xa8e5ea57f875d8cb5700eb270238ce52ede9cad8/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E57" s="22" t="str">
+        <x:v>74c87970983c756d7f97c2e244d1d04fc3edfe350df90f9ca552cb5e3b1d21ba</x:v>
+      </x:c>
+      <x:c r="F57" s="20" t="n">
+        <x:v>19047</x:v>
+      </x:c>
+      <x:c r="G57" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H57" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I57" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J57" s="20" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K57" s="22" t="str">
+        <x:v>StakingVault</x:v>
+      </x:c>
+      <x:c r="L57" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M57" s="22" t="str">
+        <x:v>0.8.4+commit.c7e474f2</x:v>
+      </x:c>
+      <x:c r="N57" s="22" t="str">
+        <x:v>contracts/0xa8e5ea57f875d8cb5700eb270238ce52ede9cad8/abi.json</x:v>
+      </x:c>
+      <x:c r="O57" s="22" t="str">
+        <x:v>contracts/0xa8e5ea57f875d8cb5700eb270238ce52ede9cad8/metadata.json</x:v>
+      </x:c>
+      <x:c r="P57" s="22" t="str">
+        <x:v>contracts/0xa8e5ea57f875d8cb5700eb270238ce52ede9cad8/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q57" s="22" t="str">
+        <x:v>contracts/0xa8e5ea57f875d8cb5700eb270238ce52ede9cad8/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R57" s="22" t="str">
+        <x:v>contracts/0xa8e5ea57f875d8cb5700eb270238ce52ede9cad8/verification.json</x:v>
+      </x:c>
+      <x:c r="S57" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0xa8e5ea57f875d8cb5700eb270238ce52ede9cad8?fields=all</x:v>
+      </x:c>
+      <x:c r="T57" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="18" customHeight="1">
+      <x:c r="A58" s="22" t="str">
+        <x:v>0xae90a7868c46861912a5cb12c1c5e9d3a1dd3e60</x:v>
+      </x:c>
+      <x:c r="B58" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C58" s="22" t="str">
+        <x:v>contracts/0xae90a7868c46861912a5cb12c1c5e9d3a1dd3e60</x:v>
+      </x:c>
+      <x:c r="D58" s="22" t="str">
+        <x:v>contracts/0xae90a7868c46861912a5cb12c1c5e9d3a1dd3e60/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E58" s="22" t="str">
+        <x:v>b229487044864cbb197aa77e0af28d6d02f1c9ca2dd221877f8ca55854420770</x:v>
+      </x:c>
+      <x:c r="F58" s="20" t="n">
+        <x:v>2920</x:v>
+      </x:c>
+      <x:c r="G58" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H58" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I58" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J58" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K58" s="22" t="str"/>
+      <x:c r="L58" s="22" t="str"/>
+      <x:c r="M58" s="22" t="str"/>
+      <x:c r="N58" s="22" t="str"/>
+      <x:c r="O58" s="22" t="str"/>
+      <x:c r="P58" s="22" t="str"/>
+      <x:c r="Q58" s="22" t="str"/>
+      <x:c r="R58" s="22" t="str">
+        <x:v>contracts/0xae90a7868c46861912a5cb12c1c5e9d3a1dd3e60/verification.json</x:v>
+      </x:c>
+      <x:c r="S58" s="22" t="str"/>
+      <x:c r="T58" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="18" customHeight="1">
+      <x:c r="A59" s="22" t="str">
+        <x:v>0xb2999240765ce4334400ab1d5ef24163c30fb35f</x:v>
+      </x:c>
+      <x:c r="B59" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C59" s="22" t="str">
+        <x:v>contracts/0xb2999240765ce4334400ab1d5ef24163c30fb35f</x:v>
+      </x:c>
+      <x:c r="D59" s="22" t="str">
+        <x:v>contracts/0xb2999240765ce4334400ab1d5ef24163c30fb35f/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E59" s="22" t="str">
+        <x:v>2946bbe9e5c2d16ee6a272decedadac06bad07ca78f21457f94071fa3627ea57</x:v>
+      </x:c>
+      <x:c r="F59" s="20" t="n">
+        <x:v>17551</x:v>
+      </x:c>
+      <x:c r="G59" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H59" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I59" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J59" s="20" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K59" s="22" t="str">
+        <x:v>ComplianceRegistry</x:v>
+      </x:c>
+      <x:c r="L59" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M59" s="22" t="str">
+        <x:v>0.6.2+commit.bacdbe57</x:v>
+      </x:c>
+      <x:c r="N59" s="22" t="str">
+        <x:v>contracts/0xb2999240765ce4334400ab1d5ef24163c30fb35f/abi.json</x:v>
+      </x:c>
+      <x:c r="O59" s="22" t="str">
+        <x:v>contracts/0xb2999240765ce4334400ab1d5ef24163c30fb35f/metadata.json</x:v>
+      </x:c>
+      <x:c r="P59" s="22" t="str">
+        <x:v>contracts/0xb2999240765ce4334400ab1d5ef24163c30fb35f/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q59" s="22" t="str">
+        <x:v>contracts/0xb2999240765ce4334400ab1d5ef24163c30fb35f/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R59" s="22" t="str">
+        <x:v>contracts/0xb2999240765ce4334400ab1d5ef24163c30fb35f/verification.json</x:v>
+      </x:c>
+      <x:c r="S59" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0xb2999240765ce4334400ab1d5ef24163c30fb35f?fields=all</x:v>
+      </x:c>
+      <x:c r="T59" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="18" customHeight="1">
+      <x:c r="A60" s="22" t="str">
+        <x:v>0xb2fd6574bbc7f18d9ebfeca4f7a11dfe4b09d740</x:v>
+      </x:c>
+      <x:c r="B60" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C60" s="22" t="str">
+        <x:v>contracts/0xb2fd6574bbc7f18d9ebfeca4f7a11dfe4b09d740</x:v>
+      </x:c>
+      <x:c r="D60" s="22" t="str">
+        <x:v>contracts/0xb2fd6574bbc7f18d9ebfeca4f7a11dfe4b09d740/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E60" s="22" t="str">
+        <x:v>22755a7bf7368e732e902a6e2c685f7cb043c9be1402fe8bf1a34ae483af8974</x:v>
+      </x:c>
+      <x:c r="F60" s="20" t="n">
+        <x:v>13512</x:v>
+      </x:c>
+      <x:c r="G60" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H60" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I60" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J60" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K60" s="22" t="str">
+        <x:v>DfTokenizedDeposit</x:v>
+      </x:c>
+      <x:c r="L60" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M60" s="22" t="str">
+        <x:v>0.5.17+commit.d19bba13</x:v>
+      </x:c>
+      <x:c r="N60" s="22" t="str">
+        <x:v>contracts/0xb2fd6574bbc7f18d9ebfeca4f7a11dfe4b09d740/abi.json</x:v>
+      </x:c>
+      <x:c r="O60" s="22" t="str">
+        <x:v>contracts/0xb2fd6574bbc7f18d9ebfeca4f7a11dfe4b09d740/metadata.json</x:v>
+      </x:c>
+      <x:c r="P60" s="22" t="str">
+        <x:v>contracts/0xb2fd6574bbc7f18d9ebfeca4f7a11dfe4b09d740/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q60" s="22" t="str">
+        <x:v>contracts/0xb2fd6574bbc7f18d9ebfeca4f7a11dfe4b09d740/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R60" s="22" t="str">
+        <x:v>contracts/0xb2fd6574bbc7f18d9ebfeca4f7a11dfe4b09d740/verification.json</x:v>
+      </x:c>
+      <x:c r="S60" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0xb2fd6574bbc7f18d9ebfeca4f7a11dfe4b09d740?fields=all</x:v>
+      </x:c>
+      <x:c r="T60" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="18" customHeight="1">
+      <x:c r="A61" s="22" t="str">
+        <x:v>0xb5113245e64e2eed58e683573694c84f4b193fa5</x:v>
+      </x:c>
+      <x:c r="B61" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C61" s="22" t="str">
+        <x:v>contracts/0xb5113245e64e2eed58e683573694c84f4b193fa5</x:v>
+      </x:c>
+      <x:c r="D61" s="22" t="str">
+        <x:v>contracts/0xb5113245e64e2eed58e683573694c84f4b193fa5/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E61" s="22" t="str">
+        <x:v>25a484692d3c17fc5649ac68631553bfa65ccd7faa11c296b737e844e544055e</x:v>
+      </x:c>
+      <x:c r="F61" s="20" t="n">
+        <x:v>9444</x:v>
+      </x:c>
+      <x:c r="G61" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H61" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I61" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J61" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K61" s="22" t="str"/>
+      <x:c r="L61" s="22" t="str"/>
+      <x:c r="M61" s="22" t="str"/>
+      <x:c r="N61" s="22" t="str"/>
+      <x:c r="O61" s="22" t="str"/>
+      <x:c r="P61" s="22" t="str"/>
+      <x:c r="Q61" s="22" t="str"/>
+      <x:c r="R61" s="22" t="str">
+        <x:v>contracts/0xb5113245e64e2eed58e683573694c84f4b193fa5/verification.json</x:v>
+      </x:c>
+      <x:c r="S61" s="22" t="str"/>
+      <x:c r="T61" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="18" customHeight="1">
+      <x:c r="A62" s="22" t="str">
+        <x:v>0xb54d451c9be013425564c2a2065bec0ade4b95af</x:v>
+      </x:c>
+      <x:c r="B62" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C62" s="22" t="str">
+        <x:v>contracts/0xb54d451c9be013425564c2a2065bec0ade4b95af</x:v>
+      </x:c>
+      <x:c r="D62" s="22" t="str">
+        <x:v>contracts/0xb54d451c9be013425564c2a2065bec0ade4b95af/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E62" s="22" t="str">
+        <x:v>8644b2fc9f6c20e866badcb991223cfd89c6382f7b83fec57468f96edc5660f5</x:v>
+      </x:c>
+      <x:c r="F62" s="20" t="n">
+        <x:v>6170</x:v>
+      </x:c>
+      <x:c r="G62" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H62" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I62" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J62" s="20" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K62" s="22" t="str">
+        <x:v>WAGMIClaimable</x:v>
+      </x:c>
+      <x:c r="L62" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M62" s="22" t="str">
+        <x:v>0.8.17+commit.8df45f5f</x:v>
+      </x:c>
+      <x:c r="N62" s="22" t="str">
+        <x:v>contracts/0xb54d451c9be013425564c2a2065bec0ade4b95af/abi.json</x:v>
+      </x:c>
+      <x:c r="O62" s="22" t="str">
+        <x:v>contracts/0xb54d451c9be013425564c2a2065bec0ade4b95af/metadata.json</x:v>
+      </x:c>
+      <x:c r="P62" s="22" t="str">
+        <x:v>contracts/0xb54d451c9be013425564c2a2065bec0ade4b95af/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q62" s="22" t="str">
+        <x:v>contracts/0xb54d451c9be013425564c2a2065bec0ade4b95af/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R62" s="22" t="str">
+        <x:v>contracts/0xb54d451c9be013425564c2a2065bec0ade4b95af/verification.json</x:v>
+      </x:c>
+      <x:c r="S62" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0xb54d451c9be013425564c2a2065bec0ade4b95af?fields=all</x:v>
+      </x:c>
+      <x:c r="T62" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="18" customHeight="1">
+      <x:c r="A63" s="22" t="str">
+        <x:v>0xb8adf0585d263f3ba6f73bce1ccc56b821581ab8</x:v>
+      </x:c>
+      <x:c r="B63" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C63" s="22" t="str">
+        <x:v>contracts/0xb8adf0585d263f3ba6f73bce1ccc56b821581ab8</x:v>
+      </x:c>
+      <x:c r="D63" s="22" t="str">
+        <x:v>contracts/0xb8adf0585d263f3ba6f73bce1ccc56b821581ab8/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E63" s="22" t="str">
+        <x:v>59a34b452856bc1d58eb8d0a4e2ad251afe77a877e93c6a3371a83eb1cf53922</x:v>
+      </x:c>
+      <x:c r="F63" s="20" t="n">
+        <x:v>12750</x:v>
+      </x:c>
+      <x:c r="G63" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H63" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I63" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J63" s="20" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K63" s="22" t="str">
+        <x:v>LandRegistry</x:v>
+      </x:c>
+      <x:c r="L63" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M63" s="22" t="str">
+        <x:v>0.8.13+commit.abaa5c0e</x:v>
+      </x:c>
+      <x:c r="N63" s="22" t="str">
+        <x:v>contracts/0xb8adf0585d263f3ba6f73bce1ccc56b821581ab8/abi.json</x:v>
+      </x:c>
+      <x:c r="O63" s="22" t="str">
+        <x:v>contracts/0xb8adf0585d263f3ba6f73bce1ccc56b821581ab8/metadata.json</x:v>
+      </x:c>
+      <x:c r="P63" s="22" t="str">
+        <x:v>contracts/0xb8adf0585d263f3ba6f73bce1ccc56b821581ab8/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q63" s="22" t="str">
+        <x:v>contracts/0xb8adf0585d263f3ba6f73bce1ccc56b821581ab8/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R63" s="22" t="str">
+        <x:v>contracts/0xb8adf0585d263f3ba6f73bce1ccc56b821581ab8/verification.json</x:v>
+      </x:c>
+      <x:c r="S63" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0xb8adf0585d263f3ba6f73bce1ccc56b821581ab8?fields=all</x:v>
+      </x:c>
+      <x:c r="T63" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="18" customHeight="1">
+      <x:c r="A64" s="22" t="str">
+        <x:v>0xb9ba467bd91aa634e7e3202becc3222644280066</x:v>
+      </x:c>
+      <x:c r="B64" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C64" s="22" t="str">
+        <x:v>contracts/0xb9ba467bd91aa634e7e3202becc3222644280066</x:v>
+      </x:c>
+      <x:c r="D64" s="22" t="str">
+        <x:v>contracts/0xb9ba467bd91aa634e7e3202becc3222644280066/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E64" s="22" t="str">
+        <x:v>2f891cd9a463d71bf0c3ec4cb8acd4d812c0d4f6116c04ce5c0df171b3425fb9</x:v>
+      </x:c>
+      <x:c r="F64" s="20" t="n">
+        <x:v>2676</x:v>
+      </x:c>
+      <x:c r="G64" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H64" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I64" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J64" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K64" s="22" t="str"/>
+      <x:c r="L64" s="22" t="str"/>
+      <x:c r="M64" s="22" t="str"/>
+      <x:c r="N64" s="22" t="str"/>
+      <x:c r="O64" s="22" t="str"/>
+      <x:c r="P64" s="22" t="str"/>
+      <x:c r="Q64" s="22" t="str"/>
+      <x:c r="R64" s="22" t="str">
+        <x:v>contracts/0xb9ba467bd91aa634e7e3202becc3222644280066/verification.json</x:v>
+      </x:c>
+      <x:c r="S64" s="22" t="str"/>
+      <x:c r="T64" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="18" customHeight="1">
+      <x:c r="A65" s="22" t="str">
+        <x:v>0xbd1ab5ed43cd8377c8fa3dbebcd5b466b1beeba0</x:v>
+      </x:c>
+      <x:c r="B65" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C65" s="22" t="str">
+        <x:v>contracts/0xbd1ab5ed43cd8377c8fa3dbebcd5b466b1beeba0</x:v>
+      </x:c>
+      <x:c r="D65" s="22" t="str">
+        <x:v>contracts/0xbd1ab5ed43cd8377c8fa3dbebcd5b466b1beeba0/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E65" s="22" t="str">
+        <x:v>163ab0522e2b219d55694431141db2de20649ae9ece6f03e578868761b84cb9e</x:v>
+      </x:c>
+      <x:c r="F65" s="20" t="n">
+        <x:v>5825</x:v>
+      </x:c>
+      <x:c r="G65" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H65" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I65" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J65" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K65" s="22" t="str"/>
+      <x:c r="L65" s="22" t="str"/>
+      <x:c r="M65" s="22" t="str"/>
+      <x:c r="N65" s="22" t="str"/>
+      <x:c r="O65" s="22" t="str"/>
+      <x:c r="P65" s="22" t="str"/>
+      <x:c r="Q65" s="22" t="str"/>
+      <x:c r="R65" s="22" t="str">
+        <x:v>contracts/0xbd1ab5ed43cd8377c8fa3dbebcd5b466b1beeba0/verification.json</x:v>
+      </x:c>
+      <x:c r="S65" s="22" t="str"/>
+      <x:c r="T65" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="18" customHeight="1">
+      <x:c r="A66" s="22" t="str">
+        <x:v>0xbdadd6dc0a1f8905cc339b9ce0a25208fd2b5da5</x:v>
+      </x:c>
+      <x:c r="B66" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C66" s="22" t="str">
+        <x:v>contracts/0xbdadd6dc0a1f8905cc339b9ce0a25208fd2b5da5</x:v>
+      </x:c>
+      <x:c r="D66" s="22" t="str">
+        <x:v>contracts/0xbdadd6dc0a1f8905cc339b9ce0a25208fd2b5da5/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E66" s="22" t="str">
+        <x:v>9f13624f25554384c247a00c3e2d0a85d1ae80b84b4c392ac7a7a3c4ce424017</x:v>
+      </x:c>
+      <x:c r="F66" s="20" t="n">
+        <x:v>1757</x:v>
+      </x:c>
+      <x:c r="G66" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H66" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I66" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J66" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K66" s="22" t="str"/>
+      <x:c r="L66" s="22" t="str"/>
+      <x:c r="M66" s="22" t="str"/>
+      <x:c r="N66" s="22" t="str"/>
+      <x:c r="O66" s="22" t="str"/>
+      <x:c r="P66" s="22" t="str"/>
+      <x:c r="Q66" s="22" t="str"/>
+      <x:c r="R66" s="22" t="str">
+        <x:v>contracts/0xbdadd6dc0a1f8905cc339b9ce0a25208fd2b5da5/verification.json</x:v>
+      </x:c>
+      <x:c r="S66" s="22" t="str"/>
+      <x:c r="T66" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="18" customHeight="1">
+      <x:c r="A67" s="22" t="str">
+        <x:v>0xbdd20d63ff83f5ce8359ee9c7842b4a621f601c2</x:v>
+      </x:c>
+      <x:c r="B67" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C67" s="22" t="str">
+        <x:v>contracts/0xbdd20d63ff83f5ce8359ee9c7842b4a621f601c2</x:v>
+      </x:c>
+      <x:c r="D67" s="22" t="str">
+        <x:v>contracts/0xbdd20d63ff83f5ce8359ee9c7842b4a621f601c2/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E67" s="22" t="str">
+        <x:v>dbf702cbdc0d32f67a2c527ff0113f7931a194e2e1d38ba8949c55399161ced3</x:v>
+      </x:c>
+      <x:c r="F67" s="20" t="n">
+        <x:v>10105</x:v>
+      </x:c>
+      <x:c r="G67" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H67" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I67" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J67" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K67" s="22" t="str"/>
+      <x:c r="L67" s="22" t="str"/>
+      <x:c r="M67" s="22" t="str"/>
+      <x:c r="N67" s="22" t="str"/>
+      <x:c r="O67" s="22" t="str"/>
+      <x:c r="P67" s="22" t="str"/>
+      <x:c r="Q67" s="22" t="str"/>
+      <x:c r="R67" s="22" t="str">
+        <x:v>contracts/0xbdd20d63ff83f5ce8359ee9c7842b4a621f601c2/verification.json</x:v>
+      </x:c>
+      <x:c r="S67" s="22" t="str"/>
+      <x:c r="T67" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="18" customHeight="1">
+      <x:c r="A68" s="22" t="str">
+        <x:v>0xbe275258013e5bbb740f77fd5c34e424e6841c86</x:v>
+      </x:c>
+      <x:c r="B68" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C68" s="22" t="str">
+        <x:v>contracts/0xbe275258013e5bbb740f77fd5c34e424e6841c86</x:v>
+      </x:c>
+      <x:c r="D68" s="22" t="str">
+        <x:v>contracts/0xbe275258013e5bbb740f77fd5c34e424e6841c86/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E68" s="22" t="str">
+        <x:v>9aac6ec9ffa92ed69f05dcc93fde2c674bcd5993cd08f63bf13dd7de8de7ac2e</x:v>
+      </x:c>
+      <x:c r="F68" s="20" t="n">
+        <x:v>2920</x:v>
+      </x:c>
+      <x:c r="G68" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H68" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I68" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J68" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K68" s="22" t="str"/>
+      <x:c r="L68" s="22" t="str"/>
+      <x:c r="M68" s="22" t="str"/>
+      <x:c r="N68" s="22" t="str"/>
+      <x:c r="O68" s="22" t="str"/>
+      <x:c r="P68" s="22" t="str"/>
+      <x:c r="Q68" s="22" t="str"/>
+      <x:c r="R68" s="22" t="str">
+        <x:v>contracts/0xbe275258013e5bbb740f77fd5c34e424e6841c86/verification.json</x:v>
+      </x:c>
+      <x:c r="S68" s="22" t="str"/>
+      <x:c r="T68" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="18" customHeight="1">
+      <x:c r="A69" s="22" t="str">
+        <x:v>0xc600727f1ce705436734f2367e7fc449da5fb3a6</x:v>
+      </x:c>
+      <x:c r="B69" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C69" s="22" t="str">
+        <x:v>contracts/0xc600727f1ce705436734f2367e7fc449da5fb3a6</x:v>
+      </x:c>
+      <x:c r="D69" s="22" t="str">
+        <x:v>contracts/0xc600727f1ce705436734f2367e7fc449da5fb3a6/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E69" s="22" t="str">
+        <x:v>8f3a0a73767e258d99a5375ccaf2a8f01170b9c0622b36141e453fb4d2d327c0</x:v>
+      </x:c>
+      <x:c r="F69" s="20" t="n">
+        <x:v>23133</x:v>
+      </x:c>
+      <x:c r="G69" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H69" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I69" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J69" s="20" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K69" s="22" t="str">
+        <x:v>AutoCoinageSnapshot2</x:v>
+      </x:c>
+      <x:c r="L69" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M69" s="22" t="str">
+        <x:v>0.8.4+commit.c7e474f2</x:v>
+      </x:c>
+      <x:c r="N69" s="22" t="str">
+        <x:v>contracts/0xc600727f1ce705436734f2367e7fc449da5fb3a6/abi.json</x:v>
+      </x:c>
+      <x:c r="O69" s="22" t="str">
+        <x:v>contracts/0xc600727f1ce705436734f2367e7fc449da5fb3a6/metadata.json</x:v>
+      </x:c>
+      <x:c r="P69" s="22" t="str">
+        <x:v>contracts/0xc600727f1ce705436734f2367e7fc449da5fb3a6/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q69" s="22" t="str">
+        <x:v>contracts/0xc600727f1ce705436734f2367e7fc449da5fb3a6/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R69" s="22" t="str">
+        <x:v>contracts/0xc600727f1ce705436734f2367e7fc449da5fb3a6/verification.json</x:v>
+      </x:c>
+      <x:c r="S69" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0xc600727f1ce705436734f2367e7fc449da5fb3a6?fields=all</x:v>
+      </x:c>
+      <x:c r="T69" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="18" customHeight="1">
+      <x:c r="A70" s="22" t="str">
+        <x:v>0xc83e731e0cab21ce5b0bbbe3252baefd0e11fc03</x:v>
+      </x:c>
+      <x:c r="B70" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C70" s="22" t="str">
+        <x:v>contracts/0xc83e731e0cab21ce5b0bbbe3252baefd0e11fc03</x:v>
+      </x:c>
+      <x:c r="D70" s="22" t="str">
+        <x:v>contracts/0xc83e731e0cab21ce5b0bbbe3252baefd0e11fc03/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E70" s="22" t="str">
+        <x:v>c1a7cbccc73a0224e57e0592ccbc0faccf27890bf167ced5d07fbf6218affe0d</x:v>
+      </x:c>
+      <x:c r="F70" s="20" t="n">
+        <x:v>17683</x:v>
+      </x:c>
+      <x:c r="G70" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H70" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I70" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J70" s="20" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K70" s="22" t="str">
+        <x:v>SAFU</x:v>
+      </x:c>
+      <x:c r="L70" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M70" s="22" t="str">
+        <x:v>0.6.10+commit.00c0fcaf</x:v>
+      </x:c>
+      <x:c r="N70" s="22" t="str">
+        <x:v>contracts/0xc83e731e0cab21ce5b0bbbe3252baefd0e11fc03/abi.json</x:v>
+      </x:c>
+      <x:c r="O70" s="22" t="str">
+        <x:v>contracts/0xc83e731e0cab21ce5b0bbbe3252baefd0e11fc03/metadata.json</x:v>
+      </x:c>
+      <x:c r="P70" s="22" t="str">
+        <x:v>contracts/0xc83e731e0cab21ce5b0bbbe3252baefd0e11fc03/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q70" s="22" t="str">
+        <x:v>contracts/0xc83e731e0cab21ce5b0bbbe3252baefd0e11fc03/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R70" s="22" t="str">
+        <x:v>contracts/0xc83e731e0cab21ce5b0bbbe3252baefd0e11fc03/verification.json</x:v>
+      </x:c>
+      <x:c r="S70" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0xc83e731e0cab21ce5b0bbbe3252baefd0e11fc03?fields=all</x:v>
+      </x:c>
+      <x:c r="T70" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="18" customHeight="1">
+      <x:c r="A71" s="22" t="str">
+        <x:v>0xc9e3d7d8f196a7e915a5c7ce49fde19be7ca35b6</x:v>
+      </x:c>
+      <x:c r="B71" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C71" s="22" t="str">
+        <x:v>contracts/0xc9e3d7d8f196a7e915a5c7ce49fde19be7ca35b6</x:v>
+      </x:c>
+      <x:c r="D71" s="22" t="str">
+        <x:v>contracts/0xc9e3d7d8f196a7e915a5c7ce49fde19be7ca35b6/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E71" s="22" t="str">
+        <x:v>41ed8a9d2036a678db3883fb04100b19b2af68678a738e9833677c593561b65e</x:v>
+      </x:c>
+      <x:c r="F71" s="20" t="n">
+        <x:v>7813</x:v>
+      </x:c>
+      <x:c r="G71" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H71" s="22" t="str">
+        <x:v>blockscout</x:v>
+      </x:c>
+      <x:c r="I71" s="22" t="str">
+        <x:v>partial_match</x:v>
+      </x:c>
+      <x:c r="J71" s="20" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K71" s="22" t="str">
+        <x:v>Bridge</x:v>
+      </x:c>
+      <x:c r="L71" s="22" t="str">
+        <x:v>solidity</x:v>
+      </x:c>
+      <x:c r="M71" s="22" t="str">
+        <x:v>v0.8.14+commit.80d49f37</x:v>
+      </x:c>
+      <x:c r="N71" s="22" t="str">
+        <x:v>contracts/0xc9e3d7d8f196a7e915a5c7ce49fde19be7ca35b6/abi.json</x:v>
+      </x:c>
+      <x:c r="O71" s="22" t="str"/>
+      <x:c r="P71" s="22" t="str"/>
+      <x:c r="Q71" s="22" t="str"/>
+      <x:c r="R71" s="22" t="str">
+        <x:v>contracts/0xc9e3d7d8f196a7e915a5c7ce49fde19be7ca35b6/verification.json</x:v>
+      </x:c>
+      <x:c r="S71" s="22" t="str">
+        <x:v>https://eth.blockscout.com/api/v2/smart-contracts/0xc9e3d7d8f196a7e915a5c7ce49fde19be7ca35b6</x:v>
+      </x:c>
+      <x:c r="T71" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="18" customHeight="1">
+      <x:c r="A72" s="22" t="str">
+        <x:v>0xcac49516e6e1c79a62bd67e4d87f7e0d80858258</x:v>
+      </x:c>
+      <x:c r="B72" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C72" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258</x:v>
+      </x:c>
+      <x:c r="D72" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E72" s="22" t="str">
+        <x:v>2172ffe2fdcceb9450519d06338aa4fc905fb50d4f5aacb3d4865a7696d61df8</x:v>
+      </x:c>
+      <x:c r="F72" s="20" t="n">
+        <x:v>20375</x:v>
+      </x:c>
+      <x:c r="G72" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H72" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I72" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J72" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K72" s="22" t="str">
+        <x:v>LoopringAmmPool</x:v>
+      </x:c>
+      <x:c r="L72" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M72" s="22" t="str">
+        <x:v>0.7.6+commit.7338295f</x:v>
+      </x:c>
+      <x:c r="N72" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258/abi.json</x:v>
+      </x:c>
+      <x:c r="O72" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258/metadata.json</x:v>
+      </x:c>
+      <x:c r="P72" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q72" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R72" s="22" t="str">
+        <x:v>contracts/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258/verification.json</x:v>
+      </x:c>
+      <x:c r="S72" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0xcac49516e6e1c79a62bd67e4d87f7e0d80858258?fields=all</x:v>
+      </x:c>
+      <x:c r="T72" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="18" customHeight="1">
+      <x:c r="A73" s="22" t="str">
+        <x:v>0xcf2bd216729092e9726f21116f380d412bd4a32e</x:v>
+      </x:c>
+      <x:c r="B73" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C73" s="22" t="str">
+        <x:v>contracts/0xcf2bd216729092e9726f21116f380d412bd4a32e</x:v>
+      </x:c>
+      <x:c r="D73" s="22" t="str">
+        <x:v>contracts/0xcf2bd216729092e9726f21116f380d412bd4a32e/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E73" s="22" t="str">
+        <x:v>094dd2c9882d1298e9b4e03cad38eed6d098ad7d3432f18193534ea1355a94be</x:v>
+      </x:c>
+      <x:c r="F73" s="20" t="n">
+        <x:v>8635</x:v>
+      </x:c>
+      <x:c r="G73" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H73" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I73" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J73" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K73" s="22" t="str"/>
+      <x:c r="L73" s="22" t="str"/>
+      <x:c r="M73" s="22" t="str"/>
+      <x:c r="N73" s="22" t="str"/>
+      <x:c r="O73" s="22" t="str"/>
+      <x:c r="P73" s="22" t="str"/>
+      <x:c r="Q73" s="22" t="str"/>
+      <x:c r="R73" s="22" t="str">
+        <x:v>contracts/0xcf2bd216729092e9726f21116f380d412bd4a32e/verification.json</x:v>
+      </x:c>
+      <x:c r="S73" s="22" t="str"/>
+      <x:c r="T73" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="18" customHeight="1">
+      <x:c r="A74" s="22" t="str">
+        <x:v>0xcfdffa11672688131bbeba3af1596055e0fa7498</x:v>
+      </x:c>
+      <x:c r="B74" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C74" s="22" t="str">
+        <x:v>contracts/0xcfdffa11672688131bbeba3af1596055e0fa7498</x:v>
+      </x:c>
+      <x:c r="D74" s="22" t="str">
+        <x:v>contracts/0xcfdffa11672688131bbeba3af1596055e0fa7498/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E74" s="22" t="str">
+        <x:v>5e200d6718a6e02fa003036c5f784795fc64f4ce606ae939d1fa01e38d5c40f2</x:v>
+      </x:c>
+      <x:c r="F74" s="20" t="n">
+        <x:v>6682</x:v>
+      </x:c>
+      <x:c r="G74" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H74" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I74" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J74" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K74" s="22" t="str">
+        <x:v>Winner</x:v>
+      </x:c>
+      <x:c r="L74" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M74" s="22" t="str">
+        <x:v>0.4.24+commit.e67f0147</x:v>
+      </x:c>
+      <x:c r="N74" s="22" t="str">
+        <x:v>contracts/0xcfdffa11672688131bbeba3af1596055e0fa7498/abi.json</x:v>
+      </x:c>
+      <x:c r="O74" s="22" t="str">
+        <x:v>contracts/0xcfdffa11672688131bbeba3af1596055e0fa7498/metadata.json</x:v>
+      </x:c>
+      <x:c r="P74" s="22" t="str">
+        <x:v>contracts/0xcfdffa11672688131bbeba3af1596055e0fa7498/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q74" s="22" t="str"/>
+      <x:c r="R74" s="22" t="str">
+        <x:v>contracts/0xcfdffa11672688131bbeba3af1596055e0fa7498/verification.json</x:v>
+      </x:c>
+      <x:c r="S74" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0xcfdffa11672688131bbeba3af1596055e0fa7498?fields=all</x:v>
+      </x:c>
+      <x:c r="T74" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="18" customHeight="1">
+      <x:c r="A75" s="22" t="str">
+        <x:v>0xd642b2892f9fd56d2e6290007909940c5bd83ff8</x:v>
+      </x:c>
+      <x:c r="B75" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C75" s="22" t="str">
+        <x:v>contracts/0xd642b2892f9fd56d2e6290007909940c5bd83ff8</x:v>
+      </x:c>
+      <x:c r="D75" s="22" t="str">
+        <x:v>contracts/0xd642b2892f9fd56d2e6290007909940c5bd83ff8/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E75" s="22" t="str">
+        <x:v>e8cd0ee9aa14f08efc41883fdfb726caf9e6cc145844e2e33bddfc47700142ca</x:v>
+      </x:c>
+      <x:c r="F75" s="20" t="n">
+        <x:v>10290</x:v>
+      </x:c>
+      <x:c r="G75" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H75" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I75" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J75" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K75" s="22" t="str"/>
+      <x:c r="L75" s="22" t="str"/>
+      <x:c r="M75" s="22" t="str"/>
+      <x:c r="N75" s="22" t="str"/>
+      <x:c r="O75" s="22" t="str"/>
+      <x:c r="P75" s="22" t="str"/>
+      <x:c r="Q75" s="22" t="str"/>
+      <x:c r="R75" s="22" t="str">
+        <x:v>contracts/0xd642b2892f9fd56d2e6290007909940c5bd83ff8/verification.json</x:v>
+      </x:c>
+      <x:c r="S75" s="22" t="str"/>
+      <x:c r="T75" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="18" customHeight="1">
+      <x:c r="A76" s="22" t="str">
+        <x:v>0xda5c71f78c34f3315eb4458939ad84ee78e0d8e7</x:v>
+      </x:c>
+      <x:c r="B76" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C76" s="22" t="str">
+        <x:v>contracts/0xda5c71f78c34f3315eb4458939ad84ee78e0d8e7</x:v>
+      </x:c>
+      <x:c r="D76" s="22" t="str">
+        <x:v>contracts/0xda5c71f78c34f3315eb4458939ad84ee78e0d8e7/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E76" s="22" t="str">
+        <x:v>e8358bce56a22dc4d4ffc169f295181d701a9b3e05254b694b79bd3a081802c9</x:v>
+      </x:c>
+      <x:c r="F76" s="20" t="n">
+        <x:v>8309</x:v>
+      </x:c>
+      <x:c r="G76" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H76" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I76" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J76" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K76" s="22" t="str"/>
+      <x:c r="L76" s="22" t="str"/>
+      <x:c r="M76" s="22" t="str"/>
+      <x:c r="N76" s="22" t="str"/>
+      <x:c r="O76" s="22" t="str"/>
+      <x:c r="P76" s="22" t="str"/>
+      <x:c r="Q76" s="22" t="str"/>
+      <x:c r="R76" s="22" t="str">
+        <x:v>contracts/0xda5c71f78c34f3315eb4458939ad84ee78e0d8e7/verification.json</x:v>
+      </x:c>
+      <x:c r="S76" s="22" t="str"/>
+      <x:c r="T76" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="18" customHeight="1">
+      <x:c r="A77" s="22" t="str">
+        <x:v>0xdd423fb05fccdfc37ea730b8f7965332c19f25f4</x:v>
+      </x:c>
+      <x:c r="B77" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C77" s="22" t="str">
+        <x:v>contracts/0xdd423fb05fccdfc37ea730b8f7965332c19f25f4</x:v>
+      </x:c>
+      <x:c r="D77" s="22" t="str">
+        <x:v>contracts/0xdd423fb05fccdfc37ea730b8f7965332c19f25f4/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E77" s="22" t="str">
+        <x:v>9859ed131bb8041cbab2127893cb35b464d24f0c74eb4289ab53e8241f72399e</x:v>
+      </x:c>
+      <x:c r="F77" s="20" t="n">
+        <x:v>7087</x:v>
+      </x:c>
+      <x:c r="G77" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H77" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I77" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J77" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K77" s="22" t="str"/>
+      <x:c r="L77" s="22" t="str"/>
+      <x:c r="M77" s="22" t="str"/>
+      <x:c r="N77" s="22" t="str"/>
+      <x:c r="O77" s="22" t="str"/>
+      <x:c r="P77" s="22" t="str"/>
+      <x:c r="Q77" s="22" t="str"/>
+      <x:c r="R77" s="22" t="str">
+        <x:v>contracts/0xdd423fb05fccdfc37ea730b8f7965332c19f25f4/verification.json</x:v>
+      </x:c>
+      <x:c r="S77" s="22" t="str"/>
+      <x:c r="T77" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="18" customHeight="1">
+      <x:c r="A78" s="22" t="str">
+        <x:v>0xe35518c73996fdc7e4db7733d4e98209dd5a1768</x:v>
+      </x:c>
+      <x:c r="B78" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C78" s="22" t="str">
+        <x:v>contracts/0xe35518c73996fdc7e4db7733d4e98209dd5a1768</x:v>
+      </x:c>
+      <x:c r="D78" s="22" t="str">
+        <x:v>contracts/0xe35518c73996fdc7e4db7733d4e98209dd5a1768/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E78" s="22" t="str">
+        <x:v>c2cfd2aa3d04ffe1f59543ddff8209e36425e0ec8b59574ca8572f72f3f7ddf3</x:v>
+      </x:c>
+      <x:c r="F78" s="20" t="n">
+        <x:v>2837</x:v>
+      </x:c>
+      <x:c r="G78" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H78" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I78" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J78" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K78" s="22" t="str">
+        <x:v>Vesting</x:v>
+      </x:c>
+      <x:c r="L78" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M78" s="22" t="str">
+        <x:v>0.6.12+commit.27d51765</x:v>
+      </x:c>
+      <x:c r="N78" s="22" t="str">
+        <x:v>contracts/0xe35518c73996fdc7e4db7733d4e98209dd5a1768/abi.json</x:v>
+      </x:c>
+      <x:c r="O78" s="22" t="str">
+        <x:v>contracts/0xe35518c73996fdc7e4db7733d4e98209dd5a1768/metadata.json</x:v>
+      </x:c>
+      <x:c r="P78" s="22" t="str">
+        <x:v>contracts/0xe35518c73996fdc7e4db7733d4e98209dd5a1768/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q78" s="22" t="str">
+        <x:v>contracts/0xe35518c73996fdc7e4db7733d4e98209dd5a1768/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R78" s="22" t="str">
+        <x:v>contracts/0xe35518c73996fdc7e4db7733d4e98209dd5a1768/verification.json</x:v>
+      </x:c>
+      <x:c r="S78" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0xe35518c73996fdc7e4db7733d4e98209dd5a1768?fields=all</x:v>
+      </x:c>
+      <x:c r="T78" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="18" customHeight="1">
+      <x:c r="A79" s="22" t="str">
+        <x:v>0xe3b81fa71fc815e233cd5c2fe97f583ebe31b723</x:v>
+      </x:c>
+      <x:c r="B79" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C79" s="22" t="str">
+        <x:v>contracts/0xe3b81fa71fc815e233cd5c2fe97f583ebe31b723</x:v>
+      </x:c>
+      <x:c r="D79" s="22" t="str">
+        <x:v>contracts/0xe3b81fa71fc815e233cd5c2fe97f583ebe31b723/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E79" s="22" t="str">
+        <x:v>abbd122997eee54ab63b543e9396bbd5aed49deabdb8fb1979edd546c18ed521</x:v>
+      </x:c>
+      <x:c r="F79" s="20" t="n">
+        <x:v>13356</x:v>
+      </x:c>
+      <x:c r="G79" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H79" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I79" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J79" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K79" s="22" t="str"/>
+      <x:c r="L79" s="22" t="str"/>
+      <x:c r="M79" s="22" t="str"/>
+      <x:c r="N79" s="22" t="str"/>
+      <x:c r="O79" s="22" t="str"/>
+      <x:c r="P79" s="22" t="str"/>
+      <x:c r="Q79" s="22" t="str"/>
+      <x:c r="R79" s="22" t="str">
+        <x:v>contracts/0xe3b81fa71fc815e233cd5c2fe97f583ebe31b723/verification.json</x:v>
+      </x:c>
+      <x:c r="S79" s="22" t="str"/>
+      <x:c r="T79" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="18" customHeight="1">
+      <x:c r="A80" s="22" t="str">
+        <x:v>0xe53a78e8744568904741d5d0139fad45b1df104b</x:v>
+      </x:c>
+      <x:c r="B80" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C80" s="22" t="str">
+        <x:v>contracts/0xe53a78e8744568904741d5d0139fad45b1df104b</x:v>
+      </x:c>
+      <x:c r="D80" s="22" t="str">
+        <x:v>contracts/0xe53a78e8744568904741d5d0139fad45b1df104b/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E80" s="22" t="str">
+        <x:v>955a10de59e993fd3364ad086ca19a035ee43585e610b9eff41f8eeef3c2952e</x:v>
+      </x:c>
+      <x:c r="F80" s="20" t="n">
+        <x:v>20838</x:v>
+      </x:c>
+      <x:c r="G80" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H80" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I80" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J80" s="20" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K80" s="22" t="str">
+        <x:v>BadgerRenCrvPlus</x:v>
+      </x:c>
+      <x:c r="L80" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M80" s="22" t="str">
+        <x:v>0.8.0+commit.c7dfd78e</x:v>
+      </x:c>
+      <x:c r="N80" s="22" t="str">
+        <x:v>contracts/0xe53a78e8744568904741d5d0139fad45b1df104b/abi.json</x:v>
+      </x:c>
+      <x:c r="O80" s="22" t="str">
+        <x:v>contracts/0xe53a78e8744568904741d5d0139fad45b1df104b/metadata.json</x:v>
+      </x:c>
+      <x:c r="P80" s="22" t="str">
+        <x:v>contracts/0xe53a78e8744568904741d5d0139fad45b1df104b/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q80" s="22" t="str">
+        <x:v>contracts/0xe53a78e8744568904741d5d0139fad45b1df104b/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R80" s="22" t="str">
+        <x:v>contracts/0xe53a78e8744568904741d5d0139fad45b1df104b/verification.json</x:v>
+      </x:c>
+      <x:c r="S80" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0xe53a78e8744568904741d5d0139fad45b1df104b?fields=all</x:v>
+      </x:c>
+      <x:c r="T80" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="18" customHeight="1">
+      <x:c r="A81" s="22" t="str">
+        <x:v>0xe6abfcabe24f06197a7a20dc9c81c251f2862430</x:v>
+      </x:c>
+      <x:c r="B81" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C81" s="22" t="str">
+        <x:v>contracts/0xe6abfcabe24f06197a7a20dc9c81c251f2862430</x:v>
+      </x:c>
+      <x:c r="D81" s="22" t="str">
+        <x:v>contracts/0xe6abfcabe24f06197a7a20dc9c81c251f2862430/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E81" s="22" t="str">
+        <x:v>6ebc0f7f093351005b9e041aad9ac7408d0b79b6b2da83e4b8deb8ed44d6e798</x:v>
+      </x:c>
+      <x:c r="F81" s="20" t="n">
+        <x:v>21741</x:v>
+      </x:c>
+      <x:c r="G81" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H81" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I81" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J81" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K81" s="22" t="str">
+        <x:v>LoopringAmmPool</x:v>
+      </x:c>
+      <x:c r="L81" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M81" s="22" t="str">
+        <x:v>0.7.0+commit.9e61f92b</x:v>
+      </x:c>
+      <x:c r="N81" s="22" t="str">
+        <x:v>contracts/0xe6abfcabe24f06197a7a20dc9c81c251f2862430/abi.json</x:v>
+      </x:c>
+      <x:c r="O81" s="22" t="str">
+        <x:v>contracts/0xe6abfcabe24f06197a7a20dc9c81c251f2862430/metadata.json</x:v>
+      </x:c>
+      <x:c r="P81" s="22" t="str">
+        <x:v>contracts/0xe6abfcabe24f06197a7a20dc9c81c251f2862430/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q81" s="22" t="str">
+        <x:v>contracts/0xe6abfcabe24f06197a7a20dc9c81c251f2862430/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R81" s="22" t="str">
+        <x:v>contracts/0xe6abfcabe24f06197a7a20dc9c81c251f2862430/verification.json</x:v>
+      </x:c>
+      <x:c r="S81" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0xe6abfcabe24f06197a7a20dc9c81c251f2862430?fields=all</x:v>
+      </x:c>
+      <x:c r="T81" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="18" customHeight="1">
+      <x:c r="A82" s="22" t="str">
+        <x:v>0xee2003f259a882f9ffa3bc2b602b02607462b846</x:v>
+      </x:c>
+      <x:c r="B82" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C82" s="22" t="str">
+        <x:v>contracts/0xee2003f259a882f9ffa3bc2b602b02607462b846</x:v>
+      </x:c>
+      <x:c r="D82" s="22" t="str">
+        <x:v>contracts/0xee2003f259a882f9ffa3bc2b602b02607462b846/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E82" s="22" t="str">
+        <x:v>4fd5dc30823b12d9726c80cac22f2bdf9c651775244be88d6be1ea08de2e5684</x:v>
+      </x:c>
+      <x:c r="F82" s="20" t="n">
+        <x:v>6958</x:v>
+      </x:c>
+      <x:c r="G82" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H82" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I82" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J82" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K82" s="22" t="str"/>
+      <x:c r="L82" s="22" t="str"/>
+      <x:c r="M82" s="22" t="str"/>
+      <x:c r="N82" s="22" t="str"/>
+      <x:c r="O82" s="22" t="str"/>
+      <x:c r="P82" s="22" t="str"/>
+      <x:c r="Q82" s="22" t="str"/>
+      <x:c r="R82" s="22" t="str">
+        <x:v>contracts/0xee2003f259a882f9ffa3bc2b602b02607462b846/verification.json</x:v>
+      </x:c>
+      <x:c r="S82" s="22" t="str"/>
+      <x:c r="T82" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="18" customHeight="1">
+      <x:c r="A83" s="22" t="str">
+        <x:v>0xf335fc85f32d2373a03d2c4ad06b644187780c13</x:v>
+      </x:c>
+      <x:c r="B83" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C83" s="22" t="str">
+        <x:v>contracts/0xf335fc85f32d2373a03d2c4ad06b644187780c13</x:v>
+      </x:c>
+      <x:c r="D83" s="22" t="str">
+        <x:v>contracts/0xf335fc85f32d2373a03d2c4ad06b644187780c13/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E83" s="22" t="str">
+        <x:v>9e2b9b3542883a4a011c01a1cbfae59680a5fdc33912e1493a9814699a55ca41</x:v>
+      </x:c>
+      <x:c r="F83" s="20" t="n">
+        <x:v>3383</x:v>
+      </x:c>
+      <x:c r="G83" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H83" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I83" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J83" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K83" s="22" t="str"/>
+      <x:c r="L83" s="22" t="str"/>
+      <x:c r="M83" s="22" t="str"/>
+      <x:c r="N83" s="22" t="str"/>
+      <x:c r="O83" s="22" t="str"/>
+      <x:c r="P83" s="22" t="str"/>
+      <x:c r="Q83" s="22" t="str"/>
+      <x:c r="R83" s="22" t="str">
+        <x:v>contracts/0xf335fc85f32d2373a03d2c4ad06b644187780c13/verification.json</x:v>
+      </x:c>
+      <x:c r="S83" s="22" t="str"/>
+      <x:c r="T83" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="18" customHeight="1">
+      <x:c r="A84" s="22" t="str">
+        <x:v>0xf61f1450d38848e7df7cc9dfe1019a397c392055</x:v>
+      </x:c>
+      <x:c r="B84" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C84" s="22" t="str">
+        <x:v>contracts/0xf61f1450d38848e7df7cc9dfe1019a397c392055</x:v>
+      </x:c>
+      <x:c r="D84" s="22" t="str">
+        <x:v>contracts/0xf61f1450d38848e7df7cc9dfe1019a397c392055/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E84" s="22" t="str">
+        <x:v>9f4d944d024557a925df323b3afb0ef824a59cacf4adde13e3c68a9b4b72d007</x:v>
+      </x:c>
+      <x:c r="F84" s="20" t="n">
+        <x:v>1670</x:v>
+      </x:c>
+      <x:c r="G84" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H84" s="22" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="I84" s="22" t="str">
+        <x:v>unavailable</x:v>
+      </x:c>
+      <x:c r="J84" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K84" s="22" t="str"/>
+      <x:c r="L84" s="22" t="str"/>
+      <x:c r="M84" s="22" t="str"/>
+      <x:c r="N84" s="22" t="str"/>
+      <x:c r="O84" s="22" t="str"/>
+      <x:c r="P84" s="22" t="str"/>
+      <x:c r="Q84" s="22" t="str"/>
+      <x:c r="R84" s="22" t="str">
+        <x:v>contracts/0xf61f1450d38848e7df7cc9dfe1019a397c392055/verification.json</x:v>
+      </x:c>
+      <x:c r="S84" s="22" t="str"/>
+      <x:c r="T84" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="18" customHeight="1">
+      <x:c r="A85" s="22" t="str">
+        <x:v>0xf9e266af4bca5890e2781812cc6a6e89495a79f2</x:v>
+      </x:c>
+      <x:c r="B85" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C85" s="22" t="str">
+        <x:v>contracts/0xf9e266af4bca5890e2781812cc6a6e89495a79f2</x:v>
+      </x:c>
+      <x:c r="D85" s="22" t="str">
+        <x:v>contracts/0xf9e266af4bca5890e2781812cc6a6e89495a79f2/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E85" s="22" t="str">
+        <x:v>74e5883541ea918b0c2dae357920b953302a7685da3d73c2623cfc7fef88174f</x:v>
+      </x:c>
+      <x:c r="F85" s="20" t="n">
+        <x:v>2082</x:v>
+      </x:c>
+      <x:c r="G85" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H85" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I85" s="22" t="str">
+        <x:v>match</x:v>
+      </x:c>
+      <x:c r="J85" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K85" s="22" t="str">
+        <x:v>AuthenticatedProxy</x:v>
+      </x:c>
+      <x:c r="L85" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M85" s="22" t="str">
+        <x:v>0.4.23+commit.124ca40d</x:v>
+      </x:c>
+      <x:c r="N85" s="22" t="str">
+        <x:v>contracts/0xf9e266af4bca5890e2781812cc6a6e89495a79f2/abi.json</x:v>
+      </x:c>
+      <x:c r="O85" s="22" t="str">
+        <x:v>contracts/0xf9e266af4bca5890e2781812cc6a6e89495a79f2/metadata.json</x:v>
+      </x:c>
+      <x:c r="P85" s="22" t="str">
+        <x:v>contracts/0xf9e266af4bca5890e2781812cc6a6e89495a79f2/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q85" s="22" t="str"/>
+      <x:c r="R85" s="22" t="str">
+        <x:v>contracts/0xf9e266af4bca5890e2781812cc6a6e89495a79f2/verification.json</x:v>
+      </x:c>
+      <x:c r="S85" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0xf9e266af4bca5890e2781812cc6a6e89495a79f2?fields=all</x:v>
+      </x:c>
+      <x:c r="T85" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="18" customHeight="1">
+      <x:c r="A86" s="22" t="str">
+        <x:v>0xfbf2310fefbe2f8969c58675406db2257ee66733</x:v>
+      </x:c>
+      <x:c r="B86" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C86" s="22" t="str">
+        <x:v>contracts/0xfbf2310fefbe2f8969c58675406db2257ee66733</x:v>
+      </x:c>
+      <x:c r="D86" s="22" t="str">
+        <x:v>contracts/0xfbf2310fefbe2f8969c58675406db2257ee66733/runtime-bytecode.hex</x:v>
+      </x:c>
+      <x:c r="E86" s="22" t="str">
+        <x:v>405b1caf0b54478d0a3d8a58072ac87d0f59ee16f20950f7703288f92962347b</x:v>
+      </x:c>
+      <x:c r="F86" s="20" t="n">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="G86" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H86" s="22" t="str">
+        <x:v>sourcify</x:v>
+      </x:c>
+      <x:c r="I86" s="22" t="str">
+        <x:v>exact_match</x:v>
+      </x:c>
+      <x:c r="J86" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K86" s="22" t="str">
+        <x:v>PriceOracleDelegate</x:v>
+      </x:c>
+      <x:c r="L86" s="22" t="str">
+        <x:v>solc</x:v>
+      </x:c>
+      <x:c r="M86" s="22" t="str">
+        <x:v>0.7.6+commit.7338295f</x:v>
+      </x:c>
+      <x:c r="N86" s="22" t="str">
+        <x:v>contracts/0xfbf2310fefbe2f8969c58675406db2257ee66733/abi.json</x:v>
+      </x:c>
+      <x:c r="O86" s="22" t="str">
+        <x:v>contracts/0xfbf2310fefbe2f8969c58675406db2257ee66733/metadata.json</x:v>
+      </x:c>
+      <x:c r="P86" s="22" t="str">
+        <x:v>contracts/0xfbf2310fefbe2f8969c58675406db2257ee66733/standard-json-input.json</x:v>
+      </x:c>
+      <x:c r="Q86" s="22" t="str">
+        <x:v>contracts/0xfbf2310fefbe2f8969c58675406db2257ee66733/storage-layout.json</x:v>
+      </x:c>
+      <x:c r="R86" s="22" t="str">
+        <x:v>contracts/0xfbf2310fefbe2f8969c58675406db2257ee66733/verification.json</x:v>
+      </x:c>
+      <x:c r="S86" s="22" t="str">
+        <x:v>https://sourcify.dev/server/v2/contract/1/0xfbf2310fefbe2f8969c58675406db2257ee66733?fields=all</x:v>
+      </x:c>
+      <x:c r="T86" s="7" t="n">
+        <x:v>46252.79980324074</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:conditionalFormatting sqref="G2:G86">
+    <x:cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <x:formula>TRUE</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra10eef2d9b7b4af2"/>
+  </x:tableParts>
+</x:worksheet>
 </file>